--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA12"/>
+  <dimension ref="A1:BA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
@@ -747,25 +747,25 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>24.66666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="O2" t="n">
-        <v>182.6666666666667</v>
+        <v>181.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="S2" t="n">
-        <v>4775000</v>
+        <v>5500000</v>
       </c>
       <c r="T2" t="n">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="U2" t="n">
         <v>19.33333333333333</v>
@@ -789,76 +789,76 @@
         <v>210</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.22377622377622</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
-        <v>179.2377622377622</v>
+        <v>179.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.027972027972028</v>
+        <v>1.018181818181818</v>
       </c>
       <c r="AE2" t="n">
-        <v>66.16083916083916</v>
+        <v>65.76363636363637</v>
       </c>
       <c r="AF2" t="n">
-        <v>1329195.804195804</v>
+        <v>1250681.818181818</v>
       </c>
       <c r="AG2" t="n">
-        <v>71.19580419580419</v>
+        <v>71.12727272727273</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.43506493506494</v>
+        <v>23.33636363636364</v>
       </c>
       <c r="AI2" t="n">
-        <v>180.0519480519481</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.116883116883117</v>
+        <v>1.127272727272727</v>
       </c>
       <c r="AK2" t="n">
-        <v>68.59740259740259</v>
+        <v>68.63636363636363</v>
       </c>
       <c r="AL2" t="n">
-        <v>3000000</v>
+        <v>3060000</v>
       </c>
       <c r="AM2" t="n">
-        <v>74.34415584415585</v>
+        <v>74.65454545454546</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.23881951381951</v>
+        <v>22.93070346320346</v>
       </c>
       <c r="AO2" t="n">
-        <v>180.5159020803757</v>
+        <v>180.5778155616313</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.095823474770843</v>
+        <v>1.070403850535429</v>
       </c>
       <c r="AQ2" t="n">
-        <v>64.87984690747848</v>
+        <v>64.45451526543631</v>
       </c>
       <c r="AR2" t="n">
-        <v>1282622.651471336</v>
+        <v>1235846.946912736</v>
       </c>
       <c r="AS2" t="n">
-        <v>71.44820179820179</v>
+        <v>71.44040043290042</v>
       </c>
       <c r="AT2" t="n">
-        <v>22.81501821920619</v>
+        <v>23.2796245407051</v>
       </c>
       <c r="AU2" t="n">
-        <v>180.4644517176486</v>
+        <v>180.743928056882</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.075317847824242</v>
+        <v>1.086749334780025</v>
       </c>
       <c r="AW2" t="n">
-        <v>63.91665265148321</v>
+        <v>64.10546347053061</v>
       </c>
       <c r="AX2" t="n">
-        <v>1854997.668837982</v>
+        <v>1879568.233957716</v>
       </c>
       <c r="AY2" t="n">
-        <v>72.31830830436969</v>
+        <v>72.02164611887119</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -878,11 +878,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
@@ -948,76 +948,76 @@
         <v>143</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.85324675324675</v>
+        <v>25.77636363636363</v>
       </c>
       <c r="AC3" t="n">
-        <v>182.3675324675325</v>
+        <v>182.4054545454545</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.012987012987013</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>66.25844155844156</v>
+        <v>66.05272727272727</v>
       </c>
       <c r="AF3" t="n">
-        <v>1641987.012987013</v>
+        <v>1592554.545454545</v>
       </c>
       <c r="AG3" t="n">
-        <v>71.14675324675325</v>
+        <v>70.99636363636363</v>
       </c>
       <c r="AH3" t="n">
-        <v>26.97272727272727</v>
+        <v>26.78454545454546</v>
       </c>
       <c r="AI3" t="n">
-        <v>179.8153846153846</v>
+        <v>179.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.226573426573426</v>
+        <v>1.224545454545455</v>
       </c>
       <c r="AK3" t="n">
-        <v>69.95104895104895</v>
+        <v>70.11636363636364</v>
       </c>
       <c r="AL3" t="n">
-        <v>3019000</v>
+        <v>2989850</v>
       </c>
       <c r="AM3" t="n">
-        <v>72.6895104895105</v>
+        <v>73.04636363636364</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.43162663616171</v>
+        <v>26.32858868184955</v>
       </c>
       <c r="AO3" t="n">
-        <v>181.2903101820438</v>
+        <v>181.4109627329193</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.093039425915294</v>
+        <v>1.101456176673568</v>
       </c>
       <c r="AQ3" t="n">
-        <v>65.644576272538</v>
+        <v>65.42633885438234</v>
       </c>
       <c r="AR3" t="n">
-        <v>1685322.9974961</v>
+        <v>1621075.241545894</v>
       </c>
       <c r="AS3" t="n">
-        <v>70.00988080014615</v>
+        <v>70.02966528640441</v>
       </c>
       <c r="AT3" t="n">
-        <v>25.35323857429121</v>
+        <v>25.44587681324523</v>
       </c>
       <c r="AU3" t="n">
-        <v>180.0550743116533</v>
+        <v>180.1224299384826</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.167335296282665</v>
+        <v>1.160869218500797</v>
       </c>
       <c r="AW3" t="n">
-        <v>64.49312325101799</v>
+        <v>64.65439355965673</v>
       </c>
       <c r="AX3" t="n">
-        <v>2463098.32053911</v>
+        <v>2615781.983367509</v>
       </c>
       <c r="AY3" t="n">
-        <v>69.22029710056026</v>
+        <v>69.23388623072833</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1079,118 +1079,118 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>28.66666666666667</v>
+        <v>26.25</v>
       </c>
       <c r="O4" t="n">
-        <v>186.6666666666667</v>
+        <v>185.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="S4" t="n">
-        <v>5250000</v>
+        <v>3000000</v>
       </c>
       <c r="T4" t="n">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>25.25</v>
       </c>
       <c r="V4" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>63</v>
+        <v>279</v>
       </c>
       <c r="Z4" t="n">
-        <v>1200000</v>
+        <v>8600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>292</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.9017316017316</v>
+        <v>26.85909090909091</v>
       </c>
       <c r="AC4" t="n">
-        <v>184.0265512265512</v>
+        <v>184.2027272727273</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.100432900432901</v>
+        <v>1.097272727272727</v>
       </c>
       <c r="AE4" t="n">
-        <v>66.99502164502165</v>
+        <v>66.78636363636363</v>
       </c>
       <c r="AF4" t="n">
-        <v>1382919.191919192</v>
+        <v>1346059.090909091</v>
       </c>
       <c r="AG4" t="n">
-        <v>70.12121212121212</v>
+        <v>70.10636363636364</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.92457386363636</v>
+        <v>25.96382575757576</v>
       </c>
       <c r="AI4" t="n">
-        <v>179.0431818181818</v>
+        <v>179.3113636363637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.172159090909091</v>
+        <v>1.153030303030303</v>
       </c>
       <c r="AK4" t="n">
-        <v>67.38082386363637</v>
+        <v>67.44109848484848</v>
       </c>
       <c r="AL4" t="n">
-        <v>3847017.755681818</v>
+        <v>3632716.856060606</v>
       </c>
       <c r="AM4" t="n">
-        <v>72.12556818181818</v>
+        <v>72.10227272727273</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.08319771289696</v>
+        <v>23.00339598997494</v>
       </c>
       <c r="AO4" t="n">
-        <v>182.1996549137996</v>
+        <v>183.0671052631579</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.011695906432749</v>
+        <v>1.016374269005848</v>
       </c>
       <c r="AQ4" t="n">
-        <v>61.52055124282568</v>
+        <v>61.38768588137009</v>
       </c>
       <c r="AR4" t="n">
-        <v>854969.6990040035</v>
+        <v>831602.4018379281</v>
       </c>
       <c r="AS4" t="n">
-        <v>70.93188246590502</v>
+        <v>70.98923141186299</v>
       </c>
       <c r="AT4" t="n">
-        <v>25.38523248259281</v>
+        <v>25.58493699228699</v>
       </c>
       <c r="AU4" t="n">
-        <v>179.1269429911703</v>
+        <v>179.544224383484</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.030477335164835</v>
+        <v>1.040636446886447</v>
       </c>
       <c r="AW4" t="n">
-        <v>65.7507114875966</v>
+        <v>65.94246160577221</v>
       </c>
       <c r="AX4" t="n">
-        <v>2067869.168324804</v>
+        <v>2327170.889970434</v>
       </c>
       <c r="AY4" t="n">
-        <v>70.66800877955043</v>
+        <v>70.67404307566383</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -1210,12 +1210,12 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1260,25 +1260,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.83333333333333</v>
+        <v>25.375</v>
       </c>
       <c r="O5" t="n">
-        <v>182.6666666666667</v>
+        <v>180.875</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>1.875</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>413</v>
+        <v>587</v>
       </c>
       <c r="S5" t="n">
-        <v>22925000</v>
+        <v>78425000</v>
       </c>
       <c r="T5" t="n">
-        <v>462</v>
+        <v>636</v>
       </c>
       <c r="U5" t="n">
         <v>37</v>
@@ -1302,76 +1302,76 @@
         <v>63</v>
       </c>
       <c r="AB5" t="n">
-        <v>27.16558441558442</v>
+        <v>27.46181818181818</v>
       </c>
       <c r="AC5" t="n">
-        <v>182.537012987013</v>
+        <v>182.1336363636364</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75974025974026</v>
+        <v>1.790909090909091</v>
       </c>
       <c r="AE5" t="n">
-        <v>73.46753246753246</v>
+        <v>74.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>6561055.194805195</v>
+        <v>7119590.909090909</v>
       </c>
       <c r="AG5" t="n">
-        <v>77.39285714285714</v>
+        <v>77.85090909090908</v>
       </c>
       <c r="AH5" t="n">
-        <v>25.56528925619835</v>
+        <v>25.62193362193362</v>
       </c>
       <c r="AI5" t="n">
-        <v>180.5613406795225</v>
+        <v>180.6487734487734</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>67.41340679522499</v>
+        <v>67.82525252525252</v>
       </c>
       <c r="AL5" t="n">
-        <v>2725716.253443526</v>
+        <v>2787283.54978355</v>
       </c>
       <c r="AM5" t="n">
-        <v>71.76391184573004</v>
+        <v>71.96810966810968</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.11151470621693</v>
+        <v>23.92445392203704</v>
       </c>
       <c r="AO5" t="n">
-        <v>183.9544779617533</v>
+        <v>184.1204358131212</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.219615856375995</v>
+        <v>1.144962198926394</v>
       </c>
       <c r="AQ5" t="n">
-        <v>67.81001379648851</v>
+        <v>67.72610264841722</v>
       </c>
       <c r="AR5" t="n">
-        <v>3041481.359684342</v>
+        <v>2630761.403558079</v>
       </c>
       <c r="AS5" t="n">
-        <v>74.12132020868547</v>
+        <v>74.334431625493</v>
       </c>
       <c r="AT5" t="n">
-        <v>23.90340912865326</v>
+        <v>24.17868408232858</v>
       </c>
       <c r="AU5" t="n">
-        <v>181.4119797595646</v>
+        <v>181.1473161003532</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>64.01180257586326</v>
+        <v>64.79033308975764</v>
       </c>
       <c r="AX5" t="n">
-        <v>1576479.064946137</v>
+        <v>1776521.967482645</v>
       </c>
       <c r="AY5" t="n">
-        <v>70.52551943522649</v>
+        <v>70.86835342832785</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
+          <t xml:space="preserve">penso c 
   usa </t>
         </is>
       </c>
@@ -1437,118 +1437,118 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>26.5</v>
+        <v>29.2</v>
       </c>
       <c r="O6" t="n">
-        <v>183</v>
+        <v>181.2</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>128</v>
+        <v>342</v>
       </c>
       <c r="S6" t="n">
-        <v>1300000</v>
+        <v>5775000</v>
       </c>
       <c r="T6" t="n">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="U6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V6" t="n">
-        <v>178.5</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>130</v>
+        <v>392</v>
       </c>
       <c r="Z6" t="n">
-        <v>1650000</v>
+        <v>6050000</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>411</v>
       </c>
       <c r="AB6" t="n">
-        <v>26.12922077922078</v>
+        <v>26.16272727272727</v>
       </c>
       <c r="AC6" t="n">
-        <v>182.3272727272727</v>
+        <v>182.2854545454546</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.153896103896104</v>
+        <v>1.151818181818182</v>
       </c>
       <c r="AE6" t="n">
-        <v>64.51753246753246</v>
+        <v>64.50636363636363</v>
       </c>
       <c r="AF6" t="n">
-        <v>1889769.480519481</v>
+        <v>1855722.727272727</v>
       </c>
       <c r="AG6" t="n">
-        <v>68.01298701298701</v>
+        <v>67.8909090909091</v>
       </c>
       <c r="AH6" t="n">
-        <v>27.51748251748252</v>
+        <v>27.72727272727273</v>
       </c>
       <c r="AI6" t="n">
-        <v>183.4825174825175</v>
+        <v>183.6818181818182</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13986013986014</v>
+        <v>1.154545454545455</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.83216783216783</v>
+        <v>69.23636363636362</v>
       </c>
       <c r="AL6" t="n">
-        <v>3155419.58041958</v>
+        <v>3228409.090909091</v>
       </c>
       <c r="AM6" t="n">
-        <v>70.71328671328673</v>
+        <v>71.06363636363638</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.22732471117564</v>
+        <v>23.19238095238095</v>
       </c>
       <c r="AO6" t="n">
-        <v>179.4231532152421</v>
+        <v>178.7954887218045</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.101663708961846</v>
+        <v>1.129285714285714</v>
       </c>
       <c r="AQ6" t="n">
-        <v>62.85069107457142</v>
+        <v>62.94058479532164</v>
       </c>
       <c r="AR6" t="n">
-        <v>1350402.842757657</v>
+        <v>1495403.571428571</v>
       </c>
       <c r="AS6" t="n">
-        <v>68.83825373710958</v>
+        <v>69.0945948203843</v>
       </c>
       <c r="AT6" t="n">
-        <v>27.79737597965023</v>
+        <v>27.72013855709508</v>
       </c>
       <c r="AU6" t="n">
-        <v>182.9625849345749</v>
+        <v>182.9667283803154</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.039589034154252</v>
+        <v>1.046920289855072</v>
       </c>
       <c r="AW6" t="n">
-        <v>65.58442407648093</v>
+        <v>65.65758679726072</v>
       </c>
       <c r="AX6" t="n">
-        <v>1125139.076363993</v>
+        <v>1139612.617455009</v>
       </c>
       <c r="AY6" t="n">
-        <v>66.71321543562347</v>
+        <v>66.79709348622393</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.86458333334</v>
+        <v>45462.98958333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
@@ -1612,106 +1612,124 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>183</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>138</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>141</v>
+      </c>
       <c r="U7" t="n">
-        <v>26.66666666666667</v>
+        <v>28.8</v>
       </c>
       <c r="V7" t="n">
-        <v>180.3333333333333</v>
+        <v>179</v>
       </c>
       <c r="W7" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>181</v>
+        <v>353</v>
       </c>
       <c r="Z7" t="n">
-        <v>1055000</v>
+        <v>15575000</v>
       </c>
       <c r="AA7" t="n">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.63076923076924</v>
+        <v>25.34444444444445</v>
       </c>
       <c r="AC7" t="n">
-        <v>178.9846153846154</v>
+        <v>179.3222222222222</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.6846153846154</v>
+        <v>69.3111111111111</v>
       </c>
       <c r="AF7" t="n">
-        <v>4039230.769230769</v>
+        <v>3874777.777777778</v>
       </c>
       <c r="AG7" t="n">
-        <v>73.24615384615385</v>
+        <v>73.35555555555555</v>
       </c>
       <c r="AH7" t="n">
-        <v>25.64025974025973</v>
+        <v>25.59545454545454</v>
       </c>
       <c r="AI7" t="n">
-        <v>183.4850649350649</v>
+        <v>183.4063636363636</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.079220779220779</v>
+        <v>1.073636363636364</v>
       </c>
       <c r="AK7" t="n">
-        <v>69.42922077922078</v>
+        <v>69.24181818181818</v>
       </c>
       <c r="AL7" t="n">
-        <v>3004616.883116883</v>
+        <v>2936227.272727272</v>
       </c>
       <c r="AM7" t="n">
-        <v>73.42402597402598</v>
+        <v>73.27636363636364</v>
       </c>
       <c r="AN7" t="n">
-        <v>24.56049074091879</v>
+        <v>24.45924268258028</v>
       </c>
       <c r="AO7" t="n">
-        <v>181.4053023075099</v>
+        <v>181.2287463294497</v>
       </c>
       <c r="AP7" t="n">
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>62.01126155443695</v>
+        <v>61.72912522496922</v>
       </c>
       <c r="AR7" t="n">
-        <v>1374300.107008127</v>
+        <v>1403723.797006725</v>
       </c>
       <c r="AS7" t="n">
-        <v>67.14983821199664</v>
+        <v>67.0782750781472</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.96542185055841</v>
+        <v>24.93868173493174</v>
       </c>
       <c r="AU7" t="n">
-        <v>181.9164002489108</v>
+        <v>181.4606655844156</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.098266037184104</v>
+        <v>1.084922161172161</v>
       </c>
       <c r="AW7" t="n">
-        <v>65.26840008730765</v>
+        <v>65.96540459540459</v>
       </c>
       <c r="AX7" t="n">
-        <v>1582963.951664582</v>
+        <v>1684907.450882451</v>
       </c>
       <c r="AY7" t="n">
-        <v>70.46450449060742</v>
+        <v>71.07748792873792</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -1731,11 +1749,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
@@ -1805,76 +1823,76 @@
         <v>149</v>
       </c>
       <c r="AB8" t="n">
-        <v>28.10844155844156</v>
+        <v>27.90090909090909</v>
       </c>
       <c r="AC8" t="n">
-        <v>179.6675324675325</v>
+        <v>179.7827272727273</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.103246753246753</v>
+        <v>1.105454545454545</v>
       </c>
       <c r="AE8" t="n">
-        <v>67.50779220779221</v>
+        <v>67.44363636363637</v>
       </c>
       <c r="AF8" t="n">
-        <v>2268766.233766234</v>
+        <v>2237772.727272728</v>
       </c>
       <c r="AG8" t="n">
-        <v>68.67077922077921</v>
+        <v>68.71909090909091</v>
       </c>
       <c r="AH8" t="n">
-        <v>27.7077441077441</v>
+        <v>27.66758494031221</v>
       </c>
       <c r="AI8" t="n">
-        <v>180.7290235690236</v>
+        <v>180.6966023875115</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.336498316498317</v>
+        <v>1.326629935720845</v>
       </c>
       <c r="AK8" t="n">
-        <v>72.32114478114478</v>
+        <v>72.14040404040405</v>
       </c>
       <c r="AL8" t="n">
-        <v>4210488.215488215</v>
+        <v>4181244.260789715</v>
       </c>
       <c r="AM8" t="n">
-        <v>75.02612794612793</v>
+        <v>74.93645546372818</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.4258960353783</v>
+        <v>28.06321873524391</v>
       </c>
       <c r="AO8" t="n">
-        <v>181.1344658878044</v>
+        <v>180.8864665286404</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.319765057052569</v>
+        <v>1.285171079873597</v>
       </c>
       <c r="AQ8" t="n">
-        <v>65.48530020703933</v>
+        <v>65.19013457556936</v>
       </c>
       <c r="AR8" t="n">
-        <v>1121186.492045331</v>
+        <v>1072562.874577749</v>
       </c>
       <c r="AS8" t="n">
-        <v>67.21833624563479</v>
+        <v>67.14049217246013</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.68044716768502</v>
+        <v>25.83136790487407</v>
       </c>
       <c r="AU8" t="n">
-        <v>179.625812292756</v>
+        <v>179.5382510840834</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.008465608465609</v>
+        <v>1.011544011544012</v>
       </c>
       <c r="AW8" t="n">
-        <v>66.78767829191742</v>
+        <v>67.0921442797431</v>
       </c>
       <c r="AX8" t="n">
-        <v>1700075.425705061</v>
+        <v>1824500.677631999</v>
       </c>
       <c r="AY8" t="n">
-        <v>72.44477395603354</v>
+        <v>72.38689622043202</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
@@ -1894,11 +1912,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
@@ -1986,76 +2004,76 @@
         <v>216</v>
       </c>
       <c r="AB9" t="n">
-        <v>25.95939393939394</v>
+        <v>25.84015151515152</v>
       </c>
       <c r="AC9" t="n">
-        <v>182.6454545454545</v>
+        <v>182.5924242424242</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.057575757575758</v>
+        <v>1.071969696969697</v>
       </c>
       <c r="AE9" t="n">
-        <v>67.2060606060606</v>
+        <v>67.51287878787879</v>
       </c>
       <c r="AF9" t="n">
-        <v>2460869.696969697</v>
+        <v>2631750</v>
       </c>
       <c r="AG9" t="n">
-        <v>70.97939393939394</v>
+        <v>71.30454545454546</v>
       </c>
       <c r="AH9" t="n">
-        <v>26.03566433566434</v>
+        <v>26.02818181818181</v>
       </c>
       <c r="AI9" t="n">
-        <v>181.4573426573427</v>
+        <v>181.6763636363636</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>65.45454545454545</v>
+        <v>65.36363636363636</v>
       </c>
       <c r="AL9" t="n">
-        <v>1218524.475524476</v>
+        <v>1179536.363636364</v>
       </c>
       <c r="AM9" t="n">
-        <v>69.68391608391609</v>
+        <v>69.55272727272728</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.723774161257</v>
+        <v>24.73982791299725</v>
       </c>
       <c r="AO9" t="n">
-        <v>179.89202755038</v>
+        <v>179.8979404208809</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.041961788529294</v>
+        <v>1.035785568994951</v>
       </c>
       <c r="AQ9" t="n">
-        <v>63.09661408131659</v>
+        <v>63.35205415135334</v>
       </c>
       <c r="AR9" t="n">
-        <v>1407335.49162508</v>
+        <v>1495196.242624017</v>
       </c>
       <c r="AS9" t="n">
-        <v>69.17287843671711</v>
+        <v>69.40809084841551</v>
       </c>
       <c r="AT9" t="n">
-        <v>24.64648307158429</v>
+        <v>24.6796679197995</v>
       </c>
       <c r="AU9" t="n">
-        <v>180.3154408007647</v>
+        <v>180.5982598541809</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>64.09366791553026</v>
+        <v>64.16247341839446</v>
       </c>
       <c r="AX9" t="n">
-        <v>1223507.308593341</v>
+        <v>1254934.272233614</v>
       </c>
       <c r="AY9" t="n">
-        <v>69.93113712648126</v>
+        <v>70.02925115819853</v>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
@@ -2075,12 +2093,12 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2119,7 +2137,11 @@
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
       <c r="N10" t="n">
         <v>20</v>
       </c>
@@ -2163,76 +2185,76 @@
         <v>66</v>
       </c>
       <c r="AB10" t="n">
-        <v>26.57393939393939</v>
+        <v>26.61735537190083</v>
       </c>
       <c r="AC10" t="n">
-        <v>180.4078787878788</v>
+        <v>180.3826446280991</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.098181818181818</v>
+        <v>1.133884297520661</v>
       </c>
       <c r="AE10" t="n">
-        <v>67.31030303030302</v>
+        <v>67.50578512396693</v>
       </c>
       <c r="AF10" t="n">
-        <v>1619018.181818182</v>
+        <v>1759818.181818182</v>
       </c>
       <c r="AG10" t="n">
-        <v>70.57333333333332</v>
+        <v>70.64132231404959</v>
       </c>
       <c r="AH10" t="n">
-        <v>26.78481877599524</v>
+        <v>26.66476301476302</v>
       </c>
       <c r="AI10" t="n">
-        <v>180.4496137849079</v>
+        <v>180.2187257187258</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23630421865716</v>
+        <v>1.216705516705517</v>
       </c>
       <c r="AK10" t="n">
-        <v>68.84061200237672</v>
+        <v>68.66080031080031</v>
       </c>
       <c r="AL10" t="n">
-        <v>1992267.082590612</v>
+        <v>2007041.56954157</v>
       </c>
       <c r="AM10" t="n">
-        <v>72.5090017825312</v>
+        <v>72.51177156177155</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.58097359140164</v>
+        <v>25.85980640076444</v>
       </c>
       <c r="AO10" t="n">
-        <v>179.8388149719143</v>
+        <v>180.0899630618365</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.092448206335674</v>
+        <v>1.126065735912283</v>
       </c>
       <c r="AQ10" t="n">
-        <v>63.97884617190041</v>
+        <v>64.60916292054705</v>
       </c>
       <c r="AR10" t="n">
-        <v>1264711.827067181</v>
+        <v>1412430.076615185</v>
       </c>
       <c r="AS10" t="n">
-        <v>68.35640899988321</v>
+        <v>68.59733624271553</v>
       </c>
       <c r="AT10" t="n">
-        <v>23.99404787869944</v>
+        <v>23.79921708838118</v>
       </c>
       <c r="AU10" t="n">
-        <v>178.89482768768</v>
+        <v>179.0368941172347</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.071210762681786</v>
+        <v>1.081406244254541</v>
       </c>
       <c r="AW10" t="n">
-        <v>63.05503540354047</v>
+        <v>63.07696383423938</v>
       </c>
       <c r="AX10" t="n">
-        <v>1328970.712753911</v>
+        <v>1355801.399151244</v>
       </c>
       <c r="AY10" t="n">
-        <v>69.18852733129376</v>
+        <v>69.58794415079244</v>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
@@ -2252,12 +2274,12 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">allatin m 
+  usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2344,76 +2366,76 @@
         <v>207</v>
       </c>
       <c r="AB11" t="n">
-        <v>27.41534090909091</v>
+        <v>27.34545454545454</v>
       </c>
       <c r="AC11" t="n">
-        <v>179.8772727272727</v>
+        <v>180.069696969697</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.059659090909091</v>
+        <v>1.062878787878788</v>
       </c>
       <c r="AE11" t="n">
-        <v>66.87215909090909</v>
+        <v>66.42121212121212</v>
       </c>
       <c r="AF11" t="n">
-        <v>1298147.727272727</v>
+        <v>1230780.303030303</v>
       </c>
       <c r="AG11" t="n">
-        <v>69.43920454545454</v>
+        <v>69.1189393939394</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.42989898989898</v>
+        <v>24.15794306703398</v>
       </c>
       <c r="AI11" t="n">
-        <v>178.9856565656565</v>
+        <v>179.1077134986226</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>65.65481481481481</v>
+        <v>65.34545454545456</v>
       </c>
       <c r="AL11" t="n">
-        <v>1554275.757575758</v>
+        <v>1582396.235078053</v>
       </c>
       <c r="AM11" t="n">
-        <v>72.01636363636364</v>
+        <v>72.20615243342517</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.04284524316973</v>
+        <v>25.40655509546814</v>
       </c>
       <c r="AO11" t="n">
-        <v>179.6592397266878</v>
+        <v>179.8499830342765</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.063668046928917</v>
+        <v>1.068224062571889</v>
       </c>
       <c r="AQ11" t="n">
-        <v>63.02220460104331</v>
+        <v>63.68009633080285</v>
       </c>
       <c r="AR11" t="n">
-        <v>975371.0728494297</v>
+        <v>1042966.57752473</v>
       </c>
       <c r="AS11" t="n">
-        <v>67.61362118398084</v>
+        <v>67.90656027145157</v>
       </c>
       <c r="AT11" t="n">
-        <v>24.71882688283583</v>
+        <v>24.48492462902774</v>
       </c>
       <c r="AU11" t="n">
-        <v>178.4388714501375</v>
+        <v>178.4899162041426</v>
       </c>
       <c r="AV11" t="n">
         <v>1</v>
       </c>
       <c r="AW11" t="n">
-        <v>63.63651672756532</v>
+        <v>63.46415832127004</v>
       </c>
       <c r="AX11" t="n">
-        <v>1284595.377747903</v>
+        <v>1280216.722640621</v>
       </c>
       <c r="AY11" t="n">
-        <v>70.65049818326034</v>
+        <v>70.45146971205446</v>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
@@ -2433,11 +2455,11 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
@@ -2511,76 +2533,76 @@
         <v>143</v>
       </c>
       <c r="AB12" t="n">
-        <v>25.41538461538461</v>
+        <v>25.50909090909091</v>
       </c>
       <c r="AC12" t="n">
-        <v>182.0237762237762</v>
+        <v>182.2161616161616</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.186013986013986</v>
+        <v>1.187878787878788</v>
       </c>
       <c r="AE12" t="n">
-        <v>67.76643356643356</v>
+        <v>68.05656565656565</v>
       </c>
       <c r="AF12" t="n">
-        <v>2046923.076923077</v>
+        <v>2127121.212121212</v>
       </c>
       <c r="AG12" t="n">
-        <v>71.37342657342657</v>
+        <v>71.4989898989899</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.04603174603175</v>
+        <v>24.04444444444444</v>
       </c>
       <c r="AI12" t="n">
-        <v>180.4849206349206</v>
+        <v>180.3522222222222</v>
       </c>
       <c r="AJ12" t="n">
         <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>65.74047619047619</v>
+        <v>65.7511111111111</v>
       </c>
       <c r="AL12" t="n">
-        <v>1728174.603174603</v>
+        <v>1707611.111111111</v>
       </c>
       <c r="AM12" t="n">
-        <v>70.92619047619048</v>
+        <v>70.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>24.04090751421146</v>
+        <v>24.09024689620665</v>
       </c>
       <c r="AO12" t="n">
-        <v>181.8817194617201</v>
+        <v>182.3019099665385</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>65.14752886768635</v>
+        <v>65.10945210620133</v>
       </c>
       <c r="AR12" t="n">
-        <v>1341458.739764408</v>
+        <v>1396322.737827188</v>
       </c>
       <c r="AS12" t="n">
-        <v>70.06019598586903</v>
+        <v>70.07864011633362</v>
       </c>
       <c r="AT12" t="n">
-        <v>21.86984086276652</v>
+        <v>22.29428047584697</v>
       </c>
       <c r="AU12" t="n">
-        <v>179.1812053523142</v>
+        <v>178.877092127821</v>
       </c>
       <c r="AV12" t="n">
         <v>1</v>
       </c>
       <c r="AW12" t="n">
-        <v>60.31865047731872</v>
+        <v>60.92184447692121</v>
       </c>
       <c r="AX12" t="n">
-        <v>789533.8336180726</v>
+        <v>831408.5970118258</v>
       </c>
       <c r="AY12" t="n">
-        <v>69.4604778427029</v>
+        <v>69.37374800533368</v>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
@@ -2590,6 +2612,356 @@
       <c r="BA12" t="inlineStr">
         <is>
           <t>KtuTuMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>167</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>30</v>
+      </c>
+      <c r="O13" t="n">
+        <v>175</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>73</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>179.0222222222222</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.053333333333333</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70.39333333333335</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3685333.333333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>74.34444444444445</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22.71296296296297</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>181.4719135802469</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>66.37314814814815</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1814714.506172839</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>72.7179012345679</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23.83124502699631</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>177.333506322819</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.030081953071084</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>64.41886417610525</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1500116.242692729</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>70.51667169041529</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>21.41088734671765</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>180.6598569639199</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>62.47829359991382</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1392189.838854588</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>71.69059731035547</v>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>167</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>132</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>141</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26</v>
+      </c>
+      <c r="V14" t="n">
+        <v>178</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>26.91487603305785</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>180.9454545454545</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>69.38264462809917</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2445404.958677686</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>72.60000000000001</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>26.94090909090909</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>178.5090909090909</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>69.78545454545454</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2787800</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>72.15727272727273</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.35847958778673</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>180.6585589092506</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>65.68679969891897</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1516387.755725119</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>70.32874554660766</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>26.85608259877004</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>179.7434613756743</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>67.11750541805377</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1614080.925611178</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>69.13865637510813</v>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -1639,10 +1639,10 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="V7" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
@@ -1651,13 +1651,13 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Z7" t="n">
-        <v>15575000</v>
+        <v>11175000</v>
       </c>
       <c r="AA7" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AB7" t="n">
         <v>25.34444444444445</v>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>26.5</v>
       </c>
       <c r="O14" t="n">
-        <v>181.5</v>
+        <v>183</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -2853,13 +2853,13 @@
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="S14" t="n">
-        <v>2500000</v>
+        <v>6800000</v>
       </c>
       <c r="T14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="U14" t="n">
         <v>26</v>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA14"/>
+  <dimension ref="A1:BA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,35 +697,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23112</v>
+        <v>20371</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -742,167 +742,171 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
       <c r="N2" t="n">
-        <v>25.5</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
+        <v>186</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>63</v>
+      </c>
+      <c r="S2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U2" t="n">
+        <v>25</v>
+      </c>
+      <c r="V2" t="n">
         <v>181.5</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>258</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>275</v>
-      </c>
-      <c r="U2" t="n">
-        <v>19.33333333333333</v>
-      </c>
-      <c r="V2" t="n">
-        <v>180</v>
-      </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="Z2" t="n">
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>25.47907647907648</v>
       </c>
       <c r="AC2" t="n">
-        <v>179.5</v>
+        <v>180.620202020202</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.018181818181818</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>65.76363636363637</v>
+        <v>67.91096681096681</v>
       </c>
       <c r="AF2" t="n">
-        <v>1250681.818181818</v>
+        <v>2844783.54978355</v>
       </c>
       <c r="AG2" t="n">
-        <v>71.12727272727273</v>
+        <v>72.13953823953824</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.33636363636364</v>
+        <v>27.21212121212121</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>180.0530303030303</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.127272727272727</v>
+        <v>1.054545454545454</v>
       </c>
       <c r="AK2" t="n">
-        <v>68.63636363636363</v>
+        <v>66.05454545454545</v>
       </c>
       <c r="AL2" t="n">
-        <v>3060000</v>
+        <v>1177405.303030303</v>
       </c>
       <c r="AM2" t="n">
-        <v>74.65454545454546</v>
+        <v>68.96893939393939</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.93070346320346</v>
+        <v>24.52395262452807</v>
       </c>
       <c r="AO2" t="n">
-        <v>180.5778155616313</v>
+        <v>181.0610903056875</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.070403850535429</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>64.45451526543631</v>
+        <v>64.96388076969917</v>
       </c>
       <c r="AR2" t="n">
-        <v>1235846.946912736</v>
+        <v>1786551.196565583</v>
       </c>
       <c r="AS2" t="n">
-        <v>71.44040043290042</v>
+        <v>70.62392522226281</v>
       </c>
       <c r="AT2" t="n">
-        <v>23.2796245407051</v>
+        <v>25.28016620657925</v>
       </c>
       <c r="AU2" t="n">
-        <v>180.743928056882</v>
+        <v>180.0291497009432</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.086749334780025</v>
+        <v>1.068224062571889</v>
       </c>
       <c r="AW2" t="n">
-        <v>64.10546347053061</v>
+        <v>63.45648521969175</v>
       </c>
       <c r="AX2" t="n">
-        <v>1879568.233957716</v>
+        <v>1026174.910858063</v>
       </c>
       <c r="AY2" t="n">
-        <v>72.02164611887119</v>
+        <v>67.74128249367379</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>K4FYmLD</t>
+          <t>6gpXy3v</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>rXawJi8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>74500</v>
+        <v>20000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -918,150 +922,168 @@
         <v>2024</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>256</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>277</v>
+      </c>
       <c r="U3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V3" t="n">
-        <v>186.5</v>
+        <v>175</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="Z3" t="n">
-        <v>615000</v>
+        <v>875000</v>
       </c>
       <c r="AA3" t="n">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.77636363636363</v>
+        <v>26.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>182.4054545454545</v>
+        <v>184.3036363636364</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>1.096363636363636</v>
       </c>
       <c r="AE3" t="n">
-        <v>66.05272727272727</v>
+        <v>66.80636363636364</v>
       </c>
       <c r="AF3" t="n">
-        <v>1592554.545454545</v>
+        <v>1350831.818181818</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.99636363636363</v>
+        <v>70.13545454545456</v>
       </c>
       <c r="AH3" t="n">
-        <v>26.78454545454546</v>
+        <v>26.72479338842976</v>
       </c>
       <c r="AI3" t="n">
-        <v>179.75</v>
+        <v>180.4487603305785</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.224545454545455</v>
+        <v>1.150413223140496</v>
       </c>
       <c r="AK3" t="n">
-        <v>70.11636363636364</v>
+        <v>67.67107438016528</v>
       </c>
       <c r="AL3" t="n">
-        <v>2989850</v>
+        <v>1823454.545454545</v>
       </c>
       <c r="AM3" t="n">
-        <v>73.04636363636364</v>
+        <v>70.72396694214876</v>
       </c>
       <c r="AN3" t="n">
-        <v>26.32858868184955</v>
+        <v>23.25672932330827</v>
       </c>
       <c r="AO3" t="n">
-        <v>181.4109627329193</v>
+        <v>182.3671052631579</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.101456176673568</v>
+        <v>1.016374269005848</v>
       </c>
       <c r="AQ3" t="n">
-        <v>65.42633885438234</v>
+        <v>61.95435254803677</v>
       </c>
       <c r="AR3" t="n">
-        <v>1621075.241545894</v>
+        <v>898935.7351712615</v>
       </c>
       <c r="AS3" t="n">
-        <v>70.02966528640441</v>
+        <v>70.95589807852966</v>
       </c>
       <c r="AT3" t="n">
-        <v>25.44587681324523</v>
+        <v>25.76192218779072</v>
       </c>
       <c r="AU3" t="n">
-        <v>180.1224299384826</v>
+        <v>180.0522974026875</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.160869218500797</v>
+        <v>1.093980174414957</v>
       </c>
       <c r="AW3" t="n">
-        <v>64.65439355965673</v>
+        <v>64.39502667316272</v>
       </c>
       <c r="AX3" t="n">
-        <v>2615781.983367509</v>
+        <v>1282244.073360128</v>
       </c>
       <c r="AY3" t="n">
-        <v>69.23388623072833</v>
+        <v>68.51270476166461</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>nJ01AhX</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>tOpyQa2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1076,34 +1098,38 @@
       <c r="K4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>26.25</v>
+        <v>26.5</v>
       </c>
       <c r="O4" t="n">
-        <v>185.75</v>
+        <v>183</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>256</v>
+        <v>138</v>
       </c>
       <c r="S4" t="n">
-        <v>3000000</v>
+        <v>3625000</v>
       </c>
       <c r="T4" t="n">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>25.25</v>
+        <v>25.5</v>
       </c>
       <c r="V4" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -1112,129 +1138,129 @@
         <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Z4" t="n">
-        <v>8600000</v>
+        <v>11275000</v>
       </c>
       <c r="AA4" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.85909090909091</v>
+        <v>25.06565656565657</v>
       </c>
       <c r="AC4" t="n">
-        <v>184.2027272727273</v>
+        <v>179.5545454545455</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.097272727272727</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>66.78636363636363</v>
+        <v>69.1010101010101</v>
       </c>
       <c r="AF4" t="n">
-        <v>1346059.090909091</v>
+        <v>3848742.424242424</v>
       </c>
       <c r="AG4" t="n">
-        <v>70.10636363636364</v>
+        <v>73.47373737373738</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.96382575757576</v>
+        <v>26.44318181818182</v>
       </c>
       <c r="AI4" t="n">
-        <v>179.3113636363637</v>
+        <v>181.1022727272727</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.153030303030303</v>
+        <v>1.095454545454546</v>
       </c>
       <c r="AK4" t="n">
-        <v>67.44109848484848</v>
+        <v>68.89772727272727</v>
       </c>
       <c r="AL4" t="n">
-        <v>3632716.856060606</v>
+        <v>3120511.363636363</v>
       </c>
       <c r="AM4" t="n">
-        <v>72.10227272727273</v>
+        <v>71.84545454545454</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.00339598997494</v>
+        <v>24.50090934924695</v>
       </c>
       <c r="AO4" t="n">
-        <v>183.0671052631579</v>
+        <v>181.3305981813015</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.016374269005848</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>61.38768588137009</v>
+        <v>61.57634744719144</v>
       </c>
       <c r="AR4" t="n">
-        <v>831602.4018379281</v>
+        <v>1320390.463673392</v>
       </c>
       <c r="AS4" t="n">
-        <v>70.98923141186299</v>
+        <v>67.01808989296201</v>
       </c>
       <c r="AT4" t="n">
-        <v>25.58493699228699</v>
+        <v>25.44471344627595</v>
       </c>
       <c r="AU4" t="n">
-        <v>179.544224383484</v>
+        <v>181.3140337705595</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.040636446886447</v>
+        <v>1.088901009121597</v>
       </c>
       <c r="AW4" t="n">
-        <v>65.94246160577221</v>
+        <v>66.02711890846082</v>
       </c>
       <c r="AX4" t="n">
-        <v>2327170.889970434</v>
+        <v>1350582.405237736</v>
       </c>
       <c r="AY4" t="n">
-        <v>70.67404307566383</v>
+        <v>71.75576204840911</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>roEEsq7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>86yPt28</t>
+          <t>Sd7snoa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1249,173 +1275,169 @@
       <c r="K5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.375</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>180.875</v>
+        <v>180</v>
       </c>
       <c r="P5" t="n">
-        <v>1.875</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>587</v>
+        <v>170</v>
       </c>
       <c r="S5" t="n">
-        <v>78425000</v>
+        <v>1600000</v>
       </c>
       <c r="T5" t="n">
-        <v>636</v>
+        <v>210</v>
       </c>
       <c r="U5" t="n">
-        <v>37</v>
+        <v>29.2</v>
       </c>
       <c r="V5" t="n">
-        <v>186</v>
+        <v>181.2</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>63</v>
+        <v>342</v>
       </c>
       <c r="Z5" t="n">
-        <v>50000</v>
+        <v>5775000</v>
       </c>
       <c r="AA5" t="n">
-        <v>63</v>
+        <v>347</v>
       </c>
       <c r="AB5" t="n">
-        <v>27.46181818181818</v>
+        <v>23.21818181818182</v>
       </c>
       <c r="AC5" t="n">
-        <v>182.1336363636364</v>
+        <v>180.0727272727273</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.790909090909091</v>
+        <v>1.109090909090909</v>
       </c>
       <c r="AE5" t="n">
-        <v>74.28</v>
+        <v>68.14545454545454</v>
       </c>
       <c r="AF5" t="n">
-        <v>7119590.909090909</v>
+        <v>2859272.727272728</v>
       </c>
       <c r="AG5" t="n">
-        <v>77.85090909090908</v>
+        <v>74.41818181818182</v>
       </c>
       <c r="AH5" t="n">
-        <v>25.62193362193362</v>
+        <v>26.17363636363637</v>
       </c>
       <c r="AI5" t="n">
-        <v>180.6487734487734</v>
+        <v>182.3781818181818</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>1.182727272727273</v>
       </c>
       <c r="AK5" t="n">
-        <v>67.82525252525252</v>
+        <v>64.54545454545455</v>
       </c>
       <c r="AL5" t="n">
-        <v>2787283.54978355</v>
+        <v>2007109.090909091</v>
       </c>
       <c r="AM5" t="n">
-        <v>71.96810966810968</v>
+        <v>67.92999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.92445392203704</v>
+        <v>23.24955918122798</v>
       </c>
       <c r="AO5" t="n">
-        <v>184.1204358131212</v>
+        <v>180.7991568150519</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.144962198926394</v>
+        <v>1.075638223668914</v>
       </c>
       <c r="AQ5" t="n">
-        <v>67.72610264841722</v>
+        <v>63.89402556203387</v>
       </c>
       <c r="AR5" t="n">
-        <v>2630761.403558079</v>
+        <v>1766865.619578631</v>
       </c>
       <c r="AS5" t="n">
-        <v>74.334431625493</v>
+        <v>71.94746311233523</v>
       </c>
       <c r="AT5" t="n">
-        <v>24.17868408232858</v>
+        <v>23.24705931495405</v>
       </c>
       <c r="AU5" t="n">
-        <v>181.1473161003532</v>
+        <v>178.4779448621554</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>1.145075187969925</v>
       </c>
       <c r="AW5" t="n">
-        <v>64.79033308975764</v>
+        <v>63.00403508771929</v>
       </c>
       <c r="AX5" t="n">
-        <v>1776521.967482645</v>
+        <v>1576511.758563075</v>
       </c>
       <c r="AY5" t="n">
-        <v>70.86835342832785</v>
+        <v>69.16009189640769</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>6BusaLE</t>
+          <t>K4FYmLD</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>EgT3xN3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30991</v>
+        <v>25500</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1430,169 +1452,169 @@
       <c r="K6" t="n">
         <v>2024</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
       <c r="N6" t="n">
-        <v>29.2</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>181.2</v>
+        <v>186.5</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="S6" t="n">
-        <v>5775000</v>
+        <v>615000</v>
       </c>
       <c r="T6" t="n">
-        <v>347</v>
+        <v>143</v>
       </c>
       <c r="U6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V6" t="n">
-        <v>179.3333333333333</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>392</v>
+        <v>201</v>
       </c>
       <c r="Z6" t="n">
-        <v>6050000</v>
+        <v>3275000</v>
       </c>
       <c r="AA6" t="n">
-        <v>411</v>
+        <v>204</v>
       </c>
       <c r="AB6" t="n">
-        <v>26.16272727272727</v>
+        <v>26.65343434343434</v>
       </c>
       <c r="AC6" t="n">
-        <v>182.2854545454546</v>
+        <v>179.7911111111111</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.151818181818182</v>
+        <v>1.227878787878788</v>
       </c>
       <c r="AE6" t="n">
-        <v>64.50636363636363</v>
+        <v>69.87191919191919</v>
       </c>
       <c r="AF6" t="n">
-        <v>1855722.727272727</v>
+        <v>2979933.333333333</v>
       </c>
       <c r="AG6" t="n">
-        <v>67.8909090909091</v>
+        <v>72.82747474747475</v>
       </c>
       <c r="AH6" t="n">
-        <v>27.72727272727273</v>
+        <v>25.47272727272727</v>
       </c>
       <c r="AI6" t="n">
-        <v>183.6818181818182</v>
+        <v>182.0666666666667</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.154545454545455</v>
+        <v>1.065656565656566</v>
       </c>
       <c r="AK6" t="n">
-        <v>69.23636363636362</v>
+        <v>67.889898989899</v>
       </c>
       <c r="AL6" t="n">
-        <v>3228409.090909091</v>
+        <v>2447146.464646464</v>
       </c>
       <c r="AM6" t="n">
-        <v>71.06363636363638</v>
+        <v>71.74040404040404</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.19238095238095</v>
+        <v>25.28426065162908</v>
       </c>
       <c r="AO6" t="n">
-        <v>178.7954887218045</v>
+        <v>180.2330359990886</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.129285714285714</v>
+        <v>1.148748006379585</v>
       </c>
       <c r="AQ6" t="n">
-        <v>62.94058479532164</v>
+        <v>64.28217133743451</v>
       </c>
       <c r="AR6" t="n">
-        <v>1495403.571428571</v>
+        <v>2554160.771246297</v>
       </c>
       <c r="AS6" t="n">
-        <v>69.0945948203843</v>
+        <v>69.17277511961723</v>
       </c>
       <c r="AT6" t="n">
-        <v>27.72013855709508</v>
+        <v>26.56630800761236</v>
       </c>
       <c r="AU6" t="n">
-        <v>182.9667283803154</v>
+        <v>180.9842464500073</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.046920289855072</v>
+        <v>1.166057312252964</v>
       </c>
       <c r="AW6" t="n">
-        <v>65.65758679726072</v>
+        <v>65.92384167764602</v>
       </c>
       <c r="AX6" t="n">
-        <v>1139612.617455009</v>
+        <v>1388838.566827697</v>
       </c>
       <c r="AY6" t="n">
-        <v>66.79709348622393</v>
+        <v>69.19558263797394</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>xA45kov</t>
+          <t>022mBmS</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>Uw6sTk0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26000</v>
+        <v>18500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1609,171 +1631,167 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>vZraQYnO</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>26.5</v>
+        <v>28.8</v>
       </c>
       <c r="O7" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="S7" t="n">
-        <v>3625000</v>
+        <v>15575000</v>
       </c>
       <c r="T7" t="n">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="U7" t="n">
-        <v>28.8</v>
+        <v>34</v>
       </c>
       <c r="V7" t="n">
         <v>179</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>353</v>
+        <v>68</v>
       </c>
       <c r="Z7" t="n">
-        <v>15575000</v>
+        <v>550000</v>
       </c>
       <c r="AA7" t="n">
-        <v>360</v>
+        <v>68</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.34444444444445</v>
+        <v>25.51652892561983</v>
       </c>
       <c r="AC7" t="n">
-        <v>179.3222222222222</v>
+        <v>183.4438016528926</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>1.066942148760331</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.3111111111111</v>
+        <v>69.16198347107438</v>
       </c>
       <c r="AF7" t="n">
-        <v>3874777.777777778</v>
+        <v>2900619.834710744</v>
       </c>
       <c r="AG7" t="n">
-        <v>73.35555555555555</v>
+        <v>73.20165289256198</v>
       </c>
       <c r="AH7" t="n">
-        <v>25.59545454545454</v>
+        <v>25.81322314049587</v>
       </c>
       <c r="AI7" t="n">
-        <v>183.4063636363636</v>
+        <v>182.4099173553719</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.073636363636364</v>
+        <v>1.008264462809917</v>
       </c>
       <c r="AK7" t="n">
-        <v>69.24181818181818</v>
+        <v>66.1305785123967</v>
       </c>
       <c r="AL7" t="n">
-        <v>2936227.272727272</v>
+        <v>1617611.570247934</v>
       </c>
       <c r="AM7" t="n">
-        <v>73.27636363636364</v>
+        <v>71.06280991735537</v>
       </c>
       <c r="AN7" t="n">
-        <v>24.45924268258028</v>
+        <v>24.67758945599855</v>
       </c>
       <c r="AO7" t="n">
-        <v>181.2287463294497</v>
+        <v>181.4551505312869</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>1.077201964701965</v>
       </c>
       <c r="AQ7" t="n">
-        <v>61.72912522496922</v>
+        <v>65.49582235945873</v>
       </c>
       <c r="AR7" t="n">
-        <v>1403723.797006725</v>
+        <v>1612552.228074955</v>
       </c>
       <c r="AS7" t="n">
-        <v>67.0782750781472</v>
+        <v>70.9492314503678</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.93868173493174</v>
+        <v>26.15433195676162</v>
       </c>
       <c r="AU7" t="n">
-        <v>181.4606655844156</v>
+        <v>181.4591639817983</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.084922161172161</v>
+        <v>1.092232887885062</v>
       </c>
       <c r="AW7" t="n">
-        <v>65.96540459540459</v>
+        <v>65.2645861243048</v>
       </c>
       <c r="AX7" t="n">
-        <v>1684907.450882451</v>
+        <v>1617341.128678085</v>
       </c>
       <c r="AY7" t="n">
-        <v>71.07748792873792</v>
+        <v>69.9521021320254</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>roEEsq7</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
+          <t>K4zRMgT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20700</v>
+        <v>19400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1790,113 +1808,131 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>24</v>
+      </c>
+      <c r="O8" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>133</v>
+      </c>
+      <c r="S8" t="n">
+        <v>18700000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>140</v>
+      </c>
       <c r="U8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V8" t="n">
-        <v>183.5</v>
+        <v>172</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2200000</v>
+        <v>750000</v>
       </c>
       <c r="AA8" t="n">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.90090909090909</v>
+        <v>26.03388429752066</v>
       </c>
       <c r="AC8" t="n">
-        <v>179.7827272727273</v>
+        <v>181.697520661157</v>
       </c>
       <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65.45454545454545</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1185487.603305785</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>69.69256198347108</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>27.86454545454545</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>179.7009090909091</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.105454545454545</v>
       </c>
-      <c r="AE8" t="n">
-        <v>67.44363636363637</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2237772.727272728</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>68.71909090909091</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>27.66758494031221</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>180.6966023875115</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.326629935720845</v>
-      </c>
       <c r="AK8" t="n">
-        <v>72.14040404040405</v>
+        <v>67.43454545454544</v>
       </c>
       <c r="AL8" t="n">
-        <v>4181244.260789715</v>
+        <v>2236636.363636364</v>
       </c>
       <c r="AM8" t="n">
-        <v>74.93645546372818</v>
+        <v>68.67363636363636</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.06321873524391</v>
+        <v>24.73552698591399</v>
       </c>
       <c r="AO8" t="n">
-        <v>180.8864665286404</v>
+        <v>180.3941399743891</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.285171079873597</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>65.19013457556936</v>
+        <v>64.23326460495754</v>
       </c>
       <c r="AR8" t="n">
-        <v>1072562.874577749</v>
+        <v>1237106.022886174</v>
       </c>
       <c r="AS8" t="n">
-        <v>67.14049217246013</v>
+        <v>70.03193955558154</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.83136790487407</v>
+        <v>28.18272337920676</v>
       </c>
       <c r="AU8" t="n">
-        <v>179.5382510840834</v>
+        <v>181.3099959404051</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.011544011544012</v>
+        <v>1.294768603093411</v>
       </c>
       <c r="AW8" t="n">
-        <v>67.0921442797431</v>
+        <v>65.16072281086348</v>
       </c>
       <c r="AX8" t="n">
-        <v>1824500.677631999</v>
+        <v>1122171.233710876</v>
       </c>
       <c r="AY8" t="n">
-        <v>72.38689622043202</v>
+        <v>67.08197824057159</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>lAVQ9RG</t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -1908,35 +1944,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20500</v>
+        <v>30000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1951,173 +1987,165 @@
       <c r="K9" t="n">
         <v>2024</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>21.33333333333333</v>
+        <v>26</v>
       </c>
       <c r="O9" t="n">
-        <v>174</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="S9" t="n">
-        <v>15450000</v>
+        <v>6050000</v>
       </c>
       <c r="T9" t="n">
-        <v>229</v>
+        <v>411</v>
       </c>
       <c r="U9" t="n">
-        <v>22.33333333333333</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="W9" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>195</v>
+        <v>58</v>
       </c>
       <c r="Z9" t="n">
-        <v>19600000</v>
+        <v>375000</v>
       </c>
       <c r="AA9" t="n">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>25.84015151515152</v>
+        <v>27.78181818181818</v>
       </c>
       <c r="AC9" t="n">
-        <v>182.5924242424242</v>
+        <v>183.8272727272727</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.071969696969697</v>
+        <v>1.163636363636364</v>
       </c>
       <c r="AE9" t="n">
-        <v>67.51287878787879</v>
+        <v>69.3090909090909</v>
       </c>
       <c r="AF9" t="n">
-        <v>2631750</v>
+        <v>3256363.636363636</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.30454545454546</v>
+        <v>71.11818181818182</v>
       </c>
       <c r="AH9" t="n">
-        <v>26.02818181818181</v>
+        <v>22.65277777777778</v>
       </c>
       <c r="AI9" t="n">
-        <v>181.6763636363636</v>
+        <v>181.3222222222222</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>65.36363636363636</v>
+        <v>66.14938271604939</v>
       </c>
       <c r="AL9" t="n">
-        <v>1179536.363636364</v>
+        <v>1785949.074074074</v>
       </c>
       <c r="AM9" t="n">
-        <v>69.55272727272728</v>
+        <v>72.53117283950617</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.73982791299725</v>
+        <v>27.64622551361682</v>
       </c>
       <c r="AO9" t="n">
-        <v>179.8979404208809</v>
+        <v>182.9841196846632</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.035785568994951</v>
+        <v>1.051268115942029</v>
       </c>
       <c r="AQ9" t="n">
-        <v>63.35205415135334</v>
+        <v>65.43584766682594</v>
       </c>
       <c r="AR9" t="n">
-        <v>1495196.242624017</v>
+        <v>1150764.791368052</v>
       </c>
       <c r="AS9" t="n">
-        <v>69.40809084841551</v>
+        <v>66.68405000796307</v>
       </c>
       <c r="AT9" t="n">
-        <v>24.6796679197995</v>
+        <v>21.6007566277634</v>
       </c>
       <c r="AU9" t="n">
-        <v>180.5982598541809</v>
+        <v>180.8526674214362</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>64.16247341839446</v>
+        <v>62.72404523390075</v>
       </c>
       <c r="AX9" t="n">
-        <v>1254934.272233614</v>
+        <v>1413142.453233673</v>
       </c>
       <c r="AY9" t="n">
-        <v>70.02925115819853</v>
+        <v>71.61935548029011</v>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>xA45kov</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>dp6AQn9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
+          <t xml:space="preserve">dujic f 
   can </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>22423</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2134,171 +2162,153 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" t="n">
-        <v>175</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>875000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>72</v>
-      </c>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>28</v>
+        <v>25.25</v>
       </c>
       <c r="V10" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="n">
-        <v>725000</v>
+        <v>8600000</v>
       </c>
       <c r="AA10" t="n">
-        <v>66</v>
+        <v>292</v>
       </c>
       <c r="AB10" t="n">
-        <v>26.61735537190083</v>
+        <v>25.55656565656566</v>
       </c>
       <c r="AC10" t="n">
-        <v>180.3826446280991</v>
+        <v>182.3242424242424</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.133884297520661</v>
+        <v>1.18989898989899</v>
       </c>
       <c r="AE10" t="n">
-        <v>67.50578512396693</v>
+        <v>68.08181818181818</v>
       </c>
       <c r="AF10" t="n">
-        <v>1759818.181818182</v>
+        <v>2174974.747474747</v>
       </c>
       <c r="AG10" t="n">
-        <v>70.64132231404959</v>
+        <v>71.47575757575758</v>
       </c>
       <c r="AH10" t="n">
-        <v>26.66476301476302</v>
+        <v>26.03958333333334</v>
       </c>
       <c r="AI10" t="n">
-        <v>180.2187257187258</v>
+        <v>179.4174242424242</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.216705516705517</v>
+        <v>1.153030303030303</v>
       </c>
       <c r="AK10" t="n">
-        <v>68.66080031080031</v>
+        <v>67.30473484848484</v>
       </c>
       <c r="AL10" t="n">
-        <v>2007041.56954157</v>
+        <v>3587451.704545455</v>
       </c>
       <c r="AM10" t="n">
-        <v>72.51177156177155</v>
+        <v>71.98863636363636</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.85980640076444</v>
+        <v>24.02377864223839</v>
       </c>
       <c r="AO10" t="n">
-        <v>180.0899630618365</v>
+        <v>182.3296877443162</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.126065735912283</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>64.60916292054705</v>
+        <v>64.86937274112196</v>
       </c>
       <c r="AR10" t="n">
-        <v>1412430.076615185</v>
+        <v>1447339.602906553</v>
       </c>
       <c r="AS10" t="n">
-        <v>68.59733624271553</v>
+        <v>69.97149725919076</v>
       </c>
       <c r="AT10" t="n">
-        <v>23.79921708838118</v>
+        <v>25.68952636426767</v>
       </c>
       <c r="AU10" t="n">
-        <v>179.0368941172347</v>
+        <v>179.6997799390395</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.081406244254541</v>
+        <v>1.040636446886447</v>
       </c>
       <c r="AW10" t="n">
-        <v>63.07696383423938</v>
+        <v>65.73400749949199</v>
       </c>
       <c r="AX10" t="n">
-        <v>1355801.399151244</v>
+        <v>2197038.039728888</v>
       </c>
       <c r="AY10" t="n">
-        <v>69.58794415079244</v>
+        <v>70.46776288242712</v>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
           <t>l6eEjGl</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  mo </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18500</v>
+        <v>18061</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2315,19 +2325,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
-        <v>181.5</v>
+        <v>179</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -2336,150 +2346,150 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="S11" t="n">
-        <v>2000000</v>
+        <v>2240000</v>
       </c>
       <c r="T11" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
-        <v>180.6666666666667</v>
+        <v>182.5</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="Z11" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="AA11" t="n">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="AB11" t="n">
-        <v>27.34545454545454</v>
+        <v>24.05333333333333</v>
       </c>
       <c r="AC11" t="n">
-        <v>180.069696969697</v>
+        <v>180.1566666666667</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.062878787878788</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>66.42121212121212</v>
+        <v>65.63222222222223</v>
       </c>
       <c r="AF11" t="n">
-        <v>1230780.303030303</v>
+        <v>1684472.222222222</v>
       </c>
       <c r="AG11" t="n">
-        <v>69.1189393939394</v>
+        <v>70.86</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.15794306703398</v>
+        <v>23.75454545454546</v>
       </c>
       <c r="AI11" t="n">
-        <v>179.1077134986226</v>
+        <v>179.3909090909091</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>1.018181818181818</v>
       </c>
       <c r="AK11" t="n">
-        <v>65.34545454545456</v>
+        <v>65.63636363636364</v>
       </c>
       <c r="AL11" t="n">
-        <v>1582396.235078053</v>
+        <v>1257500</v>
       </c>
       <c r="AM11" t="n">
-        <v>72.20615243342517</v>
+        <v>71.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.40655509546814</v>
+        <v>22.34684457841108</v>
       </c>
       <c r="AO11" t="n">
-        <v>179.8499830342765</v>
+        <v>178.76395110218</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.068224062571889</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>63.68009633080285</v>
+        <v>60.92601114358788</v>
       </c>
       <c r="AR11" t="n">
-        <v>1042966.57752473</v>
+        <v>815187.443165672</v>
       </c>
       <c r="AS11" t="n">
-        <v>67.90656027145157</v>
+        <v>69.27438903097472</v>
       </c>
       <c r="AT11" t="n">
-        <v>24.48492462902774</v>
+        <v>23.15305194805195</v>
       </c>
       <c r="AU11" t="n">
-        <v>178.4899162041426</v>
+        <v>180.671376167692</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>1.09350991114149</v>
       </c>
       <c r="AW11" t="n">
-        <v>63.46415832127004</v>
+        <v>64.77004556846661</v>
       </c>
       <c r="AX11" t="n">
-        <v>1280216.722640621</v>
+        <v>1300155.659033948</v>
       </c>
       <c r="AY11" t="n">
-        <v>70.45146971205446</v>
+        <v>71.54494588744589</v>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2PIEeC7</t>
+          <t>z9ZXDy6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>rXawJi8</t>
+          <t>rJ9D8rz</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzales g 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22423</v>
+        <v>20213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2496,157 +2506,167 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>27</v>
+      </c>
+      <c r="O12" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>265</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="T12" t="n">
+        <v>281</v>
+      </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2240000</v>
+        <v>2900000</v>
       </c>
       <c r="AA12" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AB12" t="n">
-        <v>25.50909090909091</v>
+        <v>24.08356290174472</v>
       </c>
       <c r="AC12" t="n">
-        <v>182.2161616161616</v>
+        <v>179.106795224977</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.187878787878788</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>68.05656565656565</v>
+        <v>65.2931129476584</v>
       </c>
       <c r="AF12" t="n">
-        <v>2127121.212121212</v>
+        <v>1578668.044077135</v>
       </c>
       <c r="AG12" t="n">
-        <v>71.4989898989899</v>
+        <v>72.2584940312213</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.04444444444444</v>
+        <v>26.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>180.3522222222222</v>
+        <v>179.0474747474748</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>1.048484848484848</v>
       </c>
       <c r="AK12" t="n">
-        <v>65.7511111111111</v>
+        <v>70.35757575757576</v>
       </c>
       <c r="AL12" t="n">
-        <v>1707611.111111111</v>
+        <v>3608257.575757576</v>
       </c>
       <c r="AM12" t="n">
-        <v>70.97</v>
+        <v>74.42222222222223</v>
       </c>
       <c r="AN12" t="n">
-        <v>24.09024689620665</v>
+        <v>24.75393289349056</v>
       </c>
       <c r="AO12" t="n">
-        <v>182.3019099665385</v>
+        <v>178.4845443033161</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>65.10945210620133</v>
+        <v>63.68275336259235</v>
       </c>
       <c r="AR12" t="n">
-        <v>1396322.737827188</v>
+        <v>1330429.532557976</v>
       </c>
       <c r="AS12" t="n">
-        <v>70.07864011633362</v>
+        <v>70.26097384428586</v>
       </c>
       <c r="AT12" t="n">
-        <v>22.29428047584697</v>
+        <v>23.83792837952045</v>
       </c>
       <c r="AU12" t="n">
-        <v>178.877092127821</v>
+        <v>177.4979927610043</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>1.031676234393626</v>
       </c>
       <c r="AW12" t="n">
-        <v>60.92184447692121</v>
+        <v>64.35914059299608</v>
       </c>
       <c r="AX12" t="n">
-        <v>831408.5970118258</v>
+        <v>1499889.224958758</v>
       </c>
       <c r="AY12" t="n">
-        <v>69.37374800533368</v>
+        <v>70.41775348479312</v>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>jBBpU7Y</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>dp6AQn9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27000</v>
+        <v>22000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2664,31 +2684,31 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O13" t="n">
-        <v>175</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="S13" t="n">
-        <v>2900000</v>
+        <v>5000000</v>
       </c>
       <c r="T13" t="n">
-        <v>73</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -2697,129 +2717,129 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="n">
-        <v>1350000</v>
+        <v>2400000</v>
       </c>
       <c r="AA13" t="n">
         <v>145</v>
       </c>
       <c r="AB13" t="n">
-        <v>26.41</v>
+        <v>27.27915518824609</v>
       </c>
       <c r="AC13" t="n">
-        <v>179.0222222222222</v>
+        <v>180.349494949495</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.053333333333333</v>
+        <v>1.326629935720845</v>
       </c>
       <c r="AE13" t="n">
-        <v>70.39333333333335</v>
+        <v>71.94205693296603</v>
       </c>
       <c r="AF13" t="n">
-        <v>3685333.333333333</v>
+        <v>4212235.996326906</v>
       </c>
       <c r="AG13" t="n">
-        <v>74.34444444444445</v>
+        <v>74.96951331496786</v>
       </c>
       <c r="AH13" t="n">
-        <v>22.71296296296297</v>
+        <v>26.82348484848485</v>
       </c>
       <c r="AI13" t="n">
-        <v>181.4719135802469</v>
+        <v>180.8590909090909</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>66.37314814814815</v>
+        <v>69.3280303030303</v>
       </c>
       <c r="AL13" t="n">
-        <v>1814714.506172839</v>
+        <v>2465295.454545455</v>
       </c>
       <c r="AM13" t="n">
-        <v>72.7179012345679</v>
+        <v>72.63333333333333</v>
       </c>
       <c r="AN13" t="n">
-        <v>23.83124502699631</v>
+        <v>26.14668894746784</v>
       </c>
       <c r="AO13" t="n">
-        <v>177.333506322819</v>
+        <v>179.6685753053168</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.030081953071084</v>
+        <v>1.011544011544012</v>
       </c>
       <c r="AQ13" t="n">
-        <v>64.41886417610525</v>
+        <v>67.41159755374183</v>
       </c>
       <c r="AR13" t="n">
-        <v>1500116.242692729</v>
+        <v>1863518.478013436</v>
       </c>
       <c r="AS13" t="n">
-        <v>70.51667169041529</v>
+        <v>72.42885426239008</v>
       </c>
       <c r="AT13" t="n">
-        <v>21.41088734671765</v>
+        <v>25.51957851102672</v>
       </c>
       <c r="AU13" t="n">
-        <v>180.6598569639199</v>
+        <v>180.6557623334797</v>
       </c>
       <c r="AV13" t="n">
         <v>1</v>
       </c>
       <c r="AW13" t="n">
-        <v>62.47829359991382</v>
+        <v>65.71289972400906</v>
       </c>
       <c r="AX13" t="n">
-        <v>1392189.838854588</v>
+        <v>1476202.664970248</v>
       </c>
       <c r="AY13" t="n">
-        <v>71.69059731035547</v>
+        <v>70.15898897327925</v>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2PIEeC7</t>
+          <t>KtuTuMN</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>EqKWmJf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18000</v>
+        <v>25218</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2834,38 +2854,42 @@
       <c r="K14" t="n">
         <v>2024</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O14" t="n">
-        <v>181.5</v>
+        <v>178</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="S14" t="n">
-        <v>2500000</v>
+        <v>775000</v>
       </c>
       <c r="T14" t="n">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V14" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
@@ -2874,85 +2898,85 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Z14" t="n">
-        <v>775000</v>
+        <v>1300000</v>
       </c>
       <c r="AA14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AB14" t="n">
-        <v>26.91487603305785</v>
+        <v>26.91363636363637</v>
       </c>
       <c r="AC14" t="n">
-        <v>180.9454545454545</v>
+        <v>178.6272727272727</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>69.38264462809917</v>
+        <v>69.73090909090908</v>
       </c>
       <c r="AF14" t="n">
-        <v>2445404.958677686</v>
+        <v>2783481.818181818</v>
       </c>
       <c r="AG14" t="n">
-        <v>72.60000000000001</v>
+        <v>72.15727272727273</v>
       </c>
       <c r="AH14" t="n">
-        <v>26.94090909090909</v>
+        <v>25.79595959595959</v>
       </c>
       <c r="AI14" t="n">
-        <v>178.5090909090909</v>
+        <v>177.1878787878788</v>
       </c>
       <c r="AJ14" t="n">
         <v>1</v>
       </c>
       <c r="AK14" t="n">
-        <v>69.78545454545454</v>
+        <v>69.06969696969696</v>
       </c>
       <c r="AL14" t="n">
-        <v>2787800</v>
+        <v>2686565.656565657</v>
       </c>
       <c r="AM14" t="n">
-        <v>72.15727272727273</v>
+        <v>71.77373737373738</v>
       </c>
       <c r="AN14" t="n">
-        <v>25.35847958778673</v>
+        <v>26.83216955529178</v>
       </c>
       <c r="AO14" t="n">
-        <v>180.6585589092506</v>
+        <v>179.6193309408917</v>
       </c>
       <c r="AP14" t="n">
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>65.68679969891897</v>
+        <v>67.16141846153204</v>
       </c>
       <c r="AR14" t="n">
-        <v>1516387.755725119</v>
+        <v>1629740.708219873</v>
       </c>
       <c r="AS14" t="n">
-        <v>70.32874554660766</v>
+        <v>69.17343898380378</v>
       </c>
       <c r="AT14" t="n">
-        <v>26.85608259877004</v>
+        <v>24.81521739130435</v>
       </c>
       <c r="AU14" t="n">
-        <v>179.7434613756743</v>
+        <v>177.6397247143624</v>
       </c>
       <c r="AV14" t="n">
         <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>67.11750541805377</v>
+        <v>64.96886550111188</v>
       </c>
       <c r="AX14" t="n">
-        <v>1614080.925611178</v>
+        <v>1079253.651943869</v>
       </c>
       <c r="AY14" t="n">
-        <v>69.13865637510813</v>
+        <v>69.40172149375047</v>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
@@ -2961,7 +2985,174 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>EqKWmJf</t>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>167</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>174</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>206</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>229</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>26.45707070707071</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>180.3956487956488</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.209013209013209</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>68.3454156954157</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1943349.261849262</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>72.45023310023309</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25.70378787878788</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>182.4560606060606</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.071969696969697</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>67.6189393939394</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2701181.818181818</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>71.47121212121213</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23.95306324222733</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>178.8676633480039</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.089098551946849</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>63.36927152654707</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1421666.783766629</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>69.73409799694629</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>24.83403081154797</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>180.003012884649</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.032162380589154</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>63.45350342671566</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1530920.880305177</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>69.36098939914014</v>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1636,10 +1636,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="O7" t="n">
-        <v>179</v>
+        <v>181.4</v>
       </c>
       <c r="P7" t="n">
         <v>1.4</v>
@@ -1648,13 +1648,13 @@
         <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="S7" t="n">
-        <v>15575000</v>
+        <v>12875000</v>
       </c>
       <c r="T7" t="n">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="U7" t="n">
         <v>34</v>
@@ -1696,22 +1696,22 @@
         <v>73.20165289256198</v>
       </c>
       <c r="AH7" t="n">
-        <v>25.81322314049587</v>
+        <v>25.75818181818182</v>
       </c>
       <c r="AI7" t="n">
-        <v>182.4099173553719</v>
+        <v>182.66</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.008264462809917</v>
+        <v>1.009090909090909</v>
       </c>
       <c r="AK7" t="n">
-        <v>66.1305785123967</v>
+        <v>65.87090909090909</v>
       </c>
       <c r="AL7" t="n">
-        <v>1617611.570247934</v>
+        <v>1534145.454545454</v>
       </c>
       <c r="AM7" t="n">
-        <v>71.06280991735537</v>
+        <v>70.92363636363636</v>
       </c>
       <c r="AN7" t="n">
         <v>24.67758945599855</v>
@@ -1732,22 +1732,22 @@
         <v>70.9492314503678</v>
       </c>
       <c r="AT7" t="n">
-        <v>26.15433195676162</v>
+        <v>26.32476515243778</v>
       </c>
       <c r="AU7" t="n">
-        <v>181.4591639817983</v>
+        <v>181.1750803799781</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.092232887885062</v>
+        <v>1.101456176673568</v>
       </c>
       <c r="AW7" t="n">
-        <v>65.2645861243048</v>
+        <v>65.48604473673528</v>
       </c>
       <c r="AX7" t="n">
-        <v>1617341.128678085</v>
+        <v>1668900.241545894</v>
       </c>
       <c r="AY7" t="n">
-        <v>69.9521021320254</v>
+        <v>70.06231234522795</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1859,22 +1859,22 @@
         <v>66</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.03388429752066</v>
+        <v>26.00090909090909</v>
       </c>
       <c r="AC8" t="n">
-        <v>181.697520661157</v>
+        <v>181.7309090909091</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>65.45454545454545</v>
+        <v>65.48181818181817</v>
       </c>
       <c r="AF8" t="n">
-        <v>1185487.603305785</v>
+        <v>1196763.636363636</v>
       </c>
       <c r="AG8" t="n">
-        <v>69.69256198347108</v>
+        <v>69.79818181818182</v>
       </c>
       <c r="AH8" t="n">
         <v>27.86454545454545</v>
@@ -1895,22 +1895,22 @@
         <v>68.67363636363636</v>
       </c>
       <c r="AN8" t="n">
-        <v>24.73552698591399</v>
+        <v>24.68050825593395</v>
       </c>
       <c r="AO8" t="n">
-        <v>180.3941399743891</v>
+        <v>180.4478396861137</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>64.23326460495754</v>
+        <v>64.05659106545329</v>
       </c>
       <c r="AR8" t="n">
-        <v>1237106.022886174</v>
+        <v>1207030.910889077</v>
       </c>
       <c r="AS8" t="n">
-        <v>70.03193955558154</v>
+        <v>69.89703827304447</v>
       </c>
       <c r="AT8" t="n">
         <v>28.18272337920676</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2174,25 +2174,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>25.25</v>
+        <v>24.6</v>
       </c>
       <c r="V10" t="n">
-        <v>177</v>
+        <v>175.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="Z10" t="n">
-        <v>8600000</v>
+        <v>56100000</v>
       </c>
       <c r="AA10" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AB10" t="n">
         <v>25.55656565656566</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2571,22 +2571,22 @@
         <v>72.2584940312213</v>
       </c>
       <c r="AH12" t="n">
-        <v>26.3</v>
+        <v>26.20777777777778</v>
       </c>
       <c r="AI12" t="n">
-        <v>179.0474747474748</v>
+        <v>179.1522222222222</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.048484848484848</v>
+        <v>1.042222222222222</v>
       </c>
       <c r="AK12" t="n">
-        <v>70.35757575757576</v>
+        <v>70.20444444444445</v>
       </c>
       <c r="AL12" t="n">
-        <v>3608257.575757576</v>
+        <v>3522972.222222222</v>
       </c>
       <c r="AM12" t="n">
-        <v>74.42222222222223</v>
+        <v>74.37555555555556</v>
       </c>
       <c r="AN12" t="n">
         <v>24.75393289349056</v>
@@ -2607,22 +2607,22 @@
         <v>70.26097384428586</v>
       </c>
       <c r="AT12" t="n">
-        <v>23.83792837952045</v>
+        <v>23.75088788413916</v>
       </c>
       <c r="AU12" t="n">
-        <v>177.4979927610043</v>
+        <v>177.481125370438</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.031676234393626</v>
+        <v>1.030677191166322</v>
       </c>
       <c r="AW12" t="n">
-        <v>64.35914059299608</v>
+        <v>64.4075546522957</v>
       </c>
       <c r="AX12" t="n">
-        <v>1499889.224958758</v>
+        <v>1515294.814121301</v>
       </c>
       <c r="AY12" t="n">
-        <v>70.41775348479312</v>
+        <v>70.58452883327243</v>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2705,10 +2705,10 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="V13" t="n">
-        <v>183</v>
+        <v>181.5</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -2717,13 +2717,13 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="Z13" t="n">
-        <v>2400000</v>
+        <v>1300000</v>
       </c>
       <c r="AA13" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="AB13" t="n">
         <v>27.27915518824609</v>
@@ -2744,22 +2744,22 @@
         <v>74.96951331496786</v>
       </c>
       <c r="AH13" t="n">
-        <v>26.82348484848485</v>
+        <v>26.75289256198348</v>
       </c>
       <c r="AI13" t="n">
-        <v>180.8590909090909</v>
+        <v>180.7826446280992</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.3280303030303</v>
+        <v>69.3396694214876</v>
       </c>
       <c r="AL13" t="n">
-        <v>2465295.454545455</v>
+        <v>2505595.041322314</v>
       </c>
       <c r="AM13" t="n">
-        <v>72.63333333333333</v>
+        <v>72.67272727272727</v>
       </c>
       <c r="AN13" t="n">
         <v>26.14668894746784</v>
@@ -2780,22 +2780,22 @@
         <v>72.42885426239008</v>
       </c>
       <c r="AT13" t="n">
-        <v>25.51957851102672</v>
+        <v>25.50357181440069</v>
       </c>
       <c r="AU13" t="n">
-        <v>180.6557623334797</v>
+        <v>180.5375114784206</v>
       </c>
       <c r="AV13" t="n">
         <v>1</v>
       </c>
       <c r="AW13" t="n">
-        <v>65.71289972400906</v>
+        <v>65.67889456057905</v>
       </c>
       <c r="AX13" t="n">
-        <v>1476202.664970248</v>
+        <v>1497754.685896397</v>
       </c>
       <c r="AY13" t="n">
-        <v>70.15898897327925</v>
+        <v>70.14182196294496</v>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -2705,25 +2705,25 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="V13" t="n">
-        <v>181.5</v>
+        <v>188</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="Z13" t="n">
-        <v>1300000</v>
+        <v>800000</v>
       </c>
       <c r="AA13" t="n">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="AB13" t="n">
         <v>27.27915518824609</v>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -1636,10 +1636,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>29.2</v>
+        <v>28.8</v>
       </c>
       <c r="O7" t="n">
-        <v>181.4</v>
+        <v>179</v>
       </c>
       <c r="P7" t="n">
         <v>1.4</v>
@@ -1648,13 +1648,13 @@
         <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="S7" t="n">
-        <v>12875000</v>
+        <v>15575000</v>
       </c>
       <c r="T7" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="U7" t="n">
         <v>34</v>
@@ -2174,25 +2174,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>24.6</v>
+        <v>25.25</v>
       </c>
       <c r="V10" t="n">
-        <v>175.8</v>
+        <v>177</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="n">
-        <v>56100000</v>
+        <v>8600000</v>
       </c>
       <c r="AA10" t="n">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="AB10" t="n">
         <v>25.55656565656566</v>
@@ -2705,25 +2705,25 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V13" t="n">
-        <v>188</v>
+        <v>185.5</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="Z13" t="n">
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="AA13" t="n">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="AB13" t="n">
         <v>27.27915518824609</v>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -1282,25 +1282,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19.33333333333333</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="S5" t="n">
-        <v>1600000</v>
+        <v>7600000</v>
       </c>
       <c r="T5" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="U5" t="n">
         <v>29.2</v>
@@ -1459,46 +1459,46 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>186.5</v>
+        <v>186.3333333333333</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="S6" t="n">
-        <v>615000</v>
+        <v>2815000</v>
       </c>
       <c r="T6" t="n">
-        <v>143</v>
+        <v>218</v>
       </c>
       <c r="U6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V6" t="n">
-        <v>183.6666666666667</v>
+        <v>180</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="Z6" t="n">
-        <v>3275000</v>
+        <v>6775000</v>
       </c>
       <c r="AA6" t="n">
-        <v>204</v>
+        <v>278</v>
       </c>
       <c r="AB6" t="n">
         <v>26.65343434343434</v>
@@ -1636,10 +1636,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="O7" t="n">
-        <v>179</v>
+        <v>181.4</v>
       </c>
       <c r="P7" t="n">
         <v>1.4</v>
@@ -1648,13 +1648,13 @@
         <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="S7" t="n">
-        <v>15575000</v>
+        <v>12875000</v>
       </c>
       <c r="T7" t="n">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="U7" t="n">
         <v>34</v>
@@ -2174,25 +2174,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>25.25</v>
+        <v>24.6</v>
       </c>
       <c r="V10" t="n">
-        <v>177</v>
+        <v>175.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="Z10" t="n">
-        <v>8600000</v>
+        <v>56100000</v>
       </c>
       <c r="AA10" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AB10" t="n">
         <v>25.55656565656566</v>
@@ -2705,10 +2705,10 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>185.5</v>
+        <v>183</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -2717,13 +2717,13 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="n">
-        <v>1200000</v>
+        <v>2400000</v>
       </c>
       <c r="AA13" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="AB13" t="n">
         <v>27.27915518824609</v>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA15"/>
+  <dimension ref="A1:BA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2174,25 +2174,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>24.6</v>
+        <v>25.25</v>
       </c>
       <c r="V10" t="n">
-        <v>175.8</v>
+        <v>177</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="n">
-        <v>56100000</v>
+        <v>8600000</v>
       </c>
       <c r="AA10" t="n">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="AB10" t="n">
         <v>25.55656565656566</v>
@@ -2705,10 +2705,10 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="V13" t="n">
-        <v>183</v>
+        <v>185.5</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -2717,13 +2717,13 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="Z13" t="n">
-        <v>2400000</v>
+        <v>1225000</v>
       </c>
       <c r="AA13" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="AB13" t="n">
         <v>27.27915518824609</v>
@@ -3156,6 +3156,4053 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>22.65277777777778</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>181.3222222222222</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>66.14938271604939</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1785949.074074074</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>72.53117283950617</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26.65343434343434</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>179.7911111111111</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.227878787878788</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>69.87191919191919</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2979933.333333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>72.82747474747475</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21.6007566277634</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>180.8526674214362</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>62.72404523390075</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1413142.453233673</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>71.61935548029011</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>25.28426065162908</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>180.2330359990886</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.148748006379585</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>64.28217133743451</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2554160.771246297</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>69.17277511961723</v>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>26.03958333333334</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>179.4174242424242</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.153030303030303</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>67.30473484848484</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3587451.704545455</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>71.98863636363636</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>26.17363636363637</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>182.3781818181818</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.182727272727273</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2007109.090909091</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>67.92999999999999</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.68952636426767</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>179.6997799390395</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.040636446886447</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>65.73400749949199</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2197038.039728888</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>70.46776288242712</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>23.24705931495405</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>178.4779448621554</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.145075187969925</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>63.00403508771929</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1576511.758563075</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>69.16009189640769</v>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>23.75454545454546</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>179.3909090909091</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.018181818181818</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65.63636363636364</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1257500</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>25.51652892561983</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>183.4438016528926</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.066942148760331</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>69.16198347107438</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2900619.834710744</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>73.20165289256198</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23.15305194805195</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>180.671376167692</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.09350991114149</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>64.77004556846661</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1300155.659033948</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>71.54494588744589</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>24.67758945599855</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>181.4551505312869</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.077201964701965</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>65.49582235945873</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1612552.228074955</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>70.9492314503678</v>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>26.44318181818182</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>181.1022727272727</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.095454545454546</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>68.89772727272727</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3120511.363636363</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>71.84545454545454</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25.47907647907648</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>180.620202020202</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>67.91096681096681</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2844783.54978355</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>72.13953823953824</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25.44471344627595</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>181.3140337705595</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.088901009121597</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>66.02711890846082</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1350582.405237736</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>71.75576204840911</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>24.52395262452807</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>181.0610903056875</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>64.96388076969917</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1786551.196565583</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>70.62392522226281</v>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="n">
+        <v>23.21818181818182</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>180.0727272727273</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.109090909090909</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>68.14545454545454</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2859272.727272728</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>74.41818181818182</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>184.3036363636364</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.096363636363636</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>66.80636363636364</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1350831.818181818</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>70.13545454545456</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23.24955918122798</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>180.7991568150519</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.075638223668914</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>63.89402556203387</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1766865.619578631</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>71.94746311233523</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>23.25672932330827</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>182.3671052631579</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.016374269005848</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>61.95435254803677</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>898935.7351712615</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>70.95589807852966</v>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>167</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>25.70378787878788</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>182.4560606060606</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.071969696969697</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>67.6189393939394</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2701181.818181818</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>71.47121212121213</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25.06565656565657</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>179.5545454545455</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>69.1010101010101</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3848742.424242424</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>73.47373737373738</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24.83403081154797</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>180.003012884649</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.032162380589154</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>63.45350342671566</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1530920.880305177</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>69.36098939914014</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>24.50090934924695</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>181.3305981813015</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>61.57634744719144</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1320390.463673392</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>67.01808989296201</v>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>167</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>26.72479338842976</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>180.4487603305785</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.150413223140496</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>67.67107438016528</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1823454.545454545</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>70.72396694214876</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>25.75818181818182</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>182.66</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.009090909090909</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>65.87090909090909</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1534145.454545454</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>70.92363636363636</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25.76192218779072</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>180.0522974026875</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.093980174414957</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>64.39502667316272</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1282244.073360128</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>68.51270476166461</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>26.32476515243778</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>181.1750803799781</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.101456176673568</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>65.48604473673528</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1668900.241545894</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>70.06231234522795</v>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>167</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>27.78181818181818</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>183.8272727272727</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.163636363636364</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>69.3090909090909</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3256363.636363636</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>71.11818181818182</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>27.25454545454546</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>182.2181818181818</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.736363636363636</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>73.78181818181818</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>6621363.636363636</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>77.53636363636363</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>27.64622551361682</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>182.9841196846632</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.051268115942029</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>65.43584766682594</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1150764.791368052</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>66.68405000796307</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>24.02701802460114</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>184.6031281208135</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.12188527584947</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>67.58187187918645</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>2499046.659968335</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>73.93571367677505</v>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>167</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>27.21212121212121</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>180.0530303030303</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.054545454545454</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>66.05454545454545</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1177405.303030303</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>68.96893939393939</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>27.86454545454545</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>179.7009090909091</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.105454545454545</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>67.43454545454544</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2236636.363636364</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>68.67363636363636</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>25.28016620657925</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>180.0291497009432</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.068224062571889</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>63.45648521969175</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1026174.910858063</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>67.74128249367379</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>28.18272337920676</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>181.3099959404051</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.294768603093411</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>65.16072281086348</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1122171.233710876</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>67.08197824057159</v>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>167</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>27.27915518824609</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>180.349494949495</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.326629935720845</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>71.94205693296603</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4212235.996326906</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>74.96951331496786</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>24.05333333333333</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>180.1566666666667</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>65.63222222222223</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1684472.222222222</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>26.14668894746784</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>179.6685753053168</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.011544011544012</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>67.41159755374183</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1863518.478013436</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>72.42885426239008</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>22.34684457841108</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>178.76395110218</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>60.92601114358788</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>815187.443165672</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>69.27438903097472</v>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>167</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>26.91363636363637</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>178.6272727272727</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>69.73090909090908</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2783481.818181818</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>72.15727272727273</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>26.00090909090909</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>181.7309090909091</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>65.48181818181817</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1196763.636363636</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>69.79818181818182</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>26.83216955529178</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>179.6193309408917</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>67.16141846153204</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1629740.708219873</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>69.17343898380378</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>24.68050825593395</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>180.4478396861137</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>64.05659106545329</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1207030.910889077</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>69.89703827304447</v>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>167</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>26.75289256198348</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>180.7826446280992</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>69.3396694214876</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2505595.041322314</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>72.67272727272727</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>26.20777777777778</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>179.1522222222222</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.042222222222222</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>70.20444444444445</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>3522972.222222222</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>74.37555555555556</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>25.50357181440069</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>180.5375114784206</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>65.67889456057905</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1497754.685896397</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>70.14182196294496</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>23.75088788413916</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>177.481125370438</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.030677191166322</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>64.4075546522957</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1515294.814121301</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>70.58452883327243</v>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>26.45707070707071</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>180.3956487956488</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.209013209013209</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>68.3454156954157</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1943349.261849262</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>72.45023310023309</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>25.47272727272727</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>182.0666666666667</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.065656565656566</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>67.889898989899</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2447146.464646464</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>71.74040404040404</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>23.95306324222733</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>178.8676633480039</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.089098551946849</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>63.36927152654707</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1421666.783766629</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>69.73409799694629</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>26.56630800761236</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>180.9842464500073</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.166057312252964</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>65.92384167764602</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1388838.566827697</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>69.19558263797394</v>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Uw6sTk0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>25.79595959595959</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>177.1878787878788</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>69.06969696969696</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2686565.656565657</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>71.77373737373738</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>25.55656565656566</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>182.3242424242424</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.18989898989899</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>68.08181818181818</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2174974.747474747</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>71.47575757575758</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>24.81521739130435</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>177.6397247143624</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>64.96886550111188</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1079253.651943869</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>69.40172149375047</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>24.02377864223839</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>182.3296877443162</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>64.86937274112196</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1447339.602906553</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>69.97149725919076</v>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>167</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>25.47907647907648</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>180.620202020202</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>67.91096681096681</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2844783.54978355</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>72.13953823953824</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>27.78181818181818</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>183.8272727272727</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.163636363636364</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>69.3090909090909</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>3256363.636363636</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>71.11818181818182</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>24.52395262452807</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>181.0610903056875</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>64.96388076969917</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1786551.196565583</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>70.62392522226281</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>27.64622551361682</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>182.9841196846632</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.051268115942029</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>65.43584766682594</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1150764.791368052</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>66.68405000796307</v>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>6gpXy3v</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>167</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>25.75818181818182</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>182.66</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.009090909090909</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>65.87090909090909</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1534145.454545454</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>70.92363636363636</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>27.25454545454546</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>182.2181818181818</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.736363636363636</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>73.78181818181818</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>6621363.636363636</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>77.53636363636363</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>26.32476515243778</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>181.1750803799781</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.101456176673568</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>65.48604473673528</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1668900.241545894</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>70.06231234522795</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>24.02701802460114</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>184.6031281208135</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.12188527584947</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>67.58187187918645</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>2499046.659968335</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>73.93571367677505</v>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>022mBmS</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>167</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>184.3036363636364</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.096363636363636</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>66.80636363636364</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1350831.818181818</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>70.13545454545456</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>25.06565656565657</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>179.5545454545455</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>69.1010101010101</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3848742.424242424</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>73.47373737373738</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23.25672932330827</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>182.3671052631579</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.016374269005848</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>61.95435254803677</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>898935.7351712615</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>70.95589807852966</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>24.50090934924695</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>181.3305981813015</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>61.57634744719144</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1320390.463673392</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>67.01808989296201</v>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>22.65277777777778</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>181.3222222222222</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>66.14938271604939</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1785949.074074074</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>72.53117283950617</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23.75454545454546</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>179.3909090909091</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.018181818181818</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>65.63636363636364</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1257500</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>21.6007566277634</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>180.8526674214362</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>62.72404523390075</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1413142.453233673</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>71.61935548029011</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>23.15305194805195</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>180.671376167692</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.09350991114149</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>64.77004556846661</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1300155.659033948</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>71.54494588744589</v>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>rJ9D8rz</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>26.17363636363637</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>182.3781818181818</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.182727272727273</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2007109.090909091</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>67.92999999999999</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>26.65343434343434</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>179.7911111111111</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.227878787878788</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>69.87191919191919</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2979933.333333333</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>72.82747474747475</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.24705931495405</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>178.4779448621554</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.145075187969925</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>63.00403508771929</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1576511.758563075</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>69.16009189640769</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>25.28426065162908</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>180.2330359990886</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.148748006379585</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>64.28217133743451</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>2554160.771246297</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>69.17277511961723</v>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>167</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>26.44318181818182</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>181.1022727272727</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.095454545454546</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>68.89772727272727</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3120511.363636363</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>71.84545454545454</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>26.03958333333334</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>179.4174242424242</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.153030303030303</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>67.30473484848484</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>3587451.704545455</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>71.98863636363636</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>25.44471344627595</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>181.3140337705595</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.088901009121597</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>66.02711890846082</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1350582.405237736</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>71.75576204840911</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>25.68952636426767</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>179.6997799390395</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.040636446886447</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>65.73400749949199</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>2197038.039728888</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>70.46776288242712</v>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>25.47272727272727</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>182.0666666666667</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.065656565656566</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>67.889898989899</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2447146.464646464</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>71.74040404040404</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>25.51652892561983</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>183.4438016528926</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.066942148760331</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>69.16198347107438</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2900619.834710744</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>73.20165289256198</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>26.56630800761236</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>180.9842464500073</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.166057312252964</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>65.92384167764602</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1388838.566827697</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>69.19558263797394</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>24.67758945599855</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>181.4551505312869</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.077201964701965</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>65.49582235945873</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1612552.228074955</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>70.9492314503678</v>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>167</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>26.00090909090909</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>181.7309090909091</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>65.48181818181817</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1196763.636363636</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>69.79818181818182</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>25.79595959595959</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>177.1878787878788</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>69.06969696969696</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2686565.656565657</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>71.77373737373738</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>24.68050825593395</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>180.4478396861137</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>64.05659106545329</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1207030.910889077</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>69.89703827304447</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>24.81521739130435</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>177.6397247143624</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>64.96886550111188</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1079253.651943869</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>69.40172149375047</v>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>167</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>25.55656565656566</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>182.3242424242424</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.18989898989899</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>68.08181818181818</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2174974.747474747</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>71.47575757575758</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>26.75289256198348</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>180.7826446280992</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>69.3396694214876</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2505595.041322314</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>72.67272727272727</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>24.02377864223839</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>182.3296877443162</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>64.86937274112196</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1447339.602906553</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>69.97149725919076</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>25.50357181440069</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>180.5375114784206</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>65.67889456057905</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1497754.685896397</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>70.14182196294496</v>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>167</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>24.08356290174472</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>179.106795224977</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>65.2931129476584</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1578668.044077135</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>72.2584940312213</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>26.72479338842976</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>180.4487603305785</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.150413223140496</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>67.67107438016528</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1823454.545454545</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>70.72396694214876</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>24.75393289349056</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>178.4845443033161</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>63.68275336259235</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1330429.532557976</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>70.26097384428586</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>25.76192218779072</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>180.0522974026875</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.093980174414957</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>64.39502667316272</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1282244.073360128</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>68.51270476166461</v>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>tOpyQa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>167</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>25.70378787878788</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>182.4560606060606</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.071969696969697</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>67.6189393939394</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2701181.818181818</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>71.47121212121213</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>26.91363636363637</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>178.6272727272727</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>69.73090909090908</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2783481.818181818</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>72.15727272727273</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>24.83403081154797</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>180.003012884649</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.032162380589154</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>63.45350342671566</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1530920.880305177</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>69.36098939914014</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>26.83216955529178</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>179.6193309408917</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>67.16141846153204</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1629740.708219873</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>69.17343898380378</v>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>167</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>24.05333333333333</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>180.1566666666667</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>65.63222222222223</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1684472.222222222</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>27.21212121212121</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>180.0530303030303</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.054545454545454</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>66.05454545454545</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1177405.303030303</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>68.96893939393939</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>22.34684457841108</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>178.76395110218</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>60.92601114358788</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>815187.443165672</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>69.27438903097472</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>25.28016620657925</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>180.0291497009432</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.068224062571889</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>63.45648521969175</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1026174.910858063</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>67.74128249367379</v>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>rXawJi8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>167</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>26.20777777777778</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>179.1522222222222</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.042222222222222</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>70.20444444444445</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3522972.222222222</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>74.37555555555556</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>27.27915518824609</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>180.349494949495</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.326629935720845</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>71.94205693296603</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>4212235.996326906</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>74.96951331496786</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>23.75088788413916</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>177.481125370438</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.030677191166322</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>64.4075546522957</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1515294.814121301</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>70.58452883327243</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>26.14668894746784</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>179.6685753053168</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1.011544011544012</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>67.41159755374183</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1863518.478013436</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>72.42885426239008</v>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -681,76 +681,76 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.47907647907648</v>
+        <v>25.54835858585859</v>
       </c>
       <c r="O2" t="n">
-        <v>180.620202020202</v>
+        <v>180.0435606060606</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>67.91096681096681</v>
+        <v>67.94880050505051</v>
       </c>
       <c r="R2" t="n">
-        <v>2844783.54978355</v>
+        <v>3189988.952020202</v>
       </c>
       <c r="S2" t="n">
-        <v>72.13953823953824</v>
+        <v>72.10296717171718</v>
       </c>
       <c r="T2" t="n">
-        <v>27.21212121212121</v>
+        <v>27.77359307359307</v>
       </c>
       <c r="U2" t="n">
-        <v>180.0530303030303</v>
+        <v>179.8160173160173</v>
       </c>
       <c r="V2" t="n">
-        <v>1.054545454545454</v>
+        <v>1.064502164502164</v>
       </c>
       <c r="W2" t="n">
-        <v>66.05454545454545</v>
+        <v>67.31212121212123</v>
       </c>
       <c r="X2" t="n">
-        <v>1177405.303030303</v>
+        <v>1339160.173160173</v>
       </c>
       <c r="Y2" t="n">
-        <v>68.96893939393939</v>
+        <v>69.65844155844155</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.52395262452807</v>
+        <v>24.47435026876363</v>
       </c>
       <c r="AA2" t="n">
-        <v>181.0610903056875</v>
+        <v>181.8608002897305</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>64.96388076969917</v>
+        <v>64.129170057351</v>
       </c>
       <c r="AD2" t="n">
-        <v>1786551.196565583</v>
+        <v>1414767.718228596</v>
       </c>
       <c r="AE2" t="n">
-        <v>70.62392522226281</v>
+        <v>70.10290419033225</v>
       </c>
       <c r="AF2" t="n">
-        <v>25.28016620657925</v>
+        <v>24.78553515125857</v>
       </c>
       <c r="AG2" t="n">
-        <v>180.0291497009432</v>
+        <v>179.7982529436895</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.068224062571889</v>
+        <v>1.055406191462092</v>
       </c>
       <c r="AI2" t="n">
-        <v>63.45648521969175</v>
+        <v>62.60389813896573</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1026174.910858063</v>
+        <v>929580.1522541385</v>
       </c>
       <c r="AK2" t="n">
-        <v>67.74128249367379</v>
+        <v>67.40614524070497</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,76 +816,76 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26.86</v>
+        <v>26.89409888357256</v>
       </c>
       <c r="O3" t="n">
-        <v>184.3036363636364</v>
+        <v>183.723870281765</v>
       </c>
       <c r="P3" t="n">
-        <v>1.096363636363636</v>
+        <v>1.088835725677831</v>
       </c>
       <c r="Q3" t="n">
-        <v>66.80636363636364</v>
+        <v>67.09154704944177</v>
       </c>
       <c r="R3" t="n">
-        <v>1350831.818181818</v>
+        <v>1376433.280170122</v>
       </c>
       <c r="S3" t="n">
-        <v>70.13545454545456</v>
+        <v>70.26156299840511</v>
       </c>
       <c r="T3" t="n">
-        <v>26.72479338842976</v>
+        <v>26.43588516746411</v>
       </c>
       <c r="U3" t="n">
-        <v>180.4487603305785</v>
+        <v>180.3952153110048</v>
       </c>
       <c r="V3" t="n">
-        <v>1.150413223140496</v>
+        <v>1.087081339712919</v>
       </c>
       <c r="W3" t="n">
-        <v>67.67107438016528</v>
+        <v>67.09952153110048</v>
       </c>
       <c r="X3" t="n">
-        <v>1823454.545454545</v>
+        <v>1566511.961722488</v>
       </c>
       <c r="Y3" t="n">
-        <v>70.72396694214876</v>
+        <v>70.61578947368423</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.25672932330827</v>
+        <v>22.68097217901683</v>
       </c>
       <c r="AA3" t="n">
-        <v>182.3671052631579</v>
+        <v>182.1059435958552</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.016374269005848</v>
+        <v>1.008790034942878</v>
       </c>
       <c r="AC3" t="n">
-        <v>61.95435254803677</v>
+        <v>61.00065291876844</v>
       </c>
       <c r="AD3" t="n">
-        <v>898935.7351712615</v>
+        <v>826052.7860896731</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.95589807852966</v>
+        <v>70.89340967227149</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.76192218779072</v>
+        <v>25.51323432573406</v>
       </c>
       <c r="AG3" t="n">
-        <v>180.0522974026875</v>
+        <v>179.8456790698987</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.093980174414957</v>
+        <v>1.07298542605448</v>
       </c>
       <c r="AI3" t="n">
-        <v>64.39502667316272</v>
+        <v>63.43091446593441</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1282244.073360128</v>
+        <v>1137761.141418114</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.51270476166461</v>
+        <v>68.09789395193572</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,76 +951,76 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>25.06565656565657</v>
+        <v>25.55808080808081</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5545454545455</v>
+        <v>179.3712121212121</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>69.1010101010101</v>
+        <v>69.31767676767677</v>
       </c>
       <c r="R4" t="n">
-        <v>3848742.424242424</v>
+        <v>3852702.020202021</v>
       </c>
       <c r="S4" t="n">
-        <v>73.47373737373738</v>
+        <v>72.91313131313132</v>
       </c>
       <c r="T4" t="n">
-        <v>26.44318181818182</v>
+        <v>26.35025252525253</v>
       </c>
       <c r="U4" t="n">
-        <v>181.1022727272727</v>
+        <v>181.2712121212121</v>
       </c>
       <c r="V4" t="n">
-        <v>1.095454545454546</v>
+        <v>1.109217171717172</v>
       </c>
       <c r="W4" t="n">
-        <v>68.89772727272727</v>
+        <v>69.27885101010101</v>
       </c>
       <c r="X4" t="n">
-        <v>3120511.363636363</v>
+        <v>3340707.070707071</v>
       </c>
       <c r="Y4" t="n">
-        <v>71.84545454545454</v>
+        <v>72.33377525252526</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.50090934924695</v>
+        <v>24.4862842403679</v>
       </c>
       <c r="AA4" t="n">
-        <v>181.3305981813015</v>
+        <v>181.1186014642318</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>61.57634744719144</v>
+        <v>62.05174523407126</v>
       </c>
       <c r="AD4" t="n">
-        <v>1320390.463673392</v>
+        <v>1557474.408127095</v>
       </c>
       <c r="AE4" t="n">
-        <v>67.01808989296201</v>
+        <v>67.21080752285658</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.44471344627595</v>
+        <v>25.63720537261801</v>
       </c>
       <c r="AG4" t="n">
-        <v>181.3140337705595</v>
+        <v>179.3690997472707</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.088901009121597</v>
+        <v>1.067161641140937</v>
       </c>
       <c r="AI4" t="n">
-        <v>66.02711890846082</v>
+        <v>65.87091202329447</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1350582.405237736</v>
+        <v>1256095.052245763</v>
       </c>
       <c r="AK4" t="n">
-        <v>71.75576204840911</v>
+        <v>71.01413891298759</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,76 +1086,76 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23.21818181818182</v>
+        <v>23.37799043062201</v>
       </c>
       <c r="O5" t="n">
-        <v>180.0727272727273</v>
+        <v>180.0622009569378</v>
       </c>
       <c r="P5" t="n">
-        <v>1.109090909090909</v>
+        <v>1.124401913875598</v>
       </c>
       <c r="Q5" t="n">
-        <v>68.14545454545454</v>
+        <v>68.34928229665071</v>
       </c>
       <c r="R5" t="n">
-        <v>2859272.727272728</v>
+        <v>2960382.775119618</v>
       </c>
       <c r="S5" t="n">
-        <v>74.41818181818182</v>
+        <v>74.28229665071771</v>
       </c>
       <c r="T5" t="n">
-        <v>26.17363636363637</v>
+        <v>26.42631578947368</v>
       </c>
       <c r="U5" t="n">
-        <v>182.3781818181818</v>
+        <v>182.222966507177</v>
       </c>
       <c r="V5" t="n">
-        <v>1.182727272727273</v>
+        <v>1.211004784688995</v>
       </c>
       <c r="W5" t="n">
-        <v>64.54545454545455</v>
+        <v>65.07655502392345</v>
       </c>
       <c r="X5" t="n">
-        <v>2007109.090909091</v>
+        <v>2224100.4784689</v>
       </c>
       <c r="Y5" t="n">
-        <v>67.92999999999999</v>
+        <v>68.28851674641149</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.24955918122798</v>
+        <v>22.83886346431271</v>
       </c>
       <c r="AA5" t="n">
-        <v>180.7991568150519</v>
+        <v>180.480671143442</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.075638223668914</v>
+        <v>1.060074020593606</v>
       </c>
       <c r="AC5" t="n">
-        <v>63.89402556203387</v>
+        <v>63.95358070516403</v>
       </c>
       <c r="AD5" t="n">
-        <v>1766865.619578631</v>
+        <v>1829982.318211992</v>
       </c>
       <c r="AE5" t="n">
-        <v>71.94746311233523</v>
+        <v>72.02278760298346</v>
       </c>
       <c r="AF5" t="n">
-        <v>23.24705931495405</v>
+        <v>23.18057457283039</v>
       </c>
       <c r="AG5" t="n">
-        <v>178.4779448621554</v>
+        <v>179.1445434455009</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.145075187969925</v>
+        <v>1.109160200271846</v>
       </c>
       <c r="AI5" t="n">
-        <v>63.00403508771929</v>
+        <v>62.8740878963931</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1576511.758563075</v>
+        <v>1375297.589980777</v>
       </c>
       <c r="AK5" t="n">
-        <v>69.16009189640769</v>
+        <v>68.93099661990425</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1225,76 +1225,76 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26.65343434343434</v>
+        <v>26.91919191919192</v>
       </c>
       <c r="O6" t="n">
-        <v>179.7911111111111</v>
+        <v>179.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.227878787878788</v>
+        <v>1.208080808080808</v>
       </c>
       <c r="Q6" t="n">
-        <v>69.87191919191919</v>
+        <v>69.73686868686869</v>
       </c>
       <c r="R6" t="n">
-        <v>2979933.333333333</v>
+        <v>2875444.444444444</v>
       </c>
       <c r="S6" t="n">
-        <v>72.82747474747475</v>
+        <v>72.4979797979798</v>
       </c>
       <c r="T6" t="n">
-        <v>25.47272727272727</v>
+        <v>26.23181818181818</v>
       </c>
       <c r="U6" t="n">
-        <v>182.0666666666667</v>
+        <v>182.1636363636364</v>
       </c>
       <c r="V6" t="n">
-        <v>1.065656565656566</v>
+        <v>1.123232323232323</v>
       </c>
       <c r="W6" t="n">
-        <v>67.889898989899</v>
+        <v>68.38636363636364</v>
       </c>
       <c r="X6" t="n">
-        <v>2447146.464646464</v>
+        <v>2481805.555555556</v>
       </c>
       <c r="Y6" t="n">
-        <v>71.74040404040404</v>
+        <v>71.44090909090909</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.28426065162908</v>
+        <v>25.4611501671761</v>
       </c>
       <c r="AA6" t="n">
-        <v>180.2330359990886</v>
+        <v>179.5872864528471</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.148748006379585</v>
+        <v>1.180429100308963</v>
       </c>
       <c r="AC6" t="n">
-        <v>64.28217133743451</v>
+        <v>64.88173379576888</v>
       </c>
       <c r="AD6" t="n">
-        <v>2554160.771246297</v>
+        <v>2522301.357533051</v>
       </c>
       <c r="AE6" t="n">
-        <v>69.17277511961723</v>
+        <v>69.63357305392012</v>
       </c>
       <c r="AF6" t="n">
-        <v>26.56630800761236</v>
+        <v>26.23425069925496</v>
       </c>
       <c r="AG6" t="n">
-        <v>180.9842464500073</v>
+        <v>180.8025647490002</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.166057312252964</v>
+        <v>1.143240162043444</v>
       </c>
       <c r="AI6" t="n">
-        <v>65.92384167764602</v>
+        <v>65.92626762643279</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1388838.566827697</v>
+        <v>1487202.076098336</v>
       </c>
       <c r="AK6" t="n">
-        <v>69.19558263797394</v>
+        <v>69.40392618692916</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,76 +1364,76 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25.51652892561983</v>
+        <v>25.45656565656565</v>
       </c>
       <c r="O7" t="n">
-        <v>183.4438016528926</v>
+        <v>183.5111111111111</v>
       </c>
       <c r="P7" t="n">
-        <v>1.066942148760331</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.16198347107438</v>
+        <v>69.23383838383837</v>
       </c>
       <c r="R7" t="n">
-        <v>2900619.834710744</v>
+        <v>2962782.828282828</v>
       </c>
       <c r="S7" t="n">
-        <v>73.20165289256198</v>
+        <v>73.33939393939393</v>
       </c>
       <c r="T7" t="n">
-        <v>25.75818181818182</v>
+        <v>26.1311004784689</v>
       </c>
       <c r="U7" t="n">
-        <v>182.66</v>
+        <v>182.3425837320574</v>
       </c>
       <c r="V7" t="n">
-        <v>1.009090909090909</v>
+        <v>1.019138755980861</v>
       </c>
       <c r="W7" t="n">
-        <v>65.87090909090909</v>
+        <v>66.58277511961722</v>
       </c>
       <c r="X7" t="n">
-        <v>1534145.454545454</v>
+        <v>1632133.971291865</v>
       </c>
       <c r="Y7" t="n">
-        <v>70.92363636363636</v>
+        <v>71.28516746411482</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.67758945599855</v>
+        <v>25.1544450124752</v>
       </c>
       <c r="AA7" t="n">
-        <v>181.4551505312869</v>
+        <v>181.9643642283929</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.077201964701965</v>
+        <v>1.116209096917301</v>
       </c>
       <c r="AC7" t="n">
-        <v>65.49582235945873</v>
+        <v>65.34681668520678</v>
       </c>
       <c r="AD7" t="n">
-        <v>1612552.228074955</v>
+        <v>1606587.945837559</v>
       </c>
       <c r="AE7" t="n">
-        <v>70.9492314503678</v>
+        <v>70.45709904918496</v>
       </c>
       <c r="AF7" t="n">
-        <v>26.32476515243778</v>
+        <v>26.26519287348806</v>
       </c>
       <c r="AG7" t="n">
-        <v>181.1750803799781</v>
+        <v>181.6026296559814</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.101456176673568</v>
+        <v>1.099131807566658</v>
       </c>
       <c r="AI7" t="n">
-        <v>65.48604473673528</v>
+        <v>65.25069421742762</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1668900.241545894</v>
+        <v>1561535.408347168</v>
       </c>
       <c r="AK7" t="n">
-        <v>70.06231234522795</v>
+        <v>69.87362783023201</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1503,76 +1503,76 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>26.00090909090909</v>
+        <v>26.15151515151515</v>
       </c>
       <c r="O8" t="n">
-        <v>181.7309090909091</v>
+        <v>181.0252525252525</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>65.48181818181817</v>
+        <v>65.8989898989899</v>
       </c>
       <c r="R8" t="n">
-        <v>1196763.636363636</v>
+        <v>1264545.454545454</v>
       </c>
       <c r="S8" t="n">
-        <v>69.79818181818182</v>
+        <v>70.09595959595961</v>
       </c>
       <c r="T8" t="n">
-        <v>27.86454545454545</v>
+        <v>28.23636363636364</v>
       </c>
       <c r="U8" t="n">
-        <v>179.7009090909091</v>
+        <v>179.7775119617225</v>
       </c>
       <c r="V8" t="n">
-        <v>1.105454545454545</v>
+        <v>1.100956937799043</v>
       </c>
       <c r="W8" t="n">
-        <v>67.43454545454544</v>
+        <v>67.49712918660288</v>
       </c>
       <c r="X8" t="n">
-        <v>2236636.363636364</v>
+        <v>2019736.842105263</v>
       </c>
       <c r="Y8" t="n">
-        <v>68.67363636363636</v>
+        <v>68.62344497607656</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.68050825593395</v>
+        <v>24.64087787054034</v>
       </c>
       <c r="AA8" t="n">
-        <v>180.4478396861137</v>
+        <v>180.3467339614365</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.006944444444444</v>
       </c>
       <c r="AC8" t="n">
-        <v>64.05659106545329</v>
+        <v>63.82916090781269</v>
       </c>
       <c r="AD8" t="n">
-        <v>1207030.910889077</v>
+        <v>1276583.112932989</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.89703827304447</v>
+        <v>69.63416630266364</v>
       </c>
       <c r="AF8" t="n">
-        <v>28.18272337920676</v>
+        <v>28.23349047395264</v>
       </c>
       <c r="AG8" t="n">
-        <v>181.3099959404051</v>
+        <v>181.1347096428198</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.294768603093411</v>
+        <v>1.312989938839561</v>
       </c>
       <c r="AI8" t="n">
-        <v>65.16072281086348</v>
+        <v>65.40000448692062</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1122171.233710876</v>
+        <v>1247320.658225352</v>
       </c>
       <c r="AK8" t="n">
-        <v>67.08197824057159</v>
+        <v>67.22094125839344</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1638,76 +1638,76 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>27.78181818181818</v>
+        <v>27.52020202020202</v>
       </c>
       <c r="O9" t="n">
-        <v>183.8272727272727</v>
+        <v>183.5656565656566</v>
       </c>
       <c r="P9" t="n">
-        <v>1.163636363636364</v>
+        <v>1.121212121212122</v>
       </c>
       <c r="Q9" t="n">
-        <v>69.3090909090909</v>
+        <v>68.26262626262627</v>
       </c>
       <c r="R9" t="n">
-        <v>3256363.636363636</v>
+        <v>2784722.222222222</v>
       </c>
       <c r="S9" t="n">
-        <v>71.11818181818182</v>
+        <v>70.07070707070707</v>
       </c>
       <c r="T9" t="n">
-        <v>22.65277777777778</v>
+        <v>22.70756172839506</v>
       </c>
       <c r="U9" t="n">
-        <v>181.3222222222222</v>
+        <v>181.4712962962963</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>66.14938271604939</v>
+        <v>66.45895061728395</v>
       </c>
       <c r="X9" t="n">
-        <v>1785949.074074074</v>
+        <v>1813499.228395062</v>
       </c>
       <c r="Y9" t="n">
-        <v>72.53117283950617</v>
+        <v>72.7486111111111</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.64622551361682</v>
+        <v>27.73626624985321</v>
       </c>
       <c r="AA9" t="n">
-        <v>182.9841196846632</v>
+        <v>182.9115001343262</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.051268115942029</v>
+        <v>1.050958602589037</v>
       </c>
       <c r="AC9" t="n">
-        <v>65.43584766682594</v>
+        <v>65.84022378587595</v>
       </c>
       <c r="AD9" t="n">
-        <v>1150764.791368052</v>
+        <v>1305381.228071445</v>
       </c>
       <c r="AE9" t="n">
-        <v>66.68405000796307</v>
+        <v>67.02616304790217</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.6007566277634</v>
+        <v>21.34733274380182</v>
       </c>
       <c r="AG9" t="n">
-        <v>180.8526674214362</v>
+        <v>180.7334869423811</v>
       </c>
       <c r="AH9" t="n">
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.72404523390075</v>
+        <v>62.39654966851175</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1413142.453233673</v>
+        <v>1346410.982426568</v>
       </c>
       <c r="AK9" t="n">
-        <v>71.61935548029011</v>
+        <v>71.71978576483642</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1773,76 +1773,76 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>25.55656565656566</v>
+        <v>25.38434343434343</v>
       </c>
       <c r="O10" t="n">
-        <v>182.3242424242424</v>
+        <v>182.2782828282828</v>
       </c>
       <c r="P10" t="n">
-        <v>1.18989898989899</v>
+        <v>1.185858585858586</v>
       </c>
       <c r="Q10" t="n">
-        <v>68.08181818181818</v>
+        <v>67.63181818181818</v>
       </c>
       <c r="R10" t="n">
-        <v>2174974.747474747</v>
+        <v>2058573.232323232</v>
       </c>
       <c r="S10" t="n">
-        <v>71.47575757575758</v>
+        <v>71.32373737373739</v>
       </c>
       <c r="T10" t="n">
-        <v>26.03958333333334</v>
+        <v>25.98329545454545</v>
       </c>
       <c r="U10" t="n">
-        <v>179.4174242424242</v>
+        <v>179.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.153030303030303</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>67.30473484848484</v>
+        <v>67.77829545454544</v>
       </c>
       <c r="X10" t="n">
-        <v>3587451.704545455</v>
+        <v>4713993.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>71.98863636363636</v>
+        <v>72.37818181818182</v>
       </c>
       <c r="Z10" t="n">
-        <v>24.02377864223839</v>
+        <v>24.00811574439081</v>
       </c>
       <c r="AA10" t="n">
-        <v>182.3296877443162</v>
+        <v>181.8799792072019</v>
       </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>64.86937274112196</v>
+        <v>65.18071489249532</v>
       </c>
       <c r="AD10" t="n">
-        <v>1447339.602906553</v>
+        <v>1409257.498519926</v>
       </c>
       <c r="AE10" t="n">
-        <v>69.97149725919076</v>
+        <v>70.09860154214317</v>
       </c>
       <c r="AF10" t="n">
-        <v>25.68952636426767</v>
+        <v>25.35121911236824</v>
       </c>
       <c r="AG10" t="n">
-        <v>179.6997799390395</v>
+        <v>178.8445771672633</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.040636446886447</v>
+        <v>1.024381868131868</v>
       </c>
       <c r="AI10" t="n">
-        <v>65.73400749949199</v>
+        <v>65.53279486295513</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2197038.039728888</v>
+        <v>1891623.233210568</v>
       </c>
       <c r="AK10" t="n">
-        <v>70.46776288242712</v>
+        <v>70.49293704434429</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1912,76 +1912,76 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>24.05333333333333</v>
+        <v>24.07426900584795</v>
       </c>
       <c r="O11" t="n">
-        <v>180.1566666666667</v>
+        <v>180.33216374269</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>65.63222222222223</v>
+        <v>65.80409356725147</v>
       </c>
       <c r="R11" t="n">
-        <v>1684472.222222222</v>
+        <v>1743210.526315789</v>
       </c>
       <c r="S11" t="n">
-        <v>70.86</v>
+        <v>70.94269005847954</v>
       </c>
       <c r="T11" t="n">
-        <v>23.75454545454546</v>
+        <v>24.15656565656566</v>
       </c>
       <c r="U11" t="n">
-        <v>179.3909090909091</v>
+        <v>178.9494949494949</v>
       </c>
       <c r="V11" t="n">
-        <v>1.018181818181818</v>
+        <v>1.02020202020202</v>
       </c>
       <c r="W11" t="n">
-        <v>65.63636363636364</v>
+        <v>66.3080808080808</v>
       </c>
       <c r="X11" t="n">
-        <v>1257500</v>
+        <v>1379040.404040404</v>
       </c>
       <c r="Y11" t="n">
-        <v>71.3</v>
+        <v>71.32828282828282</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.34684457841108</v>
+        <v>22.04016506444155</v>
       </c>
       <c r="AA11" t="n">
-        <v>178.76395110218</v>
+        <v>178.9118479066588</v>
       </c>
       <c r="AB11" t="n">
         <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>60.92601114358788</v>
+        <v>60.82046514604733</v>
       </c>
       <c r="AD11" t="n">
-        <v>815187.443165672</v>
+        <v>821353.0726949425</v>
       </c>
       <c r="AE11" t="n">
-        <v>69.27438903097472</v>
+        <v>69.71017763887599</v>
       </c>
       <c r="AF11" t="n">
-        <v>23.15305194805195</v>
+        <v>23.60189393939394</v>
       </c>
       <c r="AG11" t="n">
-        <v>180.671376167692</v>
+        <v>179.9364788233209</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.09350991114149</v>
+        <v>1.132637781321992</v>
       </c>
       <c r="AI11" t="n">
-        <v>64.77004556846661</v>
+        <v>65.22575282904229</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1300155.659033948</v>
+        <v>1359213.461368066</v>
       </c>
       <c r="AK11" t="n">
-        <v>71.54494588744589</v>
+        <v>71.42873977873978</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,76 +2047,76 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>24.08356290174472</v>
+        <v>24.37977139819245</v>
       </c>
       <c r="O12" t="n">
-        <v>179.106795224977</v>
+        <v>179.0470228601807</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>65.2931129476584</v>
+        <v>65.42476076555025</v>
       </c>
       <c r="R12" t="n">
-        <v>1578668.044077135</v>
+        <v>1464096.291866029</v>
       </c>
       <c r="S12" t="n">
-        <v>72.2584940312213</v>
+        <v>72.02190324295587</v>
       </c>
       <c r="T12" t="n">
-        <v>26.20777777777778</v>
+        <v>26.90526315789474</v>
       </c>
       <c r="U12" t="n">
-        <v>179.1522222222222</v>
+        <v>178.7964912280702</v>
       </c>
       <c r="V12" t="n">
-        <v>1.042222222222222</v>
+        <v>1.063742690058479</v>
       </c>
       <c r="W12" t="n">
-        <v>70.20444444444445</v>
+        <v>70.90818713450292</v>
       </c>
       <c r="X12" t="n">
-        <v>3522972.222222222</v>
+        <v>3819137.426900585</v>
       </c>
       <c r="Y12" t="n">
-        <v>74.37555555555556</v>
+        <v>74.09181286549708</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.75393289349056</v>
+        <v>24.90852065298022</v>
       </c>
       <c r="AA12" t="n">
-        <v>178.4845443033161</v>
+        <v>178.4636804914316</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>63.68275336259235</v>
+        <v>63.74772666531757</v>
       </c>
       <c r="AD12" t="n">
-        <v>1330429.532557976</v>
+        <v>1248134.223592731</v>
       </c>
       <c r="AE12" t="n">
-        <v>70.26097384428586</v>
+        <v>70.4486457060284</v>
       </c>
       <c r="AF12" t="n">
-        <v>23.75088788413916</v>
+        <v>24.18773882424768</v>
       </c>
       <c r="AG12" t="n">
-        <v>177.481125370438</v>
+        <v>177.5440907818899</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.030677191166322</v>
+        <v>1.024729849987287</v>
       </c>
       <c r="AI12" t="n">
-        <v>64.4075546522957</v>
+        <v>64.77595783883793</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1515294.814121301</v>
+        <v>1618601.113556912</v>
       </c>
       <c r="AK12" t="n">
-        <v>70.58452883327243</v>
+        <v>70.27196218720481</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2178,76 +2178,76 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>27.27915518824609</v>
+        <v>27.67126262626262</v>
       </c>
       <c r="O13" t="n">
-        <v>180.349494949495</v>
+        <v>180.8522222222222</v>
       </c>
       <c r="P13" t="n">
-        <v>1.326629935720845</v>
+        <v>1.354191919191919</v>
       </c>
       <c r="Q13" t="n">
-        <v>71.94205693296603</v>
+        <v>72.36585858585859</v>
       </c>
       <c r="R13" t="n">
-        <v>4212235.996326906</v>
+        <v>4275127.525252526</v>
       </c>
       <c r="S13" t="n">
-        <v>74.96951331496786</v>
+        <v>75.14505050505049</v>
       </c>
       <c r="T13" t="n">
-        <v>26.75289256198348</v>
+        <v>26.98681818181818</v>
       </c>
       <c r="U13" t="n">
-        <v>180.7826446280992</v>
+        <v>180.6822727272727</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>69.3396694214876</v>
+        <v>69.18454545454544</v>
       </c>
       <c r="X13" t="n">
-        <v>2505595.041322314</v>
+        <v>2278597.727272728</v>
       </c>
       <c r="Y13" t="n">
-        <v>72.67272727272727</v>
+        <v>72.10545454545453</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.14668894746784</v>
+        <v>25.15640291081468</v>
       </c>
       <c r="AA13" t="n">
-        <v>179.6685753053168</v>
+        <v>179.2186756299256</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.011544011544012</v>
+        <v>1.006349206349206</v>
       </c>
       <c r="AC13" t="n">
-        <v>67.41159755374183</v>
+        <v>66.52125877798672</v>
       </c>
       <c r="AD13" t="n">
-        <v>1863518.478013436</v>
+        <v>1634108.670026869</v>
       </c>
       <c r="AE13" t="n">
-        <v>72.42885426239008</v>
+        <v>72.52667924803954</v>
       </c>
       <c r="AF13" t="n">
-        <v>25.50357181440069</v>
+        <v>25.76766293786081</v>
       </c>
       <c r="AG13" t="n">
-        <v>180.5375114784206</v>
+        <v>181.0599622037637</v>
       </c>
       <c r="AH13" t="n">
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>65.67889456057905</v>
+        <v>65.82684175587579</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1497754.685896397</v>
+        <v>1380854.848773294</v>
       </c>
       <c r="AK13" t="n">
-        <v>70.14182196294496</v>
+        <v>69.87069622440197</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2317,76 +2317,76 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>26.91363636363637</v>
+        <v>26.95885167464115</v>
       </c>
       <c r="O14" t="n">
-        <v>178.6272727272727</v>
+        <v>179.0301435406699</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>69.73090909090908</v>
+        <v>69.63492822966506</v>
       </c>
       <c r="R14" t="n">
-        <v>2783481.818181818</v>
+        <v>2676007.177033493</v>
       </c>
       <c r="S14" t="n">
-        <v>72.15727272727273</v>
+        <v>72.02009569377991</v>
       </c>
       <c r="T14" t="n">
-        <v>25.79595959595959</v>
+        <v>25.93208556149733</v>
       </c>
       <c r="U14" t="n">
-        <v>177.1878787878788</v>
+        <v>177.3411764705882</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>69.06969696969696</v>
+        <v>69.36524064171122</v>
       </c>
       <c r="X14" t="n">
-        <v>2686565.656565657</v>
+        <v>2753796.79144385</v>
       </c>
       <c r="Y14" t="n">
-        <v>71.77373737373738</v>
+        <v>72.05508021390375</v>
       </c>
       <c r="Z14" t="n">
-        <v>26.83216955529178</v>
+        <v>26.63839937839741</v>
       </c>
       <c r="AA14" t="n">
-        <v>179.6193309408917</v>
+        <v>179.7619704214555</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>67.16141846153204</v>
+        <v>66.48620923208608</v>
       </c>
       <c r="AD14" t="n">
-        <v>1629740.708219873</v>
+        <v>1381388.993746634</v>
       </c>
       <c r="AE14" t="n">
-        <v>69.17343898380378</v>
+        <v>68.83103282962972</v>
       </c>
       <c r="AF14" t="n">
-        <v>24.81521739130435</v>
+        <v>25.08054605241306</v>
       </c>
       <c r="AG14" t="n">
-        <v>177.6397247143624</v>
+        <v>177.6831256481512</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>64.96886550111188</v>
+        <v>65.12557978395574</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1079253.651943869</v>
+        <v>1115519.369803257</v>
       </c>
       <c r="AK14" t="n">
-        <v>69.40172149375047</v>
+        <v>69.19613369722066</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,76 +2456,76 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>26.45707070707071</v>
+        <v>26.40199615199615</v>
       </c>
       <c r="O15" t="n">
-        <v>180.3956487956488</v>
+        <v>180.6973063973064</v>
       </c>
       <c r="P15" t="n">
-        <v>1.209013209013209</v>
+        <v>1.224627224627225</v>
       </c>
       <c r="Q15" t="n">
-        <v>68.3454156954157</v>
+        <v>68.50430495430496</v>
       </c>
       <c r="R15" t="n">
-        <v>1943349.261849262</v>
+        <v>1972597.162097162</v>
       </c>
       <c r="S15" t="n">
-        <v>72.45023310023309</v>
+        <v>72.43109668109666</v>
       </c>
       <c r="T15" t="n">
-        <v>25.70378787878788</v>
+        <v>25.82409090909091</v>
       </c>
       <c r="U15" t="n">
-        <v>182.4560606060606</v>
+        <v>182.5536363636364</v>
       </c>
       <c r="V15" t="n">
-        <v>1.071969696969697</v>
+        <v>1.056818181818182</v>
       </c>
       <c r="W15" t="n">
-        <v>67.6189393939394</v>
+        <v>67.10454545454546</v>
       </c>
       <c r="X15" t="n">
-        <v>2701181.818181818</v>
+        <v>2458015.909090909</v>
       </c>
       <c r="Y15" t="n">
-        <v>71.47121212121213</v>
+        <v>71.08318181818181</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.95306324222733</v>
+        <v>24.20689286441455</v>
       </c>
       <c r="AA15" t="n">
-        <v>178.8676633480039</v>
+        <v>178.9530987772897</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.089098551946849</v>
+        <v>1.083752662366396</v>
       </c>
       <c r="AC15" t="n">
-        <v>63.36927152654707</v>
+        <v>63.45343306262389</v>
       </c>
       <c r="AD15" t="n">
-        <v>1421666.783766629</v>
+        <v>1472985.778357401</v>
       </c>
       <c r="AE15" t="n">
-        <v>69.73409799694629</v>
+        <v>69.33963019803836</v>
       </c>
       <c r="AF15" t="n">
-        <v>24.83403081154797</v>
+        <v>24.84932727646115</v>
       </c>
       <c r="AG15" t="n">
-        <v>180.003012884649</v>
+        <v>179.7948985892064</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.032162380589154</v>
+        <v>1.033645254440449</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.45350342671566</v>
+        <v>63.07001072821153</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1530920.880305177</v>
+        <v>1346162.906344228</v>
       </c>
       <c r="AK15" t="n">
-        <v>69.36098939914014</v>
+        <v>68.92713374392579</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM15"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,162 +465,162 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -658,109 +658,109 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>25.54835858585859</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>180.0435606060606</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>67.94880050505051</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>3189988.952020202</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>72.10296717171718</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>27.77359307359307</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>179.8160173160173</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>1.064502164502164</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>67.31212121212123</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>1339160.173160173</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>69.65844155844155</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>24.47435026876363</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>181.8608002897305</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>64.129170057351</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>1414767.718228596</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>70.10290419033225</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>24.78553515125857</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>179.7982529436895</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
         <v>1.055406191462092</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AK2" t="n">
         <v>62.60389813896573</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
         <v>929580.1522541385</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>67.40614524070497</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>6gpXy3v</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>rXawJi8</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,105 +797,105 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>26.89409888357256</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>183.723870281765</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>1.088835725677831</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>67.09154704944177</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>1376433.280170122</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>70.26156299840511</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>26.43588516746411</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>180.3952153110048</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>1.087081339712919</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>67.09952153110048</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>1566511.961722488</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>70.61578947368423</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>22.68097217901683</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>182.1059435958552</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>1.008790034942878</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>61.00065291876844</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>826052.7860896731</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>70.89340967227149</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>25.51323432573406</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>179.8456790698987</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>1.07298542605448</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>63.43091446593441</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>1137761.141418114</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>68.09789395193572</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>nJ01AhX</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>tOpyQa2</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -905,11 +905,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
@@ -932,105 +932,105 @@
           <t>tr3oe8I8</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>25.55808080808081</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>179.3712121212121</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>69.31767676767677</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>3852702.020202021</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>72.91313131313132</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>26.35025252525253</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>181.2712121212121</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>1.109217171717172</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>69.27885101010101</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>3340707.070707071</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>72.33377525252526</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>24.4862842403679</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>181.1186014642318</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>1</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>62.05174523407126</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>1557474.408127095</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>67.21080752285658</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>25.63720537261801</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>179.3690997472707</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>1.067161641140937</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>65.87091202329447</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AL4" t="n">
         <v>1256095.052245763</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>71.01413891298759</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>roEEsq7</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,105 +1067,105 @@
           <t>zsdfgnmL</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>167</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1671</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>j9cigLCr</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>23.37799043062201</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>180.0622009569378</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1.124401913875598</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>68.34928229665071</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>2960382.775119618</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>74.28229665071771</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>26.42631578947368</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>182.222966507177</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>1.211004784688995</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>65.07655502392345</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2224100.4784689</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>68.28851674641149</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>22.83886346431271</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>180.480671143442</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>1.060074020593606</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>63.95358070516403</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>1829982.318211992</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>72.02278760298346</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>23.18057457283039</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>179.1445434455009</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>1.109160200271846</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>62.8740878963931</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AL5" t="n">
         <v>1375297.589980777</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>68.93099661990425</v>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>EgT3xN3</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,109 +1202,109 @@
           <t>UwAwNo2E</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>167</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1671</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2024</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>tr3oe8I8</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>26.91919191919192</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>179.8</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1.208080808080808</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>69.73686868686869</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>2875444.444444444</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>72.4979797979798</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>26.23181818181818</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>182.1636363636364</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>1.123232323232323</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>68.38636363636364</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>2481805.555555556</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>71.44090909090909</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>25.4611501671761</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>179.5872864528471</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>1.180429100308963</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>64.88173379576888</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>2522301.357533051</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>69.63357305392012</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>26.23425069925496</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>180.8025647490002</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>1.143240162043444</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>65.92626762643279</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AL6" t="n">
         <v>1487202.076098336</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>69.40392618692916</v>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Uw6sTk0</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,109 +1341,109 @@
           <t>QJF7WTFB</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>167</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1671</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>2024</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>25.45656565656565</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>183.5111111111111</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1.066666666666667</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>69.23383838383837</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>2962782.828282828</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>73.33939393939393</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>26.1311004784689</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>182.3425837320574</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>1.019138755980861</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>66.58277511961722</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>1632133.971291865</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>71.28516746411482</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>25.1544450124752</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>181.9643642283929</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>1.116209096917301</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>65.34681668520678</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>1606587.945837559</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>70.45709904918496</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>26.26519287348806</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>181.6026296559814</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>1.099131807566658</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>65.25069421742762</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AL7" t="n">
         <v>1561535.408347168</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>69.87362783023201</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>roEEsq7</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>K4zRMgT</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,109 +1480,109 @@
           <t>IeT6JBE3</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>167</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1671</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>2024</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>26.15151515151515</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>181.0252525252525</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>65.8989898989899</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1264545.454545454</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>70.09595959595961</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>28.23636363636364</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>179.7775119617225</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>1.100956937799043</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>67.49712918660288</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>2019736.842105263</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>68.62344497607656</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>24.64087787054034</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>180.3467339614365</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>1.006944444444444</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>63.82916090781269</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>1276583.112932989</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>69.63416630266364</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>28.23349047395264</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>181.1347096428198</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>1.312989938839561</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>65.40000448692062</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AL8" t="n">
         <v>1247320.658225352</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AM8" t="n">
         <v>67.22094125839344</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>UL7r7du</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1619,105 +1619,105 @@
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>167</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1671</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>2024</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>27.52020202020202</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>183.5656565656566</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>1.121212121212122</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>68.26262626262627</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>2784722.222222222</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>70.07070707070707</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>22.70756172839506</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>181.4712962962963</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>1</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>66.45895061728395</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>1813499.228395062</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>72.7486111111111</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>27.73626624985321</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>182.9115001343262</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>1.050958602589037</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>65.84022378587595</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>1305381.228071445</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>67.02616304790217</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>21.34733274380182</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>180.7334869423811</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>1</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>62.39654966851175</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
         <v>1346410.982426568</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AM9" t="n">
         <v>71.71978576483642</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1754,788 +1754,105 @@
           <t>EPngUvhk</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>167</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1671</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>2024</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>25.38434343434343</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>182.2782828282828</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>1.185858585858586</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>67.63181818181818</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>2058573.232323232</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>71.32373737373739</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>25.98329545454545</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>179.05</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>1.21</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>67.77829545454544</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>4713993.75</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>72.37818181818182</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>24.00811574439081</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>181.8799792072019</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>1</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>65.18071489249532</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>1409257.498519926</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>70.09860154214317</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>25.35121911236824</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>178.8445771672633</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>1.024381868131868</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>65.53279486295513</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
         <v>1891623.233210568</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AM10" t="n">
         <v>70.49293704434429</v>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>l6eEjGl</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18061</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>167</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>24.07426900584795</v>
-      </c>
-      <c r="O11" t="n">
-        <v>180.33216374269</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>65.80409356725147</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1743210.526315789</v>
-      </c>
-      <c r="S11" t="n">
-        <v>70.94269005847954</v>
-      </c>
-      <c r="T11" t="n">
-        <v>24.15656565656566</v>
-      </c>
-      <c r="U11" t="n">
-        <v>178.9494949494949</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02020202020202</v>
-      </c>
-      <c r="W11" t="n">
-        <v>66.3080808080808</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1379040.404040404</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>71.32828282828282</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>22.04016506444155</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>178.9118479066588</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>60.82046514604733</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>821353.0726949425</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>69.71017763887599</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>23.60189393939394</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>179.9364788233209</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.132637781321992</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>65.22575282904229</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1359213.461368066</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>71.42873977873978</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>rJ9D8rz</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>167</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>24.37977139819245</v>
-      </c>
-      <c r="O12" t="n">
-        <v>179.0470228601807</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>65.42476076555025</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1464096.291866029</v>
-      </c>
-      <c r="S12" t="n">
-        <v>72.02190324295587</v>
-      </c>
-      <c r="T12" t="n">
-        <v>26.90526315789474</v>
-      </c>
-      <c r="U12" t="n">
-        <v>178.7964912280702</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.063742690058479</v>
-      </c>
-      <c r="W12" t="n">
-        <v>70.90818713450292</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3819137.426900585</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>74.09181286549708</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>24.90852065298022</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>178.4636804914316</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>63.74772666531757</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1248134.223592731</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>70.4486457060284</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>24.18773882424768</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>177.5440907818899</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.024729849987287</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>64.77595783883793</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1618601.113556912</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>70.27196218720481</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>jBBpU7Y</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>167</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>27.67126262626262</v>
-      </c>
-      <c r="O13" t="n">
-        <v>180.8522222222222</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.354191919191919</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>72.36585858585859</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4275127.525252526</v>
-      </c>
-      <c r="S13" t="n">
-        <v>75.14505050505049</v>
-      </c>
-      <c r="T13" t="n">
-        <v>26.98681818181818</v>
-      </c>
-      <c r="U13" t="n">
-        <v>180.6822727272727</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>69.18454545454544</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2278597.727272728</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>72.10545454545453</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>25.15640291081468</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>179.2186756299256</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.006349206349206</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>66.52125877798672</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1634108.670026869</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>72.52667924803954</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>25.76766293786081</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>181.0599622037637</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>65.82684175587579</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1380854.848773294</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>69.87069622440197</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>167</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>26.95885167464115</v>
-      </c>
-      <c r="O14" t="n">
-        <v>179.0301435406699</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>69.63492822966506</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2676007.177033493</v>
-      </c>
-      <c r="S14" t="n">
-        <v>72.02009569377991</v>
-      </c>
-      <c r="T14" t="n">
-        <v>25.93208556149733</v>
-      </c>
-      <c r="U14" t="n">
-        <v>177.3411764705882</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>69.36524064171122</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2753796.79144385</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>72.05508021390375</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>26.63839937839741</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>179.7619704214555</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>66.48620923208608</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1381388.993746634</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>68.83103282962972</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>25.08054605241306</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>177.6831256481512</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>65.12557978395574</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1115519.369803257</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>69.19613369722066</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>167</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>26.40199615199615</v>
-      </c>
-      <c r="O15" t="n">
-        <v>180.6973063973064</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.224627224627225</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>68.50430495430496</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1972597.162097162</v>
-      </c>
-      <c r="S15" t="n">
-        <v>72.43109668109666</v>
-      </c>
-      <c r="T15" t="n">
-        <v>25.82409090909091</v>
-      </c>
-      <c r="U15" t="n">
-        <v>182.5536363636364</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.056818181818182</v>
-      </c>
-      <c r="W15" t="n">
-        <v>67.10454545454546</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2458015.909090909</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>71.08318181818181</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>24.20689286441455</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>178.9530987772897</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.083752662366396</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>63.45343306262389</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1472985.778357401</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>69.33963019803836</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>24.84932727646115</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>179.7948985892064</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.033645254440449</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>63.07001072821153</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1346162.906344228</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>68.92713374392579</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -465,162 +465,162 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
         </is>
       </c>
     </row>
@@ -658,101 +658,101 @@
           <t>x05z14ue</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>27.67126262626262</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>180.8522222222222</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1.354191919191919</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>72.36585858585859</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>4275127.525252526</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>75.14505050505049</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>26.98681818181818</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>180.6822727272727</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>69.18454545454544</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>2278597.727272728</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>72.10545454545453</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>25.15640291081468</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>179.2186756299256</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>1.006349206349206</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>66.52125877798672</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>1634108.670026869</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>72.52667924803954</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>25.76766293786081</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>181.0599622037637</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
         <v>1</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AK2" t="n">
         <v>65.82684175587579</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
         <v>1380854.848773294</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>69.87069622440197</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -789,109 +789,109 @@
           <t>K2dlua5N</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>26.95885167464115</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>179.0301435406699</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>69.63492822966506</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>2676007.177033493</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>72.02009569377991</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>25.93208556149733</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>177.3411764705882</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>1</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>69.36524064171122</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2753796.79144385</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>72.05508021390375</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>26.63839937839741</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>179.7619704214555</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>1</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>66.48620923208608</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>1381388.993746634</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>68.83103282962972</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>25.08054605241306</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>177.6831256481512</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>65.12557978395574</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>1115519.369803257</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>69.19613369722066</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -928,109 +928,109 @@
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>26.40199615199615</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>180.6973063973064</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1.224627224627225</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>68.50430495430496</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1972597.162097162</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>72.43109668109666</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>25.82409090909091</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>182.5536363636364</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>1.056818181818182</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>67.10454545454546</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>2458015.909090909</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>71.08318181818181</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>24.20689286441455</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>178.9530987772897</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>1.083752662366396</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>63.45343306262389</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>1472985.778357401</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>69.33963019803836</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>24.84932727646115</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>179.7948985892064</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>1.033645254440449</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>63.07001072821153</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AL4" t="n">
         <v>1346162.906344228</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>68.92713374392579</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM15"/>
+  <dimension ref="A1:AO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,140 +485,150 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -627,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20371</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -672,129 +682,135 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>25.54835858585859</v>
-      </c>
-      <c r="O2" t="n">
-        <v>180.0435606060606</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
       </c>
       <c r="P2" t="n">
+        <v>22.70756172839506</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>181.4712962962963</v>
+      </c>
+      <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>67.94880050505051</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3189988.952020202</v>
-      </c>
       <c r="S2" t="n">
-        <v>72.10296717171718</v>
+        <v>66.45895061728395</v>
       </c>
       <c r="T2" t="n">
-        <v>27.77359307359307</v>
+        <v>1813499.228395062</v>
       </c>
       <c r="U2" t="n">
-        <v>179.8160173160173</v>
+        <v>72.7486111111111</v>
       </c>
       <c r="V2" t="n">
-        <v>1.064502164502164</v>
+        <v>26.89186602870813</v>
       </c>
       <c r="W2" t="n">
-        <v>67.31212121212123</v>
+        <v>179.8052631578947</v>
       </c>
       <c r="X2" t="n">
-        <v>1339160.173160173</v>
+        <v>1.212918660287081</v>
       </c>
       <c r="Y2" t="n">
-        <v>69.65844155844155</v>
+        <v>69.67703349282297</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.47435026876363</v>
+        <v>2881921.052631579</v>
       </c>
       <c r="AA2" t="n">
-        <v>181.8608002897305</v>
+        <v>72.46124401913876</v>
       </c>
       <c r="AB2" t="n">
+        <v>21.33862145106584</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>180.7355522229257</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" t="n">
-        <v>64.129170057351</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1414767.718228596</v>
-      </c>
       <c r="AE2" t="n">
-        <v>70.10290419033225</v>
+        <v>62.37328628882931</v>
       </c>
       <c r="AF2" t="n">
-        <v>24.78553515125857</v>
+        <v>1339327.1508156</v>
       </c>
       <c r="AG2" t="n">
-        <v>179.7982529436895</v>
+        <v>71.70821809300291</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.055406191462092</v>
+        <v>25.4028233781916</v>
       </c>
       <c r="AI2" t="n">
-        <v>62.60389813896573</v>
+        <v>179.6647357726663</v>
       </c>
       <c r="AJ2" t="n">
-        <v>929580.1522541385</v>
+        <v>1.180220757568244</v>
       </c>
       <c r="AK2" t="n">
-        <v>67.40614524070497</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>6gpXy3v</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>rXawJi8</t>
+        <v>64.74244749692036</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2519486.735000351</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>69.57545930185621</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>71000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -809,127 +825,137 @@
       <c r="K3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>26.89409888357256</v>
-      </c>
-      <c r="O3" t="n">
-        <v>183.723870281765</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
       </c>
       <c r="P3" t="n">
-        <v>1.088835725677831</v>
+        <v>25.89647727272727</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.09154704944177</v>
+        <v>179.1068181818182</v>
       </c>
       <c r="R3" t="n">
-        <v>1376433.280170122</v>
+        <v>1.201363636363637</v>
       </c>
       <c r="S3" t="n">
-        <v>70.26156299840511</v>
+        <v>67.49147727272728</v>
       </c>
       <c r="T3" t="n">
-        <v>26.43588516746411</v>
+        <v>4434977.840909091</v>
       </c>
       <c r="U3" t="n">
-        <v>180.3952153110048</v>
+        <v>72.25727272727272</v>
       </c>
       <c r="V3" t="n">
-        <v>1.087081339712919</v>
+        <v>26.425</v>
       </c>
       <c r="W3" t="n">
-        <v>67.09952153110048</v>
+        <v>182.2868181818182</v>
       </c>
       <c r="X3" t="n">
-        <v>1566511.961722488</v>
+        <v>1.220454545454545</v>
       </c>
       <c r="Y3" t="n">
-        <v>70.61578947368423</v>
+        <v>65.07272727272728</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.68097217901683</v>
+        <v>2271395.454545455</v>
       </c>
       <c r="AA3" t="n">
-        <v>182.1059435958552</v>
+        <v>68.26909090909092</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.008790034942878</v>
+        <v>25.51050482665396</v>
       </c>
       <c r="AC3" t="n">
-        <v>61.00065291876844</v>
+        <v>179.0364819291681</v>
       </c>
       <c r="AD3" t="n">
-        <v>826052.7860896731</v>
+        <v>1.024381868131868</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.89340967227149</v>
+        <v>65.66969962485989</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.51323432573406</v>
+        <v>1899414.899877235</v>
       </c>
       <c r="AG3" t="n">
-        <v>179.8456790698987</v>
+        <v>70.52817513958237</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.07298542605448</v>
+        <v>23.16101952839939</v>
       </c>
       <c r="AI3" t="n">
-        <v>63.43091446593441</v>
+        <v>179.2031057469101</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1137761.141418114</v>
+        <v>1.11159692710036</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.09789395193572</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>nJ01AhX</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>tOpyQa2</t>
+        <v>62.87248876473134</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1383559.026271212</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>68.97655205206692</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -946,125 +972,139 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>25.55808080808081</v>
-      </c>
-      <c r="O4" t="n">
-        <v>179.3712121212121</v>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>24.06698564593302</v>
       </c>
       <c r="Q4" t="n">
-        <v>69.31767676767677</v>
+        <v>178.9090909090909</v>
       </c>
       <c r="R4" t="n">
-        <v>3852702.020202021</v>
+        <v>1.019138755980861</v>
       </c>
       <c r="S4" t="n">
-        <v>72.91313131313132</v>
+        <v>66.25358851674642</v>
       </c>
       <c r="T4" t="n">
-        <v>26.35025252525253</v>
+        <v>1378588.516746412</v>
       </c>
       <c r="U4" t="n">
-        <v>181.2712121212121</v>
+        <v>71.36363636363637</v>
       </c>
       <c r="V4" t="n">
-        <v>1.109217171717172</v>
+        <v>25.40622009569378</v>
       </c>
       <c r="W4" t="n">
-        <v>69.27885101010101</v>
+        <v>183.5263157894737</v>
       </c>
       <c r="X4" t="n">
-        <v>3340707.070707071</v>
+        <v>1.063157894736842</v>
       </c>
       <c r="Y4" t="n">
-        <v>72.33377525252526</v>
+        <v>69.16889952153109</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.4862842403679</v>
+        <v>2937741.626794258</v>
       </c>
       <c r="AA4" t="n">
-        <v>181.1186014642318</v>
+        <v>73.311004784689</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>23.62045454545455</v>
       </c>
       <c r="AC4" t="n">
-        <v>62.05174523407126</v>
+        <v>179.9254679761605</v>
       </c>
       <c r="AD4" t="n">
-        <v>1557474.408127095</v>
+        <v>1.132833878955763</v>
       </c>
       <c r="AE4" t="n">
-        <v>67.21080752285658</v>
+        <v>65.28085674713097</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.63720537261801</v>
+        <v>1376671.126080752</v>
       </c>
       <c r="AG4" t="n">
-        <v>179.3690997472707</v>
+        <v>71.44923672818409</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.067161641140937</v>
+        <v>25.01144790655545</v>
       </c>
       <c r="AI4" t="n">
-        <v>65.87091202329447</v>
+        <v>181.9234766374248</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1256095.052245763</v>
+        <v>1.110092828658496</v>
       </c>
       <c r="AK4" t="n">
-        <v>71.01413891298759</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>roEEsq7</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
+        <v>65.25948422809063</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1616553.711846108</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>70.49225173080681</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25000</v>
+        <v>68756</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1079,127 +1119,137 @@
       <c r="K5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>23.37799043062201</v>
-      </c>
-      <c r="O5" t="n">
-        <v>180.0622009569378</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
       </c>
       <c r="P5" t="n">
-        <v>1.124401913875598</v>
+        <v>26.37540106951872</v>
       </c>
       <c r="Q5" t="n">
-        <v>68.34928229665071</v>
+        <v>181.2160427807487</v>
       </c>
       <c r="R5" t="n">
-        <v>2960382.775119618</v>
+        <v>1.109328579916815</v>
       </c>
       <c r="S5" t="n">
-        <v>74.28229665071771</v>
+        <v>69.24284016636958</v>
       </c>
       <c r="T5" t="n">
-        <v>26.42631578947368</v>
+        <v>3323770.053475935</v>
       </c>
       <c r="U5" t="n">
-        <v>182.222966507177</v>
+        <v>72.28799762329174</v>
       </c>
       <c r="V5" t="n">
-        <v>1.211004784688995</v>
+        <v>25.59835858585858</v>
       </c>
       <c r="W5" t="n">
-        <v>65.07655502392345</v>
+        <v>180.1503787878788</v>
       </c>
       <c r="X5" t="n">
-        <v>2224100.4784689</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>68.28851674641149</v>
+        <v>67.96584595959597</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.83886346431271</v>
+        <v>3187346.906565657</v>
       </c>
       <c r="AA5" t="n">
-        <v>180.480671143442</v>
+        <v>72.07796717171718</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.060074020593606</v>
+        <v>25.6781540761895</v>
       </c>
       <c r="AC5" t="n">
-        <v>63.95358070516403</v>
+        <v>179.5513095660587</v>
       </c>
       <c r="AD5" t="n">
-        <v>1829982.318211992</v>
+        <v>1.078897230877744</v>
       </c>
       <c r="AE5" t="n">
-        <v>72.02278760298346</v>
+        <v>65.98438778663009</v>
       </c>
       <c r="AF5" t="n">
-        <v>23.18057457283039</v>
+        <v>1319658.088388169</v>
       </c>
       <c r="AG5" t="n">
-        <v>179.1445434455009</v>
+        <v>71.12311113379225</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.109160200271846</v>
+        <v>24.34399312590649</v>
       </c>
       <c r="AI5" t="n">
-        <v>62.8740878963931</v>
+        <v>181.7322288611591</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1375297.589980777</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>68.93099661990425</v>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>K4FYmLD</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>EgT3xN3</t>
+        <v>64.179170057351</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1513874.861085739</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>70.29873752366558</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1216,129 +1266,131 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>26.91919191919192</v>
-      </c>
-      <c r="O6" t="n">
-        <v>179.8</v>
-      </c>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.208080808080808</v>
+        <v>23.34090909090909</v>
       </c>
       <c r="Q6" t="n">
-        <v>69.73686868686869</v>
+        <v>180.0681818181818</v>
       </c>
       <c r="R6" t="n">
-        <v>2875444.444444444</v>
+        <v>1.118181818181818</v>
       </c>
       <c r="S6" t="n">
-        <v>72.4979797979798</v>
+        <v>68.23636363636363</v>
       </c>
       <c r="T6" t="n">
-        <v>26.23181818181818</v>
+        <v>2897590.909090909</v>
       </c>
       <c r="U6" t="n">
-        <v>182.1636363636364</v>
+        <v>74.25454545454546</v>
       </c>
       <c r="V6" t="n">
-        <v>1.123232323232323</v>
+        <v>26.82939393939393</v>
       </c>
       <c r="W6" t="n">
-        <v>68.38636363636364</v>
+        <v>183.7876767676768</v>
       </c>
       <c r="X6" t="n">
-        <v>2481805.555555556</v>
+        <v>1.089393939393939</v>
       </c>
       <c r="Y6" t="n">
-        <v>71.44090909090909</v>
+        <v>67.0169696969697</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.4611501671761</v>
+        <v>1375811.616161616</v>
       </c>
       <c r="AA6" t="n">
-        <v>179.5872864528471</v>
+        <v>70.27348484848486</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.180429100308963</v>
+        <v>22.82692029109707</v>
       </c>
       <c r="AC6" t="n">
-        <v>64.88173379576888</v>
+        <v>180.4216375862699</v>
       </c>
       <c r="AD6" t="n">
-        <v>2522301.357533051</v>
+        <v>1.057070319563925</v>
       </c>
       <c r="AE6" t="n">
-        <v>69.63357305392012</v>
+        <v>63.87340166990582</v>
       </c>
       <c r="AF6" t="n">
-        <v>26.23425069925496</v>
+        <v>1796558.202301393</v>
       </c>
       <c r="AG6" t="n">
-        <v>180.8025647490002</v>
+        <v>71.95414822283428</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.143240162043444</v>
+        <v>22.7830346811771</v>
       </c>
       <c r="AI6" t="n">
-        <v>65.92626762643279</v>
+        <v>182.0728686382847</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1487202.076098336</v>
+        <v>1.008350533195734</v>
       </c>
       <c r="AK6" t="n">
-        <v>69.40392618692916</v>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>022mBmS</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Uw6sTk0</t>
+        <v>61.10062027283003</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>831847.3690074116</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>70.85985029976902</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18500</v>
+        <v>20500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1355,129 +1407,139 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>25.45656565656565</v>
-      </c>
-      <c r="O7" t="n">
-        <v>183.5111111111111</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
       </c>
       <c r="P7" t="n">
-        <v>1.066666666666667</v>
+        <v>25.8064935064935</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.23383838383837</v>
+        <v>182.4709956709957</v>
       </c>
       <c r="R7" t="n">
-        <v>2962782.828282828</v>
+        <v>1.054112554112554</v>
       </c>
       <c r="S7" t="n">
-        <v>73.33939393939393</v>
+        <v>67.12987012987014</v>
       </c>
       <c r="T7" t="n">
-        <v>26.1311004784689</v>
+        <v>2463803.03030303</v>
       </c>
       <c r="U7" t="n">
-        <v>182.3425837320574</v>
+        <v>71.09220779220779</v>
       </c>
       <c r="V7" t="n">
-        <v>1.019138755980861</v>
+        <v>25.5</v>
       </c>
       <c r="W7" t="n">
-        <v>66.58277511961722</v>
+        <v>179.3755980861244</v>
       </c>
       <c r="X7" t="n">
-        <v>1632133.971291865</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.28516746411482</v>
+        <v>69.25311004784689</v>
       </c>
       <c r="Z7" t="n">
-        <v>25.1544450124752</v>
+        <v>3836387.559808613</v>
       </c>
       <c r="AA7" t="n">
-        <v>181.9643642283929</v>
+        <v>72.93205741626794</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.116209096917301</v>
+        <v>24.85650216805823</v>
       </c>
       <c r="AC7" t="n">
-        <v>65.34681668520678</v>
+        <v>179.9534748468632</v>
       </c>
       <c r="AD7" t="n">
-        <v>1606587.945837559</v>
+        <v>1.032043099467094</v>
       </c>
       <c r="AE7" t="n">
-        <v>70.45709904918496</v>
+        <v>63.0012006935348</v>
       </c>
       <c r="AF7" t="n">
-        <v>26.26519287348806</v>
+        <v>1328652.172708788</v>
       </c>
       <c r="AG7" t="n">
-        <v>181.6026296559814</v>
+        <v>68.9038178513579</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.099131807566658</v>
+        <v>24.54840963122573</v>
       </c>
       <c r="AI7" t="n">
-        <v>65.25069421742762</v>
+        <v>181.162797878395</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1561535.408347168</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>69.87362783023201</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>roEEsq7</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>K4zRMgT</t>
+        <v>62.1367410989447</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1560831.018225669</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>67.21725624972379</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">da silva a 
+  usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19400</v>
+        <v>22039</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1494,110 +1556,120 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>26.15151515151515</v>
-      </c>
-      <c r="O8" t="n">
-        <v>181.0252525252525</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>26.49136363636363</v>
       </c>
       <c r="Q8" t="n">
-        <v>65.8989898989899</v>
+        <v>180.4754545454545</v>
       </c>
       <c r="R8" t="n">
-        <v>1264545.454545454</v>
+        <v>1.091818181818182</v>
       </c>
       <c r="S8" t="n">
-        <v>70.09595959595961</v>
+        <v>67.15363636363637</v>
       </c>
       <c r="T8" t="n">
-        <v>28.23636363636364</v>
+        <v>1582981.818181818</v>
       </c>
       <c r="U8" t="n">
-        <v>179.7775119617225</v>
+        <v>70.63045454545454</v>
       </c>
       <c r="V8" t="n">
-        <v>1.100956937799043</v>
+        <v>26.10954545454546</v>
       </c>
       <c r="W8" t="n">
-        <v>67.49712918660288</v>
+        <v>182.2554545454545</v>
       </c>
       <c r="X8" t="n">
-        <v>2019736.842105263</v>
+        <v>1.018181818181818</v>
       </c>
       <c r="Y8" t="n">
-        <v>68.62344497607656</v>
+        <v>66.59863636363636</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.64087787054034</v>
+        <v>1649902.272727272</v>
       </c>
       <c r="AA8" t="n">
-        <v>180.3467339614365</v>
+        <v>71.31090909090908</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.006944444444444</v>
+        <v>25.47090594278069</v>
       </c>
       <c r="AC8" t="n">
-        <v>63.82916090781269</v>
+        <v>179.7346451164038</v>
       </c>
       <c r="AD8" t="n">
-        <v>1276583.112932989</v>
+        <v>1.073502821418422</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.63416630266364</v>
+        <v>63.40936874263768</v>
       </c>
       <c r="AF8" t="n">
-        <v>28.23349047395264</v>
+        <v>1137883.501013875</v>
       </c>
       <c r="AG8" t="n">
-        <v>181.1347096428198</v>
+        <v>68.11799925433893</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.312989938839561</v>
+        <v>26.20193322981367</v>
       </c>
       <c r="AI8" t="n">
-        <v>65.40000448692062</v>
+        <v>181.7342628790647</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1247320.658225352</v>
+        <v>1.094175217188325</v>
       </c>
       <c r="AK8" t="n">
-        <v>67.22094125839344</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>WWvwigh</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>UL7r7du</t>
+        <v>65.28227715361507</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1587179.226165103</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>69.95347585048512</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1616,7 +1688,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1633,125 +1705,139 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>27.52020202020202</v>
-      </c>
-      <c r="O9" t="n">
-        <v>183.5656565656566</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
       </c>
       <c r="P9" t="n">
-        <v>1.121212121212122</v>
+        <v>27.54545454545455</v>
       </c>
       <c r="Q9" t="n">
-        <v>68.26262626262627</v>
+        <v>183.6315789473684</v>
       </c>
       <c r="R9" t="n">
-        <v>2784722.222222222</v>
+        <v>1.124401913875598</v>
       </c>
       <c r="S9" t="n">
-        <v>70.07070707070707</v>
+        <v>68.30622009569379</v>
       </c>
       <c r="T9" t="n">
-        <v>22.70756172839506</v>
+        <v>2811124.401913876</v>
       </c>
       <c r="U9" t="n">
-        <v>181.4712962962963</v>
+        <v>70.11483253588517</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>27.11052631578947</v>
       </c>
       <c r="W9" t="n">
-        <v>66.45895061728395</v>
+        <v>182.556937799043</v>
       </c>
       <c r="X9" t="n">
-        <v>1813499.228395062</v>
+        <v>1.735406698564594</v>
       </c>
       <c r="Y9" t="n">
-        <v>72.7486111111111</v>
+        <v>73.2732057416268</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.73626624985321</v>
+        <v>6358552.631578947</v>
       </c>
       <c r="AA9" t="n">
-        <v>182.9115001343262</v>
+        <v>77.2818181818182</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.050958602589037</v>
+        <v>27.65861379276711</v>
       </c>
       <c r="AC9" t="n">
-        <v>65.84022378587595</v>
+        <v>182.8292015002542</v>
       </c>
       <c r="AD9" t="n">
-        <v>1305381.228071445</v>
+        <v>1.050564900393276</v>
       </c>
       <c r="AE9" t="n">
-        <v>67.02616304790217</v>
+        <v>65.67243168730583</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.34733274380182</v>
+        <v>1315487.021559676</v>
       </c>
       <c r="AG9" t="n">
-        <v>180.7334869423811</v>
+        <v>66.92181121700571</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>24.46721228944982</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.39654966851175</v>
+        <v>184.6655240479353</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1346410.982426568</v>
+        <v>1.265501602951745</v>
       </c>
       <c r="AK9" t="n">
-        <v>71.71978576483642</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>xA45kov</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
+        <v>67.8690851989542</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3056734.4183085</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>73.90457911237759</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
+          <t xml:space="preserve">fischer d 
   can </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22423</v>
+        <v>18500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1768,101 +1854,115 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>25.38434343434343</v>
-      </c>
-      <c r="O10" t="n">
-        <v>182.2782828282828</v>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
       </c>
       <c r="P10" t="n">
-        <v>1.185858585858586</v>
+        <v>27.61570247933884</v>
       </c>
       <c r="Q10" t="n">
-        <v>67.63181818181818</v>
+        <v>179.8289256198347</v>
       </c>
       <c r="R10" t="n">
-        <v>2058573.232323232</v>
+        <v>1.061570247933884</v>
       </c>
       <c r="S10" t="n">
-        <v>71.32373737373739</v>
+        <v>67.09793388429753</v>
       </c>
       <c r="T10" t="n">
-        <v>25.98329545454545</v>
+        <v>1318721.074380165</v>
       </c>
       <c r="U10" t="n">
-        <v>179.05</v>
+        <v>69.58305785123967</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>28.26454545454545</v>
       </c>
       <c r="W10" t="n">
-        <v>67.77829545454544</v>
+        <v>179.8336363636363</v>
       </c>
       <c r="X10" t="n">
-        <v>4713993.75</v>
+        <v>1.105909090909091</v>
       </c>
       <c r="Y10" t="n">
-        <v>72.37818181818182</v>
+        <v>67.45227272727273</v>
       </c>
       <c r="Z10" t="n">
-        <v>24.00811574439081</v>
+        <v>1968375</v>
       </c>
       <c r="AA10" t="n">
-        <v>181.8799792072019</v>
+        <v>68.56727272727274</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>24.85852466019346</v>
       </c>
       <c r="AC10" t="n">
-        <v>65.18071489249532</v>
+        <v>179.9339054778697</v>
       </c>
       <c r="AD10" t="n">
-        <v>1409257.498519926</v>
+        <v>1.052887728213815</v>
       </c>
       <c r="AE10" t="n">
-        <v>70.09860154214317</v>
+        <v>62.59423478482302</v>
       </c>
       <c r="AF10" t="n">
-        <v>25.35121911236824</v>
+        <v>919707.9318947606</v>
       </c>
       <c r="AG10" t="n">
-        <v>178.8445771672633</v>
+        <v>67.37780267047532</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.024381868131868</v>
+        <v>28.16244095025501</v>
       </c>
       <c r="AI10" t="n">
-        <v>65.53279486295513</v>
+        <v>181.1310991606788</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1891623.233210568</v>
+        <v>1.297340441897583</v>
       </c>
       <c r="AK10" t="n">
-        <v>70.49293704434429</v>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>l6eEjGl</t>
+        <v>65.1956292625746</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1212345.250314084</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>67.10364419547378</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,21 +1972,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18061</v>
+        <v>22000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1903,129 +2003,135 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>24.07426900584795</v>
-      </c>
-      <c r="O11" t="n">
-        <v>180.33216374269</v>
-      </c>
       <c r="P11" t="n">
+        <v>27.75185185185185</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>180.9198653198653</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.354641654641655</v>
+      </c>
+      <c r="S11" t="n">
+        <v>72.37873977873977</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4259753.487253487</v>
+      </c>
+      <c r="U11" t="n">
+        <v>75.09918229918227</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.11555555555555</v>
+      </c>
+      <c r="W11" t="n">
+        <v>180.3355555555555</v>
+      </c>
+      <c r="X11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>65.80409356725147</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1743210.526315789</v>
-      </c>
-      <c r="S11" t="n">
-        <v>70.94269005847954</v>
-      </c>
-      <c r="T11" t="n">
-        <v>24.15656565656566</v>
-      </c>
-      <c r="U11" t="n">
-        <v>178.9494949494949</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02020202020202</v>
-      </c>
-      <c r="W11" t="n">
-        <v>66.3080808080808</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1379040.404040404</v>
-      </c>
       <c r="Y11" t="n">
-        <v>71.32828282828282</v>
+        <v>65.84888888888888</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.04016506444155</v>
+        <v>1745325</v>
       </c>
       <c r="AA11" t="n">
-        <v>178.9118479066588</v>
+        <v>70.91555555555556</v>
       </c>
       <c r="AB11" t="n">
+        <v>25.01852037054814</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>179.0798981154571</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.00604686318972</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>66.48815535791697</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1646977.201267825</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>72.56578147846416</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22.04053776360042</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>178.9186364637068</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1</v>
       </c>
-      <c r="AC11" t="n">
-        <v>60.82046514604733</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>821353.0726949425</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>69.71017763887599</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>23.60189393939394</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>179.9364788233209</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.132637781321992</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>65.22575282904229</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1359213.461368066</v>
-      </c>
       <c r="AK11" t="n">
-        <v>71.42873977873978</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>z9ZXDy6</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>rJ9D8rz</t>
+        <v>60.81991807922115</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>820690.1809649572</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>69.6889544712179</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20213</v>
+        <v>25218</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2042,125 +2148,139 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>24.37977139819245</v>
-      </c>
-      <c r="O12" t="n">
-        <v>179.0470228601807</v>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
       </c>
       <c r="P12" t="n">
+        <v>26.93818181818182</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>179.0059090909091</v>
+      </c>
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>65.42476076555025</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1464096.291866029</v>
-      </c>
       <c r="S12" t="n">
-        <v>72.02190324295587</v>
+        <v>69.63499999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>26.90526315789474</v>
+        <v>2691184.090909091</v>
       </c>
       <c r="U12" t="n">
-        <v>178.7964912280702</v>
+        <v>72.03727272727272</v>
       </c>
       <c r="V12" t="n">
-        <v>1.063742690058479</v>
+        <v>26.1866028708134</v>
       </c>
       <c r="W12" t="n">
-        <v>70.90818713450292</v>
+        <v>181.0334928229665</v>
       </c>
       <c r="X12" t="n">
-        <v>3819137.426900585</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>74.09181286549708</v>
+        <v>65.93301435406698</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.90852065298022</v>
+        <v>1259330.14354067</v>
       </c>
       <c r="AA12" t="n">
-        <v>178.4636804914316</v>
+        <v>70.09090909090911</v>
       </c>
       <c r="AB12" t="n">
+        <v>26.59995767034711</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>179.7369153786437</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1</v>
       </c>
-      <c r="AC12" t="n">
-        <v>63.74772666531757</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1248134.223592731</v>
-      </c>
       <c r="AE12" t="n">
-        <v>70.4486457060284</v>
+        <v>66.53363790091655</v>
       </c>
       <c r="AF12" t="n">
-        <v>24.18773882424768</v>
+        <v>1419558.674494085</v>
       </c>
       <c r="AG12" t="n">
-        <v>177.5440907818899</v>
+        <v>68.90469857945259</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.024729849987287</v>
+        <v>24.62150152328702</v>
       </c>
       <c r="AI12" t="n">
-        <v>64.77595783883793</v>
+        <v>180.0844656668154</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1618601.113556912</v>
+        <v>1.006578947368421</v>
       </c>
       <c r="AK12" t="n">
-        <v>70.27196218720481</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>jBBpU7Y</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>dp6AQn9</t>
+        <v>63.93384621888476</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1278652.901247521</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>69.79217668864784</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2175,123 +2295,133 @@
       <c r="K13" t="n">
         <v>2024</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>27.67126262626262</v>
-      </c>
-      <c r="O13" t="n">
-        <v>180.8522222222222</v>
-      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.354191919191919</v>
+        <v>26.92077922077922</v>
       </c>
       <c r="Q13" t="n">
-        <v>72.36585858585859</v>
+        <v>180.5926406926407</v>
       </c>
       <c r="R13" t="n">
-        <v>4275127.525252526</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>75.14505050505049</v>
+        <v>69.14242424242424</v>
       </c>
       <c r="T13" t="n">
-        <v>26.98681818181818</v>
+        <v>2297474.025974026</v>
       </c>
       <c r="U13" t="n">
-        <v>180.6822727272727</v>
+        <v>72.13376623376624</v>
       </c>
       <c r="V13" t="n">
+        <v>26.925</v>
+      </c>
+      <c r="W13" t="n">
+        <v>178.7866666666667</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.065555555555556</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>70.88277777777778</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3757430.555555555</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>74.03222222222223</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.78071073447061</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>181.1364719400924</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1</v>
       </c>
-      <c r="W13" t="n">
-        <v>69.18454545454544</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2278597.727272728</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>72.10545454545453</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>25.15640291081468</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>179.2186756299256</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.006349206349206</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>66.52125877798672</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1634108.670026869</v>
-      </c>
       <c r="AE13" t="n">
-        <v>72.52667924803954</v>
+        <v>65.82318262464359</v>
       </c>
       <c r="AF13" t="n">
-        <v>25.76766293786081</v>
+        <v>1376697.078196788</v>
       </c>
       <c r="AG13" t="n">
-        <v>181.0599622037637</v>
+        <v>69.87288529308125</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>24.1158518830353</v>
       </c>
       <c r="AI13" t="n">
-        <v>65.82684175587579</v>
+        <v>177.7218862427954</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1380854.848773294</v>
+        <v>1.025993357487923</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.87069622440197</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
+        <v>64.74215994689602</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1610921.057879067</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>70.37586407784457</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25218</v>
+        <v>72000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2308,129 +2438,139 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>26.95885167464115</v>
-      </c>
-      <c r="O14" t="n">
-        <v>179.0301435406699</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>26.44570707070708</v>
       </c>
       <c r="Q14" t="n">
-        <v>69.63492822966506</v>
+        <v>180.7110651974289</v>
       </c>
       <c r="R14" t="n">
-        <v>2676007.177033493</v>
+        <v>1.222681359044995</v>
       </c>
       <c r="S14" t="n">
-        <v>72.02009569377991</v>
+        <v>68.58055555555555</v>
       </c>
       <c r="T14" t="n">
-        <v>25.93208556149733</v>
+        <v>1979111.340679523</v>
       </c>
       <c r="U14" t="n">
-        <v>177.3411764705882</v>
+        <v>72.44042699724518</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>26.15741626794258</v>
       </c>
       <c r="W14" t="n">
-        <v>69.36524064171122</v>
+        <v>182.1358851674641</v>
       </c>
       <c r="X14" t="n">
-        <v>2753796.79144385</v>
+        <v>1.121531100478469</v>
       </c>
       <c r="Y14" t="n">
-        <v>72.05508021390375</v>
+        <v>68.30382775119617</v>
       </c>
       <c r="Z14" t="n">
-        <v>26.63839937839741</v>
+        <v>2471279.90430622</v>
       </c>
       <c r="AA14" t="n">
-        <v>179.7619704214555</v>
+        <v>71.43205741626795</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>24.18946725293046</v>
       </c>
       <c r="AC14" t="n">
-        <v>66.48620923208608</v>
+        <v>178.8750167473059</v>
       </c>
       <c r="AD14" t="n">
-        <v>1381388.993746634</v>
+        <v>1.087967113542255</v>
       </c>
       <c r="AE14" t="n">
-        <v>68.83103282962972</v>
+        <v>63.4354962656597</v>
       </c>
       <c r="AF14" t="n">
-        <v>25.08054605241306</v>
+        <v>1460938.296453455</v>
       </c>
       <c r="AG14" t="n">
-        <v>177.6831256481512</v>
+        <v>69.38301599117567</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>26.22981645192576</v>
       </c>
       <c r="AI14" t="n">
-        <v>65.12557978395574</v>
+        <v>180.876113972737</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1115519.369803257</v>
+        <v>1.135701206146421</v>
       </c>
       <c r="AK14" t="n">
-        <v>69.19613369722066</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
+        <v>65.90646406714687</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1490099.335251055</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>69.39582480866973</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72000</v>
+        <v>54405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2447,94 +2587,104 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>26.40199615199615</v>
-      </c>
-      <c r="O15" t="n">
-        <v>180.6973063973064</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
       </c>
       <c r="P15" t="n">
-        <v>1.224627224627225</v>
+        <v>25.87020202020202</v>
       </c>
       <c r="Q15" t="n">
-        <v>68.50430495430496</v>
+        <v>177.3727272727273</v>
       </c>
       <c r="R15" t="n">
-        <v>1972597.162097162</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>72.43109668109666</v>
+        <v>69.30454545454546</v>
       </c>
       <c r="T15" t="n">
-        <v>25.82409090909091</v>
+        <v>2735025.252525253</v>
       </c>
       <c r="U15" t="n">
-        <v>182.5536363636364</v>
+        <v>72.06717171717172</v>
       </c>
       <c r="V15" t="n">
-        <v>1.056818181818182</v>
+        <v>25.37581073896863</v>
       </c>
       <c r="W15" t="n">
-        <v>67.10454545454546</v>
+        <v>182.3864433811802</v>
       </c>
       <c r="X15" t="n">
-        <v>2458015.909090909</v>
+        <v>1.187772461456672</v>
       </c>
       <c r="Y15" t="n">
-        <v>71.08318181818181</v>
+        <v>67.65119617224882</v>
       </c>
       <c r="Z15" t="n">
-        <v>24.20689286441455</v>
+        <v>2085168.793195109</v>
       </c>
       <c r="AA15" t="n">
-        <v>178.9530987772897</v>
+        <v>71.35933014354067</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.083752662366396</v>
+        <v>25.16544325239978</v>
       </c>
       <c r="AC15" t="n">
-        <v>63.45343306262389</v>
+        <v>177.7562853343651</v>
       </c>
       <c r="AD15" t="n">
-        <v>1472985.778357401</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>69.33963019803836</v>
+        <v>65.19348235634467</v>
       </c>
       <c r="AF15" t="n">
-        <v>24.84932727646115</v>
+        <v>1111698.245393897</v>
       </c>
       <c r="AG15" t="n">
-        <v>179.7948985892064</v>
+        <v>69.18523738070839</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.033645254440449</v>
+        <v>23.9655833367913</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.07001072821153</v>
+        <v>181.7573487226124</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1346162.906344228</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>68.92713374392579</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
+        <v>64.9764667402587</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1383507.103860982</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70.02499093466196</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO15"/>
+  <dimension ref="A1:BC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -697,83 +767,125 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>22.70756172839506</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.4712962962963</v>
+        <v>185</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>66.45895061728395</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1813499.228395062</v>
+        <v>58</v>
       </c>
       <c r="U2" t="n">
-        <v>72.7486111111111</v>
+        <v>375000</v>
       </c>
       <c r="V2" t="n">
-        <v>26.89186602870813</v>
+        <v>65</v>
       </c>
       <c r="W2" t="n">
-        <v>179.8052631578947</v>
+        <v>24.2</v>
       </c>
       <c r="X2" t="n">
-        <v>1.212918660287081</v>
+        <v>185.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>69.67703349282297</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>2881921.052631579</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>72.46124401913876</v>
+        <v>317</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.33862145106584</v>
+        <v>4765000</v>
       </c>
       <c r="AC2" t="n">
-        <v>180.7355522229257</v>
+        <v>359</v>
       </c>
       <c r="AD2" t="n">
+        <v>23.10956790123457</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>182.6851851851852</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1</v>
       </c>
-      <c r="AE2" t="n">
-        <v>62.37328628882931</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1339327.1508156</v>
-      </c>
       <c r="AG2" t="n">
-        <v>71.70821809300291</v>
+        <v>65.90895061728396</v>
       </c>
       <c r="AH2" t="n">
-        <v>25.4028233781916</v>
+        <v>1543217.592592593</v>
       </c>
       <c r="AI2" t="n">
-        <v>179.6647357726663</v>
+        <v>71.75308641975309</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.180220757568244</v>
+        <v>26.67685950413223</v>
       </c>
       <c r="AK2" t="n">
-        <v>64.74244749692036</v>
+        <v>179.7090909090909</v>
       </c>
       <c r="AL2" t="n">
-        <v>2519486.735000351</v>
+        <v>1.231404958677686</v>
       </c>
       <c r="AM2" t="n">
-        <v>69.57545930185621</v>
-      </c>
-      <c r="AN2" t="inlineStr">
+        <v>69.71487603305785</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2958000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>72.6694214876033</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>21.55911397594195</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>181.0105813825426</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>62.53305314553531</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1357813.972576757</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>71.51192892717728</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>25.41277671573197</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>179.8521557905459</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.153747579936716</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>64.57245684702764</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2632059.859176381</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>69.42460886050812</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>EgT3xN3S</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>Uw6sTk0t</t>
         </is>
@@ -841,84 +953,98 @@
           <t>j9cigLCr</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>25.89647727272727</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>179.1068181818182</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.201363636363637</v>
-      </c>
-      <c r="S3" t="n">
-        <v>67.49147727272728</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4434977.840909091</v>
-      </c>
-      <c r="U3" t="n">
-        <v>72.25727272727272</v>
-      </c>
-      <c r="V3" t="n">
-        <v>26.425</v>
-      </c>
-      <c r="W3" t="n">
-        <v>182.2868181818182</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.220454545454545</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>65.07272727272728</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2271395.454545455</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>68.26909090909092</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>25.51050482665396</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>179.0364819291681</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1.024381868131868</v>
+        <v>25.90087412587413</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.66969962485989</v>
+        <v>179.4230769230769</v>
       </c>
       <c r="AF3" t="n">
-        <v>1899414.899877235</v>
+        <v>1.175524475524476</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.52817513958237</v>
+        <v>67.23374125874126</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.16101952839939</v>
+        <v>4023791.083916084</v>
       </c>
       <c r="AI3" t="n">
-        <v>179.2031057469101</v>
+        <v>72.07412587412588</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11159692710036</v>
+        <v>26.19421487603306</v>
       </c>
       <c r="AK3" t="n">
-        <v>62.87248876473134</v>
+        <v>182.4801652892562</v>
       </c>
       <c r="AL3" t="n">
-        <v>1383559.026271212</v>
+        <v>1.202479338842975</v>
       </c>
       <c r="AM3" t="n">
-        <v>68.97655205206692</v>
-      </c>
-      <c r="AN3" t="inlineStr">
+        <v>64.58677685950414</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2112826.446280992</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>67.92727272727274</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>25.75187049009323</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>179.8382584052673</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03751056635672</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>65.72562230722339</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2103155.305903589</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>70.48947342993273</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>23.2054606212501</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>178.6450216450216</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.146240601503759</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>62.98931419457734</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1573240.354674566</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>69.22209311156679</v>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>z9ZXDy6o</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>xA45kovo</t>
         </is>
@@ -990,84 +1116,98 @@
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>24.06698564593302</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>178.9090909090909</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.019138755980861</v>
-      </c>
-      <c r="S4" t="n">
-        <v>66.25358851674642</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1378588.516746412</v>
-      </c>
-      <c r="U4" t="n">
-        <v>71.36363636363637</v>
-      </c>
-      <c r="V4" t="n">
-        <v>25.40622009569378</v>
-      </c>
-      <c r="W4" t="n">
-        <v>183.5263157894737</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.063157894736842</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>69.16889952153109</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2937741.626794258</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>73.311004784689</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>23.62045454545455</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>179.9254679761605</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>1.132833878955763</v>
+        <v>23.63636363636364</v>
       </c>
       <c r="AE4" t="n">
-        <v>65.28085674713097</v>
+        <v>179.2809917355372</v>
       </c>
       <c r="AF4" t="n">
-        <v>1376671.126080752</v>
+        <v>1.016528925619835</v>
       </c>
       <c r="AG4" t="n">
-        <v>71.44923672818409</v>
+        <v>65.60330578512396</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.01144790655545</v>
+        <v>1267768.595041322</v>
       </c>
       <c r="AI4" t="n">
-        <v>181.9234766374248</v>
+        <v>71.36363636363636</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.110092828658496</v>
+        <v>25.70648148148148</v>
       </c>
       <c r="AK4" t="n">
-        <v>65.25948422809063</v>
+        <v>183.6495791245792</v>
       </c>
       <c r="AL4" t="n">
-        <v>1616553.711846108</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AM4" t="n">
-        <v>70.49225173080681</v>
-      </c>
-      <c r="AN4" t="inlineStr">
+        <v>69.34503367003367</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2970762.626262626</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>73.03569023569024</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>23.22591499409681</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>180.5855485821993</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.097405704343503</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>64.90665299612668</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1335678.698295325</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>71.5697855175128</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>24.50724933802394</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>181.1947520257802</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.070842992369361</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>65.2882518238185</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1590171.859358947</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>70.88647381326133</v>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>lAVQ9RGh</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>022mBmSn</t>
         </is>
@@ -1135,84 +1275,98 @@
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>26.37540106951872</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>181.2160427807487</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.109328579916815</v>
-      </c>
-      <c r="S5" t="n">
-        <v>69.24284016636958</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3323770.053475935</v>
-      </c>
-      <c r="U5" t="n">
-        <v>72.28799762329174</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25.59835858585858</v>
-      </c>
-      <c r="W5" t="n">
-        <v>180.1503787878788</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>26.48035914702582</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>181.016835016835</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.097194163860831</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>68.87205387205387</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3112985.409652076</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>71.81324354657689</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>25.26818181818182</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>180.4727272727273</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>67.96584595959597</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3187346.906565657</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>72.07796717171718</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>25.6781540761895</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>179.5513095660587</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.078897230877744</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>65.98438778663009</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1319658.088388169</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>71.12311113379225</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24.34399312590649</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>181.7322288611591</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AM5" t="n">
+        <v>68.3659090909091</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3131392.045454545</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>72.69204545454545</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>25.54344898928232</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>181.4421040923492</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.108652748848827</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>66.22410569640962</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1460147.323174284</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>71.87919589488217</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>24.33802787419315</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>180.9723922177567</v>
+      </c>
+      <c r="AX5" t="n">
         <v>1</v>
       </c>
-      <c r="AK5" t="n">
-        <v>64.179170057351</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1513874.861085739</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>70.29873752366558</v>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AY5" t="n">
+        <v>65.03660295639995</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1911195.794894045</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>70.87722833698697</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>roEEsq76</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>jBBpU7Y0</t>
         </is>
@@ -1276,84 +1430,98 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>23.34090909090909</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>180.0681818181818</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.118181818181818</v>
-      </c>
-      <c r="S6" t="n">
-        <v>68.23636363636363</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2897590.909090909</v>
-      </c>
-      <c r="U6" t="n">
-        <v>74.25454545454546</v>
-      </c>
-      <c r="V6" t="n">
-        <v>26.82939393939393</v>
-      </c>
-      <c r="W6" t="n">
-        <v>183.7876767676768</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.089393939393939</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>67.0169696969697</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1375811.616161616</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>70.27348484848486</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>22.82692029109707</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>180.4216375862699</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>1.057070319563925</v>
+        <v>22.99917355371901</v>
       </c>
       <c r="AE6" t="n">
-        <v>63.87340166990582</v>
+        <v>179.3239669421488</v>
       </c>
       <c r="AF6" t="n">
-        <v>1796558.202301393</v>
+        <v>1.109090909090909</v>
       </c>
       <c r="AG6" t="n">
-        <v>71.95414822283428</v>
+        <v>67.7809917355372</v>
       </c>
       <c r="AH6" t="n">
-        <v>22.7830346811771</v>
+        <v>2817396.694214876</v>
       </c>
       <c r="AI6" t="n">
-        <v>182.0728686382847</v>
+        <v>74.36446280991736</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.008350533195734</v>
+        <v>26.33553719008264</v>
       </c>
       <c r="AK6" t="n">
-        <v>61.10062027283003</v>
+        <v>184.5619834710744</v>
       </c>
       <c r="AL6" t="n">
-        <v>831847.3690074116</v>
+        <v>1.091735537190083</v>
       </c>
       <c r="AM6" t="n">
-        <v>70.85985029976902</v>
-      </c>
-      <c r="AN6" t="inlineStr">
+        <v>66.12892561983472</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1300818.181818182</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>70.36776859504131</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23.19050834657089</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>180.6628698318654</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.068762021517195</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>63.75365960184897</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1711832.381435119</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>71.82951192030477</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>23.20697987473951</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>182.4942501083368</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.014380648591175</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>61.80556105869925</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>885170.3845377502</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>71.00139593027292</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>rJ9D8rzj</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>86yPt28f</t>
         </is>
@@ -1425,84 +1593,98 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>25.8064935064935</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>182.4709956709957</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.054112554112554</v>
-      </c>
-      <c r="S7" t="n">
-        <v>67.12987012987014</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2463803.03030303</v>
-      </c>
-      <c r="U7" t="n">
-        <v>71.09220779220779</v>
-      </c>
-      <c r="V7" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>179.3755980861244</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>25.68461538461538</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>182.33006993007</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.066433566433566</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>67.62027972027971</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2691825.174825174</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>71.45594405594406</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25.00454545454546</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>179.5445454545455</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>69.25311004784689</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3836387.559808613</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>72.93205741626794</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>24.85650216805823</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>179.9534748468632</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.032043099467094</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>63.0012006935348</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1328652.172708788</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>68.9038178513579</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24.54840963122573</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>181.162797878395</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AM7" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3818140.909090909</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>73.45363636363636</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.84679767219813</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>180.243165739676</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.029688351313065</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>63.3128493169683</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1488422.15874324</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>69.28995175305243</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>24.61748508098892</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>181.3933716965047</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1</v>
       </c>
-      <c r="AK7" t="n">
-        <v>62.1367410989447</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1560831.018225669</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>67.21725624972379</v>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AY7" t="n">
+        <v>61.78537936913897</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1350476.417306053</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>67.04961423699915</v>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>GzULyFoh</t>
         </is>
@@ -1574,84 +1756,98 @@
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>26.49136363636363</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>180.4754545454545</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.091818181818182</v>
-      </c>
-      <c r="S8" t="n">
-        <v>67.15363636363637</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1582981.818181818</v>
-      </c>
-      <c r="U8" t="n">
-        <v>70.63045454545454</v>
-      </c>
-      <c r="V8" t="n">
-        <v>26.10954545454546</v>
-      </c>
-      <c r="W8" t="n">
-        <v>182.2554545454545</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.018181818181818</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>66.59863636363636</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1649902.272727272</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>71.31090909090908</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>25.47090594278069</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>179.7346451164038</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>1.073502821418422</v>
+        <v>26.79318181818182</v>
       </c>
       <c r="AE8" t="n">
-        <v>63.40936874263768</v>
+        <v>180.5780303030303</v>
       </c>
       <c r="AF8" t="n">
-        <v>1137883.501013875</v>
+        <v>1.153030303030303</v>
       </c>
       <c r="AG8" t="n">
-        <v>68.11799925433893</v>
+        <v>67.71363636363635</v>
       </c>
       <c r="AH8" t="n">
-        <v>26.20193322981367</v>
+        <v>1829492.424242425</v>
       </c>
       <c r="AI8" t="n">
-        <v>181.7342628790647</v>
+        <v>70.73939393939393</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.094175217188325</v>
+        <v>25.94462809917355</v>
       </c>
       <c r="AK8" t="n">
-        <v>65.28227715361507</v>
+        <v>182.3898071625344</v>
       </c>
       <c r="AL8" t="n">
-        <v>1587179.226165103</v>
+        <v>1.008264462809917</v>
       </c>
       <c r="AM8" t="n">
-        <v>69.95347585048512</v>
-      </c>
-      <c r="AN8" t="inlineStr">
+        <v>66.14003673094582</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1602788.337924701</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>71.02240587695132</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>25.67065089436371</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>179.8500226191302</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.093092937658155</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>64.27877445039915</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1270407.761691228</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>68.5116460315259</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>26.37666089851918</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>181.3269249021923</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.094407019005949</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>65.67699184356938</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1736085.048826693</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>70.1953940667176</v>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>nJ01AhXP</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>022mBmSn</t>
         </is>
@@ -1723,86 +1919,100 @@
           <t>rsHkUNCo</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>27.54545454545455</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>183.6315789473684</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.124401913875598</v>
-      </c>
-      <c r="S9" t="n">
-        <v>68.30622009569379</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2811124.401913876</v>
-      </c>
-      <c r="U9" t="n">
-        <v>70.11483253588517</v>
-      </c>
-      <c r="V9" t="n">
-        <v>27.11052631578947</v>
-      </c>
-      <c r="W9" t="n">
-        <v>182.556937799043</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.735406698564594</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>73.2732057416268</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6358552.631578947</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>77.2818181818182</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>27.65861379276711</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>182.8292015002542</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>1.050564900393276</v>
+        <v>27.80165289256198</v>
       </c>
       <c r="AE9" t="n">
-        <v>65.67243168730583</v>
+        <v>183.9173553719008</v>
       </c>
       <c r="AF9" t="n">
-        <v>1315487.021559676</v>
+        <v>1.165289256198347</v>
       </c>
       <c r="AG9" t="n">
-        <v>66.92181121700571</v>
+        <v>69.28925619834712</v>
       </c>
       <c r="AH9" t="n">
-        <v>24.46721228944982</v>
+        <v>3259090.909090909</v>
       </c>
       <c r="AI9" t="n">
-        <v>184.6655240479353</v>
+        <v>71.09917355371901</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.265501602951745</v>
+        <v>27.37</v>
       </c>
       <c r="AK9" t="n">
-        <v>67.8690851989542</v>
+        <v>182.0390909090909</v>
       </c>
       <c r="AL9" t="n">
-        <v>3056734.4183085</v>
+        <v>1.753636363636363</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.90457911237759</v>
-      </c>
-      <c r="AN9" t="inlineStr">
+        <v>73.84</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6696227.272727272</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>27.60005409610153</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>182.8966305433696</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.050919271769074</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>65.31591613261573</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1190932.419030245</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>66.50598150202893</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>24.19655674390969</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>184.2788071895425</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.13625</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>67.32904114676174</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2497732.36036839</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>73.68435308972074</v>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>EgT3xN3S</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>zoZ995a</t>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
         </is>
       </c>
     </row>
@@ -1872,84 +2082,98 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>27.61570247933884</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>179.8289256198347</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.061570247933884</v>
-      </c>
-      <c r="S10" t="n">
-        <v>67.09793388429753</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1318721.074380165</v>
-      </c>
-      <c r="U10" t="n">
-        <v>69.58305785123967</v>
-      </c>
-      <c r="V10" t="n">
-        <v>28.26454545454545</v>
-      </c>
-      <c r="W10" t="n">
-        <v>179.8336363636363</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.105909090909091</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>67.45227272727273</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1968375</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>68.56727272727274</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>24.85852466019346</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>179.9339054778697</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>1.052887728213815</v>
+        <v>26.98811188811189</v>
       </c>
       <c r="AE10" t="n">
-        <v>62.59423478482302</v>
+        <v>180.0566433566434</v>
       </c>
       <c r="AF10" t="n">
-        <v>919707.9318947606</v>
+        <v>1.05034965034965</v>
       </c>
       <c r="AG10" t="n">
-        <v>67.37780267047532</v>
+        <v>65.7888111888112</v>
       </c>
       <c r="AH10" t="n">
-        <v>28.16244095025501</v>
+        <v>1155258.741258741</v>
       </c>
       <c r="AI10" t="n">
-        <v>181.1310991606788</v>
+        <v>68.8944055944056</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.297340441897583</v>
+        <v>27.94454545454546</v>
       </c>
       <c r="AK10" t="n">
-        <v>65.1956292625746</v>
+        <v>179.7818181818182</v>
       </c>
       <c r="AL10" t="n">
-        <v>1212345.250314084</v>
+        <v>1.116363636363636</v>
       </c>
       <c r="AM10" t="n">
-        <v>67.10364419547378</v>
-      </c>
-      <c r="AN10" t="inlineStr">
+        <v>67.31272727272726</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2094977.272727273</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>68.51454545454547</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>25.36563837129055</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>180.2409542389977</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.062976057758667</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>63.37454822954823</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1002037.710357275</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>67.66753835536444</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>28.00286226809564</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>181.4884681626274</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.261435269760078</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>64.70308392197458</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1080869.150377542</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>66.83614490723826</v>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>zoZ995af</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>KtuTuMN0</t>
         </is>
@@ -2017,84 +2241,98 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>27.75185185185185</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>180.9198653198653</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.354641654641655</v>
-      </c>
-      <c r="S11" t="n">
-        <v>72.37873977873977</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4259753.487253487</v>
-      </c>
-      <c r="U11" t="n">
-        <v>75.09918229918227</v>
-      </c>
-      <c r="V11" t="n">
-        <v>24.11555555555555</v>
-      </c>
-      <c r="W11" t="n">
-        <v>180.3355555555555</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>27.55361952861953</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>180.596127946128</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.335774410774411</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>71.99309764309764</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4189000.420875421</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>74.8462962962963</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>24.10909090909091</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>180.2181818181818</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" t="n">
-        <v>65.84888888888888</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1745325</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>70.91555555555556</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>25.01852037054814</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>179.0798981154571</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.00604686318972</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>66.48815535791697</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1646977.201267825</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>72.56578147846416</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22.04053776360042</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>178.9186364637068</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AM11" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1664545.454545455</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>70.65454545454546</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>25.96729267464562</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>179.5308471620972</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01058201058201</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>67.10095466216789</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1779057.356212687</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>72.29551528944911</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>22.00460505677897</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>180.0500345065562</v>
+      </c>
+      <c r="AX11" t="n">
         <v>1</v>
       </c>
-      <c r="AK11" t="n">
-        <v>60.81991807922115</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>820690.1809649572</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>69.6889544712179</v>
-      </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AY11" t="n">
+        <v>60.12587991718426</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>771341.3325804631</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>69.14493381015122</v>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>K4FYmLD9</t>
         </is>
@@ -2166,84 +2404,98 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>26.93818181818182</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>179.0059090909091</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>26.60330578512396</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>178.595041322314</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>69.63499999999999</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2691184.090909091</v>
-      </c>
-      <c r="U12" t="n">
-        <v>72.03727272727272</v>
-      </c>
-      <c r="V12" t="n">
-        <v>26.1866028708134</v>
-      </c>
-      <c r="W12" t="n">
-        <v>181.0334928229665</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AG12" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2824834.710743802</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>72.3801652892562</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26.07438016528926</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>181.595041322314</v>
+      </c>
+      <c r="AL12" t="n">
         <v>1</v>
       </c>
-      <c r="Y12" t="n">
-        <v>65.93301435406698</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1259330.14354067</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>70.09090909090911</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>26.59995767034711</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>179.7369153786437</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AM12" t="n">
+        <v>65.57851239669422</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1191322.314049587</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>69.80165289256198</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>26.4414631668933</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>179.5150468715453</v>
+      </c>
+      <c r="AR12" t="n">
         <v>1</v>
       </c>
-      <c r="AE12" t="n">
-        <v>66.53363790091655</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1419558.674494085</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>68.90469857945259</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24.62150152328702</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>180.0844656668154</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.006578947368421</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>63.93384621888476</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1278652.901247521</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>69.79217668864784</v>
-      </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AS12" t="n">
+        <v>67.28170106586172</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1725852.07901582</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>69.64167702534361</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>24.57734727134041</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>180.0279639315681</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>64.01881342024363</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1197046.509141761</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>70.01258515194444</v>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>EqKWmJfM</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>KtuTuMN0</t>
         </is>
@@ -2307,84 +2559,98 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>26.92077922077922</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>180.5926406926407</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>26.50513468013468</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>180.6112794612795</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>69.14242424242424</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2297474.025974026</v>
-      </c>
-      <c r="U13" t="n">
-        <v>72.13376623376624</v>
-      </c>
-      <c r="V13" t="n">
-        <v>26.925</v>
-      </c>
-      <c r="W13" t="n">
-        <v>178.7866666666667</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.065555555555556</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>70.88277777777778</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3757430.555555555</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>74.03222222222223</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>25.78071073447061</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>181.1364719400924</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
+        <v>68.87929292929293</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2444636.363636364</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>72.42516835016835</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>26.42083333333333</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>179.3511111111111</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.043611111111111</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>70.44472222222223</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3444270.833333333</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>74.17416666666665</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>25.65482804232805</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>180.6182309638832</v>
+      </c>
+      <c r="AR13" t="n">
         <v>1</v>
       </c>
-      <c r="AE13" t="n">
-        <v>65.82318262464359</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1376697.078196788</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>69.87288529308125</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24.1158518830353</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>177.7218862427954</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.025993357487923</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>64.74215994689602</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1610921.057879067</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>70.37586407784457</v>
-      </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AS13" t="n">
+        <v>65.99736743731309</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1526651.066827697</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>70.33711036346905</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>24.02631308663816</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>178.6731279178338</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.034250085999312</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>64.88229925303456</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1584494.082940194</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>70.35187656641604</v>
+      </c>
+      <c r="BB13" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>2PIEeC7j</t>
         </is>
@@ -2456,84 +2722,98 @@
           <t>tr3oe8I8</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>26.44570707070708</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>180.7110651974289</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.222681359044995</v>
-      </c>
-      <c r="S14" t="n">
-        <v>68.58055555555555</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1979111.340679523</v>
-      </c>
-      <c r="U14" t="n">
-        <v>72.44042699724518</v>
-      </c>
-      <c r="V14" t="n">
-        <v>26.15741626794258</v>
-      </c>
-      <c r="W14" t="n">
-        <v>182.1358851674641</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.121531100478469</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>68.30382775119617</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2471279.90430622</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>71.43205741626795</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>24.18946725293046</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>178.8750167473059</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>1.087967113542255</v>
+        <v>26.7968253968254</v>
       </c>
       <c r="AE14" t="n">
-        <v>63.4354962656597</v>
+        <v>178.9045634920635</v>
       </c>
       <c r="AF14" t="n">
-        <v>1460938.296453455</v>
+        <v>1.228571428571428</v>
       </c>
       <c r="AG14" t="n">
-        <v>69.38301599117567</v>
+        <v>68.7220238095238</v>
       </c>
       <c r="AH14" t="n">
-        <v>26.22981645192576</v>
+        <v>2021661.706349206</v>
       </c>
       <c r="AI14" t="n">
-        <v>180.876113972737</v>
+        <v>72.56825396825397</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.135701206146421</v>
+        <v>25.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>65.90646406714687</v>
+        <v>181.8090909090909</v>
       </c>
       <c r="AL14" t="n">
-        <v>1490099.335251055</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="AM14" t="n">
-        <v>69.39582480866973</v>
-      </c>
-      <c r="AN14" t="inlineStr">
+        <v>67.66363636363636</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2407272.727272728</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>72.02727272727273</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>23.85587126917892</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>178.3148709560102</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.09323959942482</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>63.16177276402552</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1392433.157053821</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>69.73043520230365</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>26.3531794406966</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>181.0415329578888</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.143556272103183</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>65.89872009569379</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1427711.637790127</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>69.4474534904455</v>
+      </c>
+      <c r="BB14" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>Uw6sTk0t</t>
         </is>
@@ -2605,86 +2885,5013 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>25.87020202020202</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>177.3727272727273</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>25.67181818181819</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>177.1909090909091</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
-        <v>69.30454545454546</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2735025.252525253</v>
-      </c>
-      <c r="U15" t="n">
-        <v>72.06717171717172</v>
-      </c>
-      <c r="V15" t="n">
-        <v>25.37581073896863</v>
-      </c>
-      <c r="W15" t="n">
-        <v>182.3864433811802</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.187772461456672</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>67.65119617224882</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2085168.793195109</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>71.35933014354067</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>25.16544325239978</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>177.7562853343651</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
+        <v>68.94727272727273</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2670090.909090909</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>71.83727272727273</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>25.52313131313131</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>182.5251515151515</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.193131313131313</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>68.07363636363637</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2213866.161616161</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>71.52818181818182</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>24.9841533180778</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>177.7262194435364</v>
+      </c>
+      <c r="AR15" t="n">
         <v>1</v>
       </c>
-      <c r="AE15" t="n">
-        <v>65.19348235634467</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1111698.245393897</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>69.18523738070839</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23.9655833367913</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>181.7573487226124</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AS15" t="n">
+        <v>64.98816888235079</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1051843.875994334</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>69.31582089281173</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>23.94140077801456</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>182.0517189698846</v>
+      </c>
+      <c r="AX15" t="n">
         <v>1</v>
       </c>
-      <c r="AK15" t="n">
-        <v>64.9764667402587</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1383507.103860982</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>70.02499093466196</v>
-      </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AY15" t="n">
+        <v>64.51243546700977</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1394605.642615898</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>69.84434753327169</v>
+      </c>
+      <c r="BB15" t="inlineStr">
         <is>
           <t>EqKWmJfM</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>25.26818181818182</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>180.4727272727273</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>68.3659090909091</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3131392.045454545</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>72.69204545454545</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>27.80165289256198</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>183.9173553719008</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.165289256198347</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>69.28925619834712</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3259090.909090909</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>71.09917355371901</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>24.33802787419315</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>180.9723922177567</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>65.03660295639995</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1911195.794894045</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>70.87722833698697</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>27.60005409610153</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>182.8966305433696</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.050919271769074</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>65.31591613261573</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1190932.419030245</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>66.50598150202893</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>25.94462809917355</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>182.3898071625344</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.008264462809917</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>66.14003673094582</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1602788.337924701</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>71.02240587695132</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>182.0390909090909</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.753636363636363</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6696227.272727272</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>26.37666089851918</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>181.3269249021923</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.094407019005949</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>65.67699184356938</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1736085.048826693</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>70.1953940667176</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>24.19655674390969</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>184.2788071895425</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.13625</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>67.32904114676174</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2497732.36036839</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>73.68435308972074</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>26.33553719008264</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>184.5619834710744</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.091735537190083</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>66.12892561983472</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1300818.181818182</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>70.36776859504131</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>25.00454545454546</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>179.5445454545455</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3818140.909090909</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>73.45363636363636</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>23.20697987473951</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>182.4942501083368</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.014380648591175</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>61.80556105869925</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>885170.3845377502</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>71.00139593027292</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>24.61748508098892</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>181.3933716965047</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>61.78537936913897</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1350476.417306053</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>67.04961423699915</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="n">
+        <v>23.10956790123457</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>182.6851851851852</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>65.90895061728396</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1543217.592592593</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>71.75308641975309</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>23.63636363636364</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>179.2809917355372</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.016528925619835</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>65.60330578512396</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1267768.595041322</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>21.55911397594195</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>181.0105813825426</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>62.53305314553531</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1357813.972576757</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>71.51192892717728</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>23.22591499409681</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>180.5855485821993</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.097405704343503</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>64.90665299612668</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1335678.698295325</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>71.5697855175128</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>26.19421487603306</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>182.4801652892562</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.202479338842975</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>64.58677685950414</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2112826.446280992</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>67.92727272727274</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>26.67685950413223</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>179.7090909090909</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.231404958677686</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>69.71487603305785</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2958000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>72.6694214876033</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>23.2054606212501</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>178.6450216450216</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.146240601503759</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>62.98931419457734</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1573240.354674566</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>69.22209311156679</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>25.41277671573197</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>179.8521557905459</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.153747579936716</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>64.57245684702764</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2632059.859176381</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>69.42460886050812</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>167</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="n">
+        <v>26.48035914702582</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>181.016835016835</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.097194163860831</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>68.87205387205387</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>3112985.409652076</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>71.81324354657689</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>25.90087412587413</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>179.4230769230769</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.175524475524476</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>67.23374125874126</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>4023791.083916084</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>72.07412587412588</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>25.54344898928232</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>181.4421040923492</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.108652748848827</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>66.22410569640962</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1460147.323174284</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>71.87919589488217</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>25.75187049009323</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>179.8382584052673</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03751056635672</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>65.72562230722339</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2103155.305903589</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>70.48947342993273</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>167</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>181.8090909090909</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.063636363636364</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>67.66363636363636</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2407272.727272728</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>72.02727272727273</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>25.70648148148148</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>183.6495791245792</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>69.34503367003367</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2970762.626262626</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>73.03569023569024</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>26.3531794406966</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>181.0415329578888</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.143556272103183</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>65.89872009569379</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1427711.637790127</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>69.4474534904455</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>24.50724933802394</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>181.1947520257802</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.070842992369361</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>65.2882518238185</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1590171.859358947</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>70.88647381326133</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>167</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>26.07438016528926</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>181.595041322314</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>65.57851239669422</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1191322.314049587</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>69.80165289256198</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>25.67181818181819</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>177.1909090909091</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>68.94727272727273</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2670090.909090909</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>71.83727272727273</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>24.57734727134041</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>180.0279639315681</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>64.01881342024363</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1197046.509141761</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>70.01258515194444</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>24.9841533180778</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>177.7262194435364</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>64.98816888235079</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1051843.875994334</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>69.31582089281173</v>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>167</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="n">
+        <v>25.52313131313131</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>182.5251515151515</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.193131313131313</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>68.07363636363637</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2213866.161616161</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>71.52818181818182</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>26.50513468013468</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>180.6112794612795</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>68.87929292929293</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2444636.363636364</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>72.42516835016835</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>23.94140077801456</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>182.0517189698846</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>64.51243546700977</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1394605.642615898</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>69.84434753327169</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>25.65482804232805</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>180.6182309638832</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>65.99736743731309</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1526651.066827697</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>70.33711036346905</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>167</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="n">
+        <v>24.40075757575758</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>178.9327441077441</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>66.04755892255893</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1930372.474747475</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>72.55101010101009</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>26.79318181818182</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>180.5780303030303</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.153030303030303</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>67.71363636363635</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1829492.424242425</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>70.73939393939393</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>24.74314626110082</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>178.7516843533312</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>63.79586524871346</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1494232.098642793</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>70.26155345389344</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>25.67065089436371</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>179.8500226191302</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.093092937658155</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>64.27877445039915</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1270407.761691228</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>68.5116460315259</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>167</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="n">
+        <v>25.68461538461538</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>182.33006993007</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.066433566433566</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>67.62027972027971</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2691825.174825174</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>71.45594405594406</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>26.60330578512396</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>178.595041322314</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2824834.710743802</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>72.3801652892562</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>24.84679767219813</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>180.243165739676</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.029688351313065</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>63.3128493169683</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1488422.15874324</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>69.28995175305243</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>26.4414631668933</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>179.5150468715453</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>67.28170106586172</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1725852.07901582</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>69.64167702534361</v>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>167</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="n">
+        <v>24.10909090909091</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>180.2181818181818</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1664545.454545455</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>70.65454545454546</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>26.98811188811189</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>180.0566433566434</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.05034965034965</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>65.7888111888112</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1155258.741258741</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>68.8944055944056</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>22.00460505677897</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>180.0500345065562</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>60.12587991718426</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>771341.3325804631</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>69.14493381015122</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>25.36563837129055</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>180.2409542389977</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.062976057758667</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>63.37454822954823</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1002037.710357275</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>67.66753835536444</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="n">
+        <v>26.42083333333333</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>179.3511111111111</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.043611111111111</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>70.44472222222223</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3444270.833333333</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>74.17416666666665</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>27.55361952861953</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>180.596127946128</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.335774410774411</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>71.99309764309764</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>4189000.420875421</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>74.8462962962963</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>24.02631308663816</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>178.6731279178338</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.034250085999312</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>64.88229925303456</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1584494.082940194</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>70.35187656641604</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>25.96729267464562</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>179.5308471620972</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01058201058201</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>67.10095466216789</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1779057.356212687</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>72.29551528944911</v>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="n">
+        <v>23.63636363636364</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>179.2809917355372</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.016528925619835</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>65.60330578512396</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1267768.595041322</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>25.67181818181819</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>177.1909090909091</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>68.94727272727273</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2670090.909090909</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>71.83727272727273</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>23.22591499409681</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>180.5855485821993</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.097405704343503</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>64.90665299612668</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1335678.698295325</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>71.5697855175128</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>24.9841533180778</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>177.7262194435364</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>64.98816888235079</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1051843.875994334</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>69.31582089281173</v>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>167</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="n">
+        <v>25.26818181818182</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>180.4727272727273</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>68.3659090909091</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>3131392.045454545</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>72.69204545454545</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>26.19421487603306</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>182.4801652892562</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.202479338842975</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>64.58677685950414</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2112826.446280992</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>67.92727272727274</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>24.33802787419315</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>180.9723922177567</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>65.03660295639995</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1911195.794894045</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>70.87722833698697</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>23.2054606212501</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>178.6450216450216</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.146240601503759</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>62.98931419457734</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1573240.354674566</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>69.22209311156679</v>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>167</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="n">
+        <v>25.00454545454546</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>179.5445454545455</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>69</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3818140.909090909</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>73.45363636363636</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>182.0390909090909</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.753636363636363</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>6696227.272727272</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>24.61748508098892</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>181.3933716965047</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>61.78537936913897</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1350476.417306053</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>67.04961423699915</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>24.19655674390969</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>184.2788071895425</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.13625</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>67.32904114676174</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2497732.36036839</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>73.68435308972074</v>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>167</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="n">
+        <v>26.67685950413223</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>179.7090909090909</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.231404958677686</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>69.71487603305785</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2958000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>72.6694214876033</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>26.33553719008264</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>184.5619834710744</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.091735537190083</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>66.12892561983472</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1300818.181818182</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>70.36776859504131</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>25.41277671573197</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>179.8521557905459</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.153747579936716</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>64.57245684702764</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2632059.859176381</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>69.42460886050812</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>23.20697987473951</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>182.4942501083368</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.014380648591175</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>61.80556105869925</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>885170.3845377502</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>71.00139593027292</v>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="n">
+        <v>25.70648148148148</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>183.6495791245792</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>69.34503367003367</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>2970762.626262626</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>73.03569023569024</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>22.99917355371901</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>179.3239669421488</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.109090909090909</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>67.7809917355372</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2817396.694214876</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>74.36446280991736</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>24.50724933802394</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>181.1947520257802</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.070842992369361</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>65.2882518238185</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1590171.859358947</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>70.88647381326133</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>23.19050834657089</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>180.6628698318654</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.068762021517195</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>63.75365960184897</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1711832.381435119</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>71.82951192030477</v>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45479.89583333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="n">
+        <v>27.94454545454546</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>179.7818181818182</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.116363636363636</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>67.31272727272726</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2094977.272727273</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>68.51454545454547</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>23.10956790123457</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>182.6851851851852</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>65.90895061728396</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1543217.592592593</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>71.75308641975309</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>28.00286226809564</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>181.4884681626274</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.261435269760078</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>64.70308392197458</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1080869.150377542</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>66.83614490723826</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>21.55911397594195</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>181.0105813825426</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>62.53305314553531</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1357813.972576757</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>71.51192892717728</v>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45479.9375</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>167</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="n">
+        <v>24.40075757575758</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>178.9327441077441</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>66.04755892255893</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1930372.474747475</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>72.55101010101009</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>25.90087412587413</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>179.4230769230769</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.175524475524476</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>67.23374125874126</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>4023791.083916084</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>72.07412587412588</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>24.74314626110082</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>178.7516843533312</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>63.79586524871346</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1494232.098642793</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>70.26155345389344</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>25.75187049009323</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>179.8382584052673</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03751056635672</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>65.72562230722339</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>2103155.305903589</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>70.48947342993273</v>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="n">
+        <v>26.7968253968254</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>178.9045634920635</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.228571428571428</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>68.7220238095238</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2021661.706349206</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>72.56825396825397</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>26.48035914702582</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>181.016835016835</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.097194163860831</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>68.87205387205387</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>3112985.409652076</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>71.81324354657689</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>23.85587126917892</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>178.3148709560102</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.09323959942482</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>63.16177276402552</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1392433.157053821</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>69.73043520230365</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>25.54344898928232</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>181.4421040923492</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.108652748848827</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>66.22410569640962</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1460147.323174284</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>71.87919589488217</v>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>167</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="n">
+        <v>26.79318181818182</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>180.5780303030303</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.153030303030303</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>67.71363636363635</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1829492.424242425</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>70.73939393939393</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>27.55361952861953</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>180.596127946128</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.335774410774411</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>71.99309764309764</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>4189000.420875421</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>74.8462962962963</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>25.67065089436371</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>179.8500226191302</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.093092937658155</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>64.27877445039915</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1270407.761691228</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>68.5116460315259</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>25.96729267464562</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>179.5308471620972</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.01058201058201</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>67.10095466216789</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1779057.356212687</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>72.29551528944911</v>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>167</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="n">
+        <v>26.50513468013468</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>180.6112794612795</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>68.87929292929293</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2444636.363636364</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>72.42516835016835</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>181.8090909090909</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.063636363636364</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>67.66363636363636</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2407272.727272728</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>72.02727272727273</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>25.65482804232805</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>180.6182309638832</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>65.99736743731309</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1526651.066827697</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>70.33711036346905</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>26.3531794406966</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>181.0415329578888</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.143556272103183</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>65.89872009569379</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1427711.637790127</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>69.4474534904455</v>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>167</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="n">
+        <v>26.98811188811189</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>180.0566433566434</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.05034965034965</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>65.7888111888112</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1155258.741258741</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>68.8944055944056</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>25.68461538461538</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>182.33006993007</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.066433566433566</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>67.62027972027971</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2691825.174825174</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>71.45594405594406</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>25.36563837129055</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>180.2409542389977</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.062976057758667</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>63.37454822954823</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1002037.710357275</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>67.66753835536444</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>24.84679767219813</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>180.243165739676</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.029688351313065</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>63.3128493169683</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1488422.15874324</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>69.28995175305243</v>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45480.9375</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>167</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="n">
+        <v>24.10909090909091</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>180.2181818181818</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1664545.454545455</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>70.65454545454546</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>25.52313131313131</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>182.5251515151515</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.193131313131313</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>68.07363636363637</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2213866.161616161</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>71.52818181818182</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>22.00460505677897</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>180.0500345065562</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>60.12587991718426</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>771341.3325804631</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>69.14493381015122</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>23.94140077801456</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>182.0517189698846</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>64.51243546700977</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1394605.642615898</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>69.84434753327169</v>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>167</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="n">
+        <v>26.42083333333333</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>179.3511111111111</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.043611111111111</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>70.44472222222223</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>3444270.833333333</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>74.17416666666665</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>26.07438016528926</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>181.595041322314</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>65.57851239669422</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1191322.314049587</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>69.80165289256198</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>24.02631308663816</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>178.6731279178338</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.034250085999312</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>64.88229925303456</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1584494.082940194</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>70.35187656641604</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>24.57734727134041</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>180.0279639315681</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>64.01881342024363</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1197046.509141761</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>70.01258515194444</v>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>167</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="n">
+        <v>26.60330578512396</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>178.595041322314</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2824834.710743802</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>72.3801652892562</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>27.80165289256198</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>183.9173553719008</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.165289256198347</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>69.28925619834712</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3259090.909090909</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>71.09917355371901</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>26.4414631668933</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>179.5150468715453</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>67.28170106586172</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1725852.07901582</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>69.64167702534361</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>27.60005409610153</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>182.8966305433696</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.050919271769074</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>65.31591613261573</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1190932.419030245</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>66.50598150202893</v>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">surgan j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>167</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="n">
+        <v>25.90087412587413</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>179.4230769230769</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.175524475524476</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>67.23374125874126</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>4023791.083916084</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>72.07412587412588</v>
+      </c>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="n">
+        <v>25.75187049009323</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>179.8382584052673</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.03751056635672</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>65.72562230722339</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2103155.305903589</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>70.48947342993273</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>190</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>247500</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>MRdhQQTs</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>167</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="n">
+        <v>26.7968253968254</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>178.9045634920635</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.228571428571428</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>68.7220238095238</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2021661.706349206</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>72.56825396825397</v>
+      </c>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="n">
+        <v>23.85587126917892</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>178.3148709560102</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.09323959942482</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>63.16177276402552</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1392433.157053821</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>69.73043520230365</v>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>167</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="n">
+        <v>26.98811188811189</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>180.0566433566434</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.05034965034965</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>65.7888111888112</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1155258.741258741</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>68.8944055944056</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>25.68461538461538</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>182.33006993007</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.066433566433566</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>67.62027972027971</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>2691825.174825174</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>71.45594405594406</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>25.36563837129055</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>180.2409542389977</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.062976057758667</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>63.37454822954823</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1002037.710357275</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>67.66753835536444</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>24.84679767219813</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>180.243165739676</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.029688351313065</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>63.3128493169683</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1488422.15874324</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>69.28995175305243</v>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corbyn m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>167</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="n">
+        <v>27.55361952861953</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>180.596127946128</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.335774410774411</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>71.99309764309764</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>4189000.420875421</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>74.8462962962963</v>
+      </c>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="n">
+        <v>25.96729267464562</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>179.5308471620972</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.01058201058201</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>67.10095466216789</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1779057.356212687</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>72.29551528944911</v>
+      </c>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -715,8 +715,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -809,76 +809,76 @@
         <v>359</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.10956790123457</v>
+        <v>23.13888888888889</v>
       </c>
       <c r="AE2" t="n">
-        <v>182.6851851851852</v>
+        <v>182.5052083333333</v>
       </c>
       <c r="AF2" t="n">
         <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>65.90895061728396</v>
+        <v>65.81944444444446</v>
       </c>
       <c r="AH2" t="n">
-        <v>1543217.592592593</v>
+        <v>1529869.791666667</v>
       </c>
       <c r="AI2" t="n">
-        <v>71.75308641975309</v>
+        <v>71.59722222222223</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.67685950413223</v>
+        <v>26.78454545454546</v>
       </c>
       <c r="AK2" t="n">
-        <v>179.7090909090909</v>
+        <v>179.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.231404958677686</v>
+        <v>1.254545454545455</v>
       </c>
       <c r="AM2" t="n">
-        <v>69.71487603305785</v>
+        <v>69.70636363636363</v>
       </c>
       <c r="AN2" t="n">
-        <v>2958000</v>
+        <v>2999050</v>
       </c>
       <c r="AO2" t="n">
-        <v>72.6694214876033</v>
+        <v>72.59636363636363</v>
       </c>
       <c r="AP2" t="n">
-        <v>21.55911397594195</v>
+        <v>21.42800103607076</v>
       </c>
       <c r="AQ2" t="n">
-        <v>181.0105813825426</v>
+        <v>181.0745590240812</v>
       </c>
       <c r="AR2" t="n">
         <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>62.53305314553531</v>
+        <v>62.4763392438315</v>
       </c>
       <c r="AT2" t="n">
-        <v>1357813.972576757</v>
+        <v>1375662.868080455</v>
       </c>
       <c r="AU2" t="n">
-        <v>71.51192892717728</v>
+        <v>71.68958286594577</v>
       </c>
       <c r="AV2" t="n">
-        <v>25.41277671573197</v>
+        <v>25.17310200635278</v>
       </c>
       <c r="AW2" t="n">
-        <v>179.8521557905459</v>
+        <v>179.86118089341</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.153747579936716</v>
+        <v>1.126265195073245</v>
       </c>
       <c r="AY2" t="n">
-        <v>64.57245684702764</v>
+        <v>64.3297025317304</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2632059.859176381</v>
+        <v>2591051.559379733</v>
       </c>
       <c r="BA2" t="n">
-        <v>69.42460886050812</v>
+        <v>69.41945069893987</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
@@ -953,91 +953,119 @@
           <t>j9cigLCr</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>177</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>279</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>292</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>524</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7565000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>542</v>
+      </c>
       <c r="AD3" t="n">
-        <v>25.90087412587413</v>
+        <v>25.97594696969697</v>
       </c>
       <c r="AE3" t="n">
-        <v>179.4230769230769</v>
+        <v>179.4507575757576</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.175524475524476</v>
+        <v>1.167424242424243</v>
       </c>
       <c r="AG3" t="n">
-        <v>67.23374125874126</v>
+        <v>67.11685606060605</v>
       </c>
       <c r="AH3" t="n">
-        <v>4023791.083916084</v>
+        <v>3824334.28030303</v>
       </c>
       <c r="AI3" t="n">
-        <v>72.07412587412588</v>
+        <v>71.89090909090909</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.19421487603306</v>
+        <v>26.12272727272727</v>
       </c>
       <c r="AK3" t="n">
-        <v>182.4801652892562</v>
+        <v>182.4281818181818</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.202479338842975</v>
+        <v>1.213636363636364</v>
       </c>
       <c r="AM3" t="n">
-        <v>64.58677685950414</v>
+        <v>64.49090909090908</v>
       </c>
       <c r="AN3" t="n">
-        <v>2112826.446280992</v>
+        <v>2153018.181818182</v>
       </c>
       <c r="AO3" t="n">
-        <v>67.92727272727274</v>
+        <v>67.84727272727272</v>
       </c>
       <c r="AP3" t="n">
-        <v>25.75187049009323</v>
+        <v>25.67727146230688</v>
       </c>
       <c r="AQ3" t="n">
-        <v>179.8382584052673</v>
+        <v>179.9767407233533</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03751056635672</v>
+        <v>1.040636446886447</v>
       </c>
       <c r="AS3" t="n">
-        <v>65.72562230722339</v>
+        <v>65.67824769557043</v>
       </c>
       <c r="AT3" t="n">
-        <v>2103155.305903589</v>
+        <v>2142756.483356339</v>
       </c>
       <c r="AU3" t="n">
-        <v>70.48947342993273</v>
+        <v>70.50575307850555</v>
       </c>
       <c r="AV3" t="n">
-        <v>23.2054606212501</v>
+        <v>23.30219715956558</v>
       </c>
       <c r="AW3" t="n">
-        <v>178.6450216450216</v>
+        <v>178.6619047619047</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.146240601503759</v>
+        <v>1.160864661654135</v>
       </c>
       <c r="AY3" t="n">
-        <v>62.98931419457734</v>
+        <v>63.18348370927318</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1573240.354674566</v>
+        <v>1659254.866332498</v>
       </c>
       <c r="BA3" t="n">
-        <v>69.22209311156679</v>
+        <v>69.38239766081873</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1061,7 +1089,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
@@ -1116,91 +1144,119 @@
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>120</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>128</v>
+      </c>
+      <c r="W4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>353</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15575000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>360</v>
+      </c>
       <c r="AD4" t="n">
-        <v>23.63636363636364</v>
+        <v>23.53636363636364</v>
       </c>
       <c r="AE4" t="n">
-        <v>179.2809917355372</v>
+        <v>179.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.016528925619835</v>
+        <v>1.018181818181818</v>
       </c>
       <c r="AG4" t="n">
-        <v>65.60330578512396</v>
+        <v>65.54545454545455</v>
       </c>
       <c r="AH4" t="n">
-        <v>1267768.595041322</v>
+        <v>1271363.636363636</v>
       </c>
       <c r="AI4" t="n">
-        <v>71.36363636363636</v>
+        <v>71.47272727272727</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25.70648148148148</v>
+        <v>25.62525252525252</v>
       </c>
       <c r="AK4" t="n">
-        <v>183.6495791245792</v>
+        <v>183.7086317722681</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.066666666666667</v>
+        <v>1.054545454545455</v>
       </c>
       <c r="AM4" t="n">
-        <v>69.34503367003367</v>
+        <v>69.08549127640036</v>
       </c>
       <c r="AN4" t="n">
-        <v>2970762.626262626</v>
+        <v>2903104.683195592</v>
       </c>
       <c r="AO4" t="n">
-        <v>73.03569023569024</v>
+        <v>72.80257116620754</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.22591499409681</v>
+        <v>23.30267316017316</v>
       </c>
       <c r="AQ4" t="n">
-        <v>180.5855485821993</v>
+        <v>180.6566034404192</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.097405704343503</v>
+        <v>1.102979608111187</v>
       </c>
       <c r="AS4" t="n">
-        <v>64.90665299612668</v>
+        <v>65.01815162907266</v>
       </c>
       <c r="AT4" t="n">
-        <v>1335678.698295325</v>
+        <v>1357684.068124857</v>
       </c>
       <c r="AU4" t="n">
-        <v>71.5697855175128</v>
+        <v>71.58093073593074</v>
       </c>
       <c r="AV4" t="n">
-        <v>24.50724933802394</v>
+        <v>24.52495382329884</v>
       </c>
       <c r="AW4" t="n">
-        <v>181.1947520257802</v>
+        <v>181.0988203917602</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.070842992369361</v>
+        <v>1.07728326440294</v>
       </c>
       <c r="AY4" t="n">
-        <v>65.2882518238185</v>
+        <v>65.3030928987111</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1590171.859358947</v>
+        <v>1594335.210209761</v>
       </c>
       <c r="BA4" t="n">
-        <v>70.88647381326133</v>
+        <v>70.95569870537601</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1224,7 +1280,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">fierro r 
   usa </t>
         </is>
       </c>
@@ -1275,91 +1331,119 @@
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>172.3333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>206</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9475000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>214</v>
+      </c>
+      <c r="W5" t="n">
+        <v>37</v>
+      </c>
+      <c r="X5" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>63</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>63</v>
+      </c>
       <c r="AD5" t="n">
-        <v>26.48035914702582</v>
+        <v>26.34040404040404</v>
       </c>
       <c r="AE5" t="n">
-        <v>181.016835016835</v>
+        <v>180.9939393939394</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.097194163860831</v>
+        <v>1.096843434343434</v>
       </c>
       <c r="AG5" t="n">
-        <v>68.87205387205387</v>
+        <v>68.7560606060606</v>
       </c>
       <c r="AH5" t="n">
-        <v>3112985.409652076</v>
+        <v>3075858.585858586</v>
       </c>
       <c r="AI5" t="n">
-        <v>71.81324354657689</v>
+        <v>71.93989898989899</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.26818181818182</v>
+        <v>25.63506493506494</v>
       </c>
       <c r="AK5" t="n">
-        <v>180.4727272727273</v>
+        <v>180.1545454545455</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>68.3659090909091</v>
+        <v>68.86103896103897</v>
       </c>
       <c r="AN5" t="n">
-        <v>3131392.045454545</v>
+        <v>3372662.337662338</v>
       </c>
       <c r="AO5" t="n">
-        <v>72.69204545454545</v>
+        <v>72.7909090909091</v>
       </c>
       <c r="AP5" t="n">
-        <v>25.54344898928232</v>
+        <v>25.61919261294261</v>
       </c>
       <c r="AQ5" t="n">
-        <v>181.4421040923492</v>
+        <v>181.7083046038928</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.108652748848827</v>
+        <v>1.122234342454931</v>
       </c>
       <c r="AS5" t="n">
-        <v>66.22410569640962</v>
+        <v>66.29118140846083</v>
       </c>
       <c r="AT5" t="n">
-        <v>1460147.323174284</v>
+        <v>1492275.113571069</v>
       </c>
       <c r="AU5" t="n">
-        <v>71.87919589488217</v>
+        <v>72.05159538174244</v>
       </c>
       <c r="AV5" t="n">
-        <v>24.33802787419315</v>
+        <v>24.10060328479218</v>
       </c>
       <c r="AW5" t="n">
-        <v>180.9723922177567</v>
+        <v>181.3597525966909</v>
       </c>
       <c r="AX5" t="n">
         <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>65.03660295639995</v>
+        <v>64.4952480992397</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1911195.794894045</v>
+        <v>1538416.312177045</v>
       </c>
       <c r="BA5" t="n">
-        <v>70.87722833698697</v>
+        <v>70.67956530438262</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1383,7 +1467,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
@@ -1430,91 +1514,119 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>310</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>362</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>187.1666666666667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>383</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>426</v>
+      </c>
       <c r="AD6" t="n">
-        <v>22.99917355371901</v>
+        <v>22.98909090909091</v>
       </c>
       <c r="AE6" t="n">
-        <v>179.3239669421488</v>
+        <v>179.2063636363636</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.109090909090909</v>
+        <v>1.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>67.7809917355372</v>
+        <v>67.69909090909091</v>
       </c>
       <c r="AH6" t="n">
-        <v>2817396.694214876</v>
+        <v>2739636.363636364</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.36446280991736</v>
+        <v>74.25090909090909</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26.33553719008264</v>
+        <v>26.36909090909091</v>
       </c>
       <c r="AK6" t="n">
-        <v>184.5619834710744</v>
+        <v>184.6181818181818</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.091735537190083</v>
+        <v>1.091818181818182</v>
       </c>
       <c r="AM6" t="n">
-        <v>66.12892561983472</v>
+        <v>66.12363636363636</v>
       </c>
       <c r="AN6" t="n">
-        <v>1300818.181818182</v>
+        <v>1288945.454545455</v>
       </c>
       <c r="AO6" t="n">
-        <v>70.36776859504131</v>
+        <v>70.38636363636363</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.19050834657089</v>
+        <v>23.14434178992363</v>
       </c>
       <c r="AQ6" t="n">
-        <v>180.6628698318654</v>
+        <v>180.929156815052</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.068762021517195</v>
+        <v>1.066942571495001</v>
       </c>
       <c r="AS6" t="n">
-        <v>63.75365960184897</v>
+        <v>63.58989512725126</v>
       </c>
       <c r="AT6" t="n">
-        <v>1711832.381435119</v>
+        <v>1687493.880448197</v>
       </c>
       <c r="AU6" t="n">
-        <v>71.82951192030477</v>
+        <v>71.84289789494393</v>
       </c>
       <c r="AV6" t="n">
-        <v>23.20697987473951</v>
+        <v>23.1688543328017</v>
       </c>
       <c r="AW6" t="n">
-        <v>182.4942501083368</v>
+        <v>182.3730868838764</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.014380648591175</v>
+        <v>1.015818713450293</v>
       </c>
       <c r="AY6" t="n">
-        <v>61.80556105869925</v>
+        <v>61.85670539986329</v>
       </c>
       <c r="AZ6" t="n">
-        <v>885170.3845377502</v>
+        <v>911540.3641679958</v>
       </c>
       <c r="BA6" t="n">
-        <v>71.00139593027292</v>
+        <v>70.92506493506492</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1538,7 +1650,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
@@ -1593,91 +1705,119 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>174</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>206</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>229</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>284</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>295</v>
+      </c>
       <c r="AD7" t="n">
-        <v>25.68461538461538</v>
+        <v>25.64166666666667</v>
       </c>
       <c r="AE7" t="n">
-        <v>182.33006993007</v>
+        <v>182.2909090909091</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.066433566433566</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="AG7" t="n">
-        <v>67.62027972027971</v>
+        <v>67.5719696969697</v>
       </c>
       <c r="AH7" t="n">
-        <v>2691825.174825174</v>
+        <v>2702393.939393939</v>
       </c>
       <c r="AI7" t="n">
-        <v>71.45594405594406</v>
+        <v>71.45227272727273</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25.00454545454546</v>
+        <v>24.7939393939394</v>
       </c>
       <c r="AK7" t="n">
-        <v>179.5445454545455</v>
+        <v>179.6828282828283</v>
       </c>
       <c r="AL7" t="n">
         <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>69</v>
+        <v>68.85555555555555</v>
       </c>
       <c r="AN7" t="n">
-        <v>3818140.909090909</v>
+        <v>3821267.676767677</v>
       </c>
       <c r="AO7" t="n">
-        <v>73.45363636363636</v>
+        <v>73.5929292929293</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.84679767219813</v>
+        <v>24.88561811313528</v>
       </c>
       <c r="AQ7" t="n">
-        <v>180.243165739676</v>
+        <v>180.3666041544903</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.029688351313065</v>
+        <v>1.0281941266209</v>
       </c>
       <c r="AS7" t="n">
-        <v>63.3128493169683</v>
+        <v>63.1603486648109</v>
       </c>
       <c r="AT7" t="n">
-        <v>1488422.15874324</v>
+        <v>1398727.179908351</v>
       </c>
       <c r="AU7" t="n">
-        <v>69.28995175305243</v>
+        <v>69.15141598644173</v>
       </c>
       <c r="AV7" t="n">
-        <v>24.61748508098892</v>
+        <v>24.63979823813584</v>
       </c>
       <c r="AW7" t="n">
-        <v>181.3933716965047</v>
+        <v>181.5852278109311</v>
       </c>
       <c r="AX7" t="n">
         <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>61.78537936913897</v>
+        <v>61.77542152126552</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1350476.417306053</v>
+        <v>1247427.500710429</v>
       </c>
       <c r="BA7" t="n">
-        <v>67.04961423699915</v>
+        <v>67.09679359666572</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -1701,8 +1841,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1756,13 +1896,27 @@
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>875000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>72</v>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
@@ -1771,76 +1925,76 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>26.79318181818182</v>
+        <v>26.90661157024794</v>
       </c>
       <c r="AE8" t="n">
-        <v>180.5780303030303</v>
+        <v>180.7297520661157</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.153030303030303</v>
+        <v>1.166942148760331</v>
       </c>
       <c r="AG8" t="n">
-        <v>67.71363636363635</v>
+        <v>67.78677685950413</v>
       </c>
       <c r="AH8" t="n">
-        <v>1829492.424242425</v>
+        <v>1879652.892561984</v>
       </c>
       <c r="AI8" t="n">
-        <v>70.73939393939393</v>
+        <v>70.75702479338842</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25.94462809917355</v>
+        <v>25.92090909090909</v>
       </c>
       <c r="AK8" t="n">
-        <v>182.3898071625344</v>
+        <v>182.610606060606</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.008264462809917</v>
+        <v>1.009090909090909</v>
       </c>
       <c r="AM8" t="n">
-        <v>66.14003673094582</v>
+        <v>66.05404040404041</v>
       </c>
       <c r="AN8" t="n">
-        <v>1602788.337924701</v>
+        <v>1559339.898989899</v>
       </c>
       <c r="AO8" t="n">
-        <v>71.02240587695132</v>
+        <v>70.98828282828283</v>
       </c>
       <c r="AP8" t="n">
-        <v>25.67065089436371</v>
+        <v>25.41993084579937</v>
       </c>
       <c r="AQ8" t="n">
-        <v>179.8500226191302</v>
+        <v>179.6805441559342</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.093092937658155</v>
+        <v>1.075581906016688</v>
       </c>
       <c r="AS8" t="n">
-        <v>64.27877445039915</v>
+        <v>64.01840329653933</v>
       </c>
       <c r="AT8" t="n">
-        <v>1270407.761691228</v>
+        <v>1201462.146953202</v>
       </c>
       <c r="AU8" t="n">
-        <v>68.5116460315259</v>
+        <v>68.50188225084209</v>
       </c>
       <c r="AV8" t="n">
-        <v>26.37666089851918</v>
+        <v>26.50004127408539</v>
       </c>
       <c r="AW8" t="n">
-        <v>181.3269249021923</v>
+        <v>181.2310459638401</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.094407019005949</v>
+        <v>1.103847720906544</v>
       </c>
       <c r="AY8" t="n">
-        <v>65.67699184356938</v>
+        <v>65.6256434088787</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1736085.048826693</v>
+        <v>1705455.458471267</v>
       </c>
       <c r="BA8" t="n">
-        <v>70.1953940667176</v>
+        <v>70.09112394957984</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -1864,8 +2018,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">szpala l 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1919,91 +2073,119 @@
           <t>rsHkUNCo</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>392</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>411</v>
+      </c>
+      <c r="W9" t="n">
+        <v>28.42857142857143</v>
+      </c>
+      <c r="X9" t="n">
+        <v>178.2857142857143</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>535</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>84725000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>557</v>
+      </c>
       <c r="AD9" t="n">
-        <v>27.80165289256198</v>
+        <v>27.78181818181818</v>
       </c>
       <c r="AE9" t="n">
-        <v>183.9173553719008</v>
+        <v>184.0090909090909</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.165289256198347</v>
+        <v>1.172727272727273</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.28925619834712</v>
+        <v>69.33636363636364</v>
       </c>
       <c r="AH9" t="n">
-        <v>3259090.909090909</v>
+        <v>3287272.727272728</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.09917355371901</v>
+        <v>71.11818181818182</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27.37</v>
+        <v>27.41111111111111</v>
       </c>
       <c r="AK9" t="n">
-        <v>182.0390909090909</v>
+        <v>182.0767676767677</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.753636363636363</v>
+        <v>1.75959595959596</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.84</v>
+        <v>73.87777777777779</v>
       </c>
       <c r="AN9" t="n">
-        <v>6696227.272727272</v>
+        <v>6643585.858585859</v>
       </c>
       <c r="AO9" t="n">
-        <v>77.55</v>
+        <v>77.57777777777778</v>
       </c>
       <c r="AP9" t="n">
-        <v>27.60005409610153</v>
+        <v>27.51658124484211</v>
       </c>
       <c r="AQ9" t="n">
-        <v>182.8966305433696</v>
+        <v>182.7862935977066</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.050919271769074</v>
+        <v>1.042967720685112</v>
       </c>
       <c r="AS9" t="n">
-        <v>65.31591613261573</v>
+        <v>65.20837731109471</v>
       </c>
       <c r="AT9" t="n">
-        <v>1190932.419030245</v>
+        <v>1180460.443541965</v>
       </c>
       <c r="AU9" t="n">
-        <v>66.50598150202893</v>
+        <v>66.44788400005791</v>
       </c>
       <c r="AV9" t="n">
-        <v>24.19655674390969</v>
+        <v>24.05172971545521</v>
       </c>
       <c r="AW9" t="n">
-        <v>184.2788071895425</v>
+        <v>184.2958968772694</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.13625</v>
+        <v>1.088888888888889</v>
       </c>
       <c r="AY9" t="n">
-        <v>67.32904114676174</v>
+        <v>66.98365682973525</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2497732.36036839</v>
+        <v>2245049.844853766</v>
       </c>
       <c r="BA9" t="n">
-        <v>73.68435308972074</v>
+        <v>73.43400343302305</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2027,7 +2209,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
+          <t xml:space="preserve">dujic f 
   can </t>
         </is>
       </c>
@@ -2082,13 +2264,27 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>129</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>137</v>
+      </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -2097,22 +2293,22 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>26.98811188811189</v>
+        <v>26.85378787878788</v>
       </c>
       <c r="AE10" t="n">
-        <v>180.0566433566434</v>
+        <v>180.1280303030303</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.05034965034965</v>
+        <v>1.046212121212121</v>
       </c>
       <c r="AG10" t="n">
-        <v>65.7888111888112</v>
+        <v>65.57954545454545</v>
       </c>
       <c r="AH10" t="n">
-        <v>1155258.741258741</v>
+        <v>1125405.303030303</v>
       </c>
       <c r="AI10" t="n">
-        <v>68.8944055944056</v>
+        <v>68.76893939393939</v>
       </c>
       <c r="AJ10" t="n">
         <v>27.94454545454546</v>
@@ -2133,22 +2329,22 @@
         <v>68.51454545454547</v>
       </c>
       <c r="AP10" t="n">
-        <v>25.36563837129055</v>
+        <v>25.3405526800092</v>
       </c>
       <c r="AQ10" t="n">
-        <v>180.2409542389977</v>
+        <v>180.075848573729</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.062976057758667</v>
+        <v>1.063594432942259</v>
       </c>
       <c r="AS10" t="n">
-        <v>63.37454822954823</v>
+        <v>63.50298280423281</v>
       </c>
       <c r="AT10" t="n">
-        <v>1002037.710357275</v>
+        <v>1022022.33436853</v>
       </c>
       <c r="AU10" t="n">
-        <v>67.66753835536444</v>
+        <v>67.78798136645963</v>
       </c>
       <c r="AV10" t="n">
         <v>28.00286226809564</v>
@@ -2190,7 +2386,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">penso c 
   usa </t>
         </is>
       </c>
@@ -2241,91 +2437,119 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>189</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>400000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>68</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20</v>
+      </c>
+      <c r="X11" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>118</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>143</v>
+      </c>
       <c r="AD11" t="n">
-        <v>27.55361952861953</v>
+        <v>27.50477502295684</v>
       </c>
       <c r="AE11" t="n">
-        <v>180.596127946128</v>
+        <v>180.5924701561065</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.335774410774411</v>
+        <v>1.333241505968779</v>
       </c>
       <c r="AG11" t="n">
-        <v>71.99309764309764</v>
+        <v>71.90156106519743</v>
       </c>
       <c r="AH11" t="n">
-        <v>4189000.420875421</v>
+        <v>4181388.888888889</v>
       </c>
       <c r="AI11" t="n">
-        <v>74.8462962962963</v>
+        <v>74.79100091827364</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24.10909090909091</v>
+        <v>24.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>180.2181818181818</v>
+        <v>180.07</v>
       </c>
       <c r="AL11" t="n">
         <v>1</v>
       </c>
       <c r="AM11" t="n">
-        <v>65.54545454545455</v>
+        <v>65.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>1664545.454545455</v>
+        <v>1665900</v>
       </c>
       <c r="AO11" t="n">
-        <v>70.65454545454546</v>
+        <v>70.71000000000001</v>
       </c>
       <c r="AP11" t="n">
-        <v>25.96729267464562</v>
+        <v>25.79076556242331</v>
       </c>
       <c r="AQ11" t="n">
-        <v>179.5308471620972</v>
+        <v>179.3477010363374</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01058201058201</v>
+        <v>1.011544011544012</v>
       </c>
       <c r="AS11" t="n">
-        <v>67.10095466216789</v>
+        <v>67.11013235872862</v>
       </c>
       <c r="AT11" t="n">
-        <v>1779057.356212687</v>
+        <v>1820748.520827064</v>
       </c>
       <c r="AU11" t="n">
-        <v>72.29551528944911</v>
+        <v>72.34717370419243</v>
       </c>
       <c r="AV11" t="n">
-        <v>22.00460505677897</v>
+        <v>22.13284334023464</v>
       </c>
       <c r="AW11" t="n">
-        <v>180.0500345065562</v>
+        <v>180.1050379572118</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
       </c>
       <c r="AY11" t="n">
-        <v>60.12587991718426</v>
+        <v>60.41624568668046</v>
       </c>
       <c r="AZ11" t="n">
-        <v>771341.3325804631</v>
+        <v>796169.9102829538</v>
       </c>
       <c r="BA11" t="n">
-        <v>69.14493381015122</v>
+        <v>69.25387163561076</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
@@ -2349,8 +2573,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">ford t 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2404,91 +2628,119 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>179</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>130</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>130</v>
+      </c>
+      <c r="W12" t="n">
+        <v>23</v>
+      </c>
+      <c r="X12" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>131</v>
+      </c>
       <c r="AD12" t="n">
-        <v>26.60330578512396</v>
+        <v>26.59090909090909</v>
       </c>
       <c r="AE12" t="n">
-        <v>178.595041322314</v>
+        <v>178.7909090909091</v>
       </c>
       <c r="AF12" t="n">
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>69.72727272727273</v>
+        <v>69.66363636363636</v>
       </c>
       <c r="AH12" t="n">
-        <v>2824834.710743802</v>
+        <v>2848909.090909091</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.3801652892562</v>
+        <v>72.32727272727273</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26.07438016528926</v>
+        <v>25.97272727272728</v>
       </c>
       <c r="AK12" t="n">
-        <v>181.595041322314</v>
+        <v>181.6181818181818</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
       </c>
       <c r="AM12" t="n">
-        <v>65.57851239669422</v>
+        <v>65.53636363636363</v>
       </c>
       <c r="AN12" t="n">
-        <v>1191322.314049587</v>
+        <v>1180454.545454545</v>
       </c>
       <c r="AO12" t="n">
-        <v>69.80165289256198</v>
+        <v>69.87272727272727</v>
       </c>
       <c r="AP12" t="n">
-        <v>26.4414631668933</v>
+        <v>26.45082687488698</v>
       </c>
       <c r="AQ12" t="n">
-        <v>179.5150468715453</v>
+        <v>179.3100298195695</v>
       </c>
       <c r="AR12" t="n">
         <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>67.28170106586172</v>
+        <v>67.32726247679572</v>
       </c>
       <c r="AT12" t="n">
-        <v>1725852.07901582</v>
+        <v>1739937.286917402</v>
       </c>
       <c r="AU12" t="n">
-        <v>69.64167702534361</v>
+        <v>69.67975777135624</v>
       </c>
       <c r="AV12" t="n">
-        <v>24.57734727134041</v>
+        <v>24.61127247466492</v>
       </c>
       <c r="AW12" t="n">
-        <v>180.0279639315681</v>
+        <v>180.0212365152011</v>
       </c>
       <c r="AX12" t="n">
         <v>1</v>
       </c>
       <c r="AY12" t="n">
-        <v>64.01881342024363</v>
+        <v>64.03498047655371</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1197046.509141761</v>
+        <v>1194274.969579746</v>
       </c>
       <c r="BA12" t="n">
-        <v>70.01258515194444</v>
+        <v>70.09479604809124</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -2512,7 +2764,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
@@ -2559,37 +2811,65 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>197</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3325000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>206</v>
+      </c>
+      <c r="W13" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>172</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18900000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>155</v>
+      </c>
       <c r="AD13" t="n">
-        <v>26.50513468013468</v>
+        <v>26.50973370064279</v>
       </c>
       <c r="AE13" t="n">
-        <v>180.6112794612795</v>
+        <v>180.6089990817264</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>68.87929292929293</v>
+        <v>68.94269972451791</v>
       </c>
       <c r="AH13" t="n">
-        <v>2444636.363636364</v>
+        <v>2500595.041322314</v>
       </c>
       <c r="AI13" t="n">
-        <v>72.42516835016835</v>
+        <v>72.51340679522497</v>
       </c>
       <c r="AJ13" t="n">
         <v>26.42083333333333</v>
@@ -2610,22 +2890,22 @@
         <v>74.17416666666665</v>
       </c>
       <c r="AP13" t="n">
-        <v>25.65482804232805</v>
+        <v>25.65981240981241</v>
       </c>
       <c r="AQ13" t="n">
-        <v>180.6182309638832</v>
+        <v>180.5198883242362</v>
       </c>
       <c r="AR13" t="n">
         <v>1</v>
       </c>
       <c r="AS13" t="n">
-        <v>65.99736743731309</v>
+        <v>66.02894629525063</v>
       </c>
       <c r="AT13" t="n">
-        <v>1526651.066827697</v>
+        <v>1533505.709266579</v>
       </c>
       <c r="AU13" t="n">
-        <v>70.33711036346905</v>
+        <v>70.34957494196624</v>
       </c>
       <c r="AV13" t="n">
         <v>24.02631308663816</v>
@@ -2667,7 +2947,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
@@ -2729,84 +3009,98 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6775000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>278</v>
+      </c>
       <c r="AD14" t="n">
-        <v>26.7968253968254</v>
+        <v>26.75042735042735</v>
       </c>
       <c r="AE14" t="n">
-        <v>178.9045634920635</v>
+        <v>178.7895299145299</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.228571428571428</v>
+        <v>1.230769230769231</v>
       </c>
       <c r="AG14" t="n">
-        <v>68.7220238095238</v>
+        <v>68.68525641025641</v>
       </c>
       <c r="AH14" t="n">
-        <v>2021661.706349206</v>
+        <v>2021981.837606838</v>
       </c>
       <c r="AI14" t="n">
-        <v>72.56825396825397</v>
+        <v>72.58119658119658</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25.1</v>
+        <v>25.04040404040404</v>
       </c>
       <c r="AK14" t="n">
-        <v>181.8090909090909</v>
+        <v>181.6767676767677</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.063636363636364</v>
+        <v>1.070707070707071</v>
       </c>
       <c r="AM14" t="n">
-        <v>67.66363636363636</v>
+        <v>67.60606060606061</v>
       </c>
       <c r="AN14" t="n">
-        <v>2407272.727272728</v>
+        <v>2416919.191919192</v>
       </c>
       <c r="AO14" t="n">
-        <v>72.02727272727273</v>
+        <v>72.06060606060606</v>
       </c>
       <c r="AP14" t="n">
-        <v>23.85587126917892</v>
+        <v>23.85288160972304</v>
       </c>
       <c r="AQ14" t="n">
-        <v>178.3148709560102</v>
+        <v>178.3471889647721</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.09323959942482</v>
+        <v>1.084217544319846</v>
       </c>
       <c r="AS14" t="n">
-        <v>63.16177276402552</v>
+        <v>63.18636257178457</v>
       </c>
       <c r="AT14" t="n">
-        <v>1392433.157053821</v>
+        <v>1407336.922171321</v>
       </c>
       <c r="AU14" t="n">
-        <v>69.73043520230365</v>
+        <v>69.77042819357396</v>
       </c>
       <c r="AV14" t="n">
-        <v>26.3531794406966</v>
+        <v>26.4158134136395</v>
       </c>
       <c r="AW14" t="n">
-        <v>181.0415329578888</v>
+        <v>181.116323169584</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.143556272103183</v>
+        <v>1.141963109354414</v>
       </c>
       <c r="AY14" t="n">
-        <v>65.89872009569379</v>
+        <v>66.02196969696969</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1427711.637790127</v>
+        <v>1468510.006901311</v>
       </c>
       <c r="BA14" t="n">
-        <v>69.4474534904455</v>
+        <v>69.53810621745404</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -2830,8 +3124,8 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">allatin m 
+  usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2885,13 +3179,27 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>137</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>137</v>
+      </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -2900,22 +3208,22 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
-        <v>25.67181818181819</v>
+        <v>25.81313131313131</v>
       </c>
       <c r="AE15" t="n">
-        <v>177.1909090909091</v>
+        <v>177.1565656565657</v>
       </c>
       <c r="AF15" t="n">
         <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>68.94727272727273</v>
+        <v>69.03030303030303</v>
       </c>
       <c r="AH15" t="n">
-        <v>2670090.909090909</v>
+        <v>2684267.676767677</v>
       </c>
       <c r="AI15" t="n">
-        <v>71.83727272727273</v>
+        <v>71.83030303030303</v>
       </c>
       <c r="AJ15" t="n">
         <v>25.52313131313131</v>
@@ -2936,22 +3244,22 @@
         <v>71.52818181818182</v>
       </c>
       <c r="AP15" t="n">
-        <v>24.9841533180778</v>
+        <v>24.83424442749386</v>
       </c>
       <c r="AQ15" t="n">
-        <v>177.7262194435364</v>
+        <v>177.5793972653049</v>
       </c>
       <c r="AR15" t="n">
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>64.98816888235079</v>
+        <v>64.89690722377603</v>
       </c>
       <c r="AT15" t="n">
-        <v>1051843.875994334</v>
+        <v>1063953.513009577</v>
       </c>
       <c r="AU15" t="n">
-        <v>69.31582089281173</v>
+        <v>69.34562109783315</v>
       </c>
       <c r="AV15" t="n">
         <v>23.94140077801456</v>
@@ -3063,76 +3371,76 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
-        <v>25.26818181818182</v>
+        <v>25.63506493506494</v>
       </c>
       <c r="AE16" t="n">
-        <v>180.4727272727273</v>
+        <v>180.1545454545455</v>
       </c>
       <c r="AF16" t="n">
         <v>1</v>
       </c>
       <c r="AG16" t="n">
-        <v>68.3659090909091</v>
+        <v>68.86103896103897</v>
       </c>
       <c r="AH16" t="n">
-        <v>3131392.045454545</v>
+        <v>3372662.337662338</v>
       </c>
       <c r="AI16" t="n">
-        <v>72.69204545454545</v>
+        <v>72.7909090909091</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27.80165289256198</v>
+        <v>27.78181818181818</v>
       </c>
       <c r="AK16" t="n">
-        <v>183.9173553719008</v>
+        <v>184.0090909090909</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.165289256198347</v>
+        <v>1.172727272727273</v>
       </c>
       <c r="AM16" t="n">
-        <v>69.28925619834712</v>
+        <v>69.33636363636364</v>
       </c>
       <c r="AN16" t="n">
-        <v>3259090.909090909</v>
+        <v>3287272.727272728</v>
       </c>
       <c r="AO16" t="n">
-        <v>71.09917355371901</v>
+        <v>71.11818181818182</v>
       </c>
       <c r="AP16" t="n">
-        <v>24.33802787419315</v>
+        <v>24.10060328479218</v>
       </c>
       <c r="AQ16" t="n">
-        <v>180.9723922177567</v>
+        <v>181.3597525966909</v>
       </c>
       <c r="AR16" t="n">
         <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>65.03660295639995</v>
+        <v>64.4952480992397</v>
       </c>
       <c r="AT16" t="n">
-        <v>1911195.794894045</v>
+        <v>1538416.312177045</v>
       </c>
       <c r="AU16" t="n">
-        <v>70.87722833698697</v>
+        <v>70.67956530438262</v>
       </c>
       <c r="AV16" t="n">
-        <v>27.60005409610153</v>
+        <v>27.51658124484211</v>
       </c>
       <c r="AW16" t="n">
-        <v>182.8966305433696</v>
+        <v>182.7862935977066</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.050919271769074</v>
+        <v>1.042967720685112</v>
       </c>
       <c r="AY16" t="n">
-        <v>65.31591613261573</v>
+        <v>65.20837731109471</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1190932.419030245</v>
+        <v>1180460.443541965</v>
       </c>
       <c r="BA16" t="n">
-        <v>66.50598150202893</v>
+        <v>66.44788400005791</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -3226,76 +3534,76 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>25.94462809917355</v>
+        <v>25.92090909090909</v>
       </c>
       <c r="AE17" t="n">
-        <v>182.3898071625344</v>
+        <v>182.610606060606</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.008264462809917</v>
+        <v>1.009090909090909</v>
       </c>
       <c r="AG17" t="n">
-        <v>66.14003673094582</v>
+        <v>66.05404040404041</v>
       </c>
       <c r="AH17" t="n">
-        <v>1602788.337924701</v>
+        <v>1559339.898989899</v>
       </c>
       <c r="AI17" t="n">
-        <v>71.02240587695132</v>
+        <v>70.98828282828283</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27.37</v>
+        <v>27.41111111111111</v>
       </c>
       <c r="AK17" t="n">
-        <v>182.0390909090909</v>
+        <v>182.0767676767677</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.753636363636363</v>
+        <v>1.75959595959596</v>
       </c>
       <c r="AM17" t="n">
-        <v>73.84</v>
+        <v>73.87777777777779</v>
       </c>
       <c r="AN17" t="n">
-        <v>6696227.272727272</v>
+        <v>6643585.858585859</v>
       </c>
       <c r="AO17" t="n">
-        <v>77.55</v>
+        <v>77.57777777777778</v>
       </c>
       <c r="AP17" t="n">
-        <v>26.37666089851918</v>
+        <v>26.50004127408539</v>
       </c>
       <c r="AQ17" t="n">
-        <v>181.3269249021923</v>
+        <v>181.2310459638401</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.094407019005949</v>
+        <v>1.103847720906544</v>
       </c>
       <c r="AS17" t="n">
-        <v>65.67699184356938</v>
+        <v>65.6256434088787</v>
       </c>
       <c r="AT17" t="n">
-        <v>1736085.048826693</v>
+        <v>1705455.458471267</v>
       </c>
       <c r="AU17" t="n">
-        <v>70.1953940667176</v>
+        <v>70.09112394957984</v>
       </c>
       <c r="AV17" t="n">
-        <v>24.19655674390969</v>
+        <v>24.05172971545521</v>
       </c>
       <c r="AW17" t="n">
-        <v>184.2788071895425</v>
+        <v>184.2958968772694</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.13625</v>
+        <v>1.088888888888889</v>
       </c>
       <c r="AY17" t="n">
-        <v>67.32904114676174</v>
+        <v>66.98365682973525</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2497732.36036839</v>
+        <v>2245049.844853766</v>
       </c>
       <c r="BA17" t="n">
-        <v>73.68435308972074</v>
+        <v>73.43400343302305</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -3385,76 +3693,76 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>26.33553719008264</v>
+        <v>26.36909090909091</v>
       </c>
       <c r="AE18" t="n">
-        <v>184.5619834710744</v>
+        <v>184.6181818181818</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.091735537190083</v>
+        <v>1.091818181818182</v>
       </c>
       <c r="AG18" t="n">
-        <v>66.12892561983472</v>
+        <v>66.12363636363636</v>
       </c>
       <c r="AH18" t="n">
-        <v>1300818.181818182</v>
+        <v>1288945.454545455</v>
       </c>
       <c r="AI18" t="n">
-        <v>70.36776859504131</v>
+        <v>70.38636363636363</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25.00454545454546</v>
+        <v>24.7939393939394</v>
       </c>
       <c r="AK18" t="n">
-        <v>179.5445454545455</v>
+        <v>179.6828282828283</v>
       </c>
       <c r="AL18" t="n">
         <v>1</v>
       </c>
       <c r="AM18" t="n">
-        <v>69</v>
+        <v>68.85555555555555</v>
       </c>
       <c r="AN18" t="n">
-        <v>3818140.909090909</v>
+        <v>3821267.676767677</v>
       </c>
       <c r="AO18" t="n">
-        <v>73.45363636363636</v>
+        <v>73.5929292929293</v>
       </c>
       <c r="AP18" t="n">
-        <v>23.20697987473951</v>
+        <v>23.1688543328017</v>
       </c>
       <c r="AQ18" t="n">
-        <v>182.4942501083368</v>
+        <v>182.3730868838764</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.014380648591175</v>
+        <v>1.015818713450293</v>
       </c>
       <c r="AS18" t="n">
-        <v>61.80556105869925</v>
+        <v>61.85670539986329</v>
       </c>
       <c r="AT18" t="n">
-        <v>885170.3845377502</v>
+        <v>911540.3641679958</v>
       </c>
       <c r="AU18" t="n">
-        <v>71.00139593027292</v>
+        <v>70.92506493506492</v>
       </c>
       <c r="AV18" t="n">
-        <v>24.61748508098892</v>
+        <v>24.63979823813584</v>
       </c>
       <c r="AW18" t="n">
-        <v>181.3933716965047</v>
+        <v>181.5852278109311</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
       </c>
       <c r="AY18" t="n">
-        <v>61.78537936913897</v>
+        <v>61.77542152126552</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1350476.417306053</v>
+        <v>1247427.500710429</v>
       </c>
       <c r="BA18" t="n">
-        <v>67.04961423699915</v>
+        <v>67.09679359666572</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -3544,76 +3852,76 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
-        <v>23.10956790123457</v>
+        <v>23.13888888888889</v>
       </c>
       <c r="AE19" t="n">
-        <v>182.6851851851852</v>
+        <v>182.5052083333333</v>
       </c>
       <c r="AF19" t="n">
         <v>1</v>
       </c>
       <c r="AG19" t="n">
-        <v>65.90895061728396</v>
+        <v>65.81944444444446</v>
       </c>
       <c r="AH19" t="n">
-        <v>1543217.592592593</v>
+        <v>1529869.791666667</v>
       </c>
       <c r="AI19" t="n">
-        <v>71.75308641975309</v>
+        <v>71.59722222222223</v>
       </c>
       <c r="AJ19" t="n">
-        <v>23.63636363636364</v>
+        <v>23.53636363636364</v>
       </c>
       <c r="AK19" t="n">
-        <v>179.2809917355372</v>
+        <v>179.3</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.016528925619835</v>
+        <v>1.018181818181818</v>
       </c>
       <c r="AM19" t="n">
-        <v>65.60330578512396</v>
+        <v>65.54545454545455</v>
       </c>
       <c r="AN19" t="n">
-        <v>1267768.595041322</v>
+        <v>1271363.636363636</v>
       </c>
       <c r="AO19" t="n">
-        <v>71.36363636363636</v>
+        <v>71.47272727272727</v>
       </c>
       <c r="AP19" t="n">
-        <v>21.55911397594195</v>
+        <v>21.42800103607076</v>
       </c>
       <c r="AQ19" t="n">
-        <v>181.0105813825426</v>
+        <v>181.0745590240812</v>
       </c>
       <c r="AR19" t="n">
         <v>1</v>
       </c>
       <c r="AS19" t="n">
-        <v>62.53305314553531</v>
+        <v>62.4763392438315</v>
       </c>
       <c r="AT19" t="n">
-        <v>1357813.972576757</v>
+        <v>1375662.868080455</v>
       </c>
       <c r="AU19" t="n">
-        <v>71.51192892717728</v>
+        <v>71.68958286594577</v>
       </c>
       <c r="AV19" t="n">
-        <v>23.22591499409681</v>
+        <v>23.30267316017316</v>
       </c>
       <c r="AW19" t="n">
-        <v>180.5855485821993</v>
+        <v>180.6566034404192</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.097405704343503</v>
+        <v>1.102979608111187</v>
       </c>
       <c r="AY19" t="n">
-        <v>64.90665299612668</v>
+        <v>65.01815162907266</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1335678.698295325</v>
+        <v>1357684.068124857</v>
       </c>
       <c r="BA19" t="n">
-        <v>71.5697855175128</v>
+        <v>71.58093073593074</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
@@ -3707,76 +4015,76 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
-        <v>26.19421487603306</v>
+        <v>26.12272727272727</v>
       </c>
       <c r="AE20" t="n">
-        <v>182.4801652892562</v>
+        <v>182.4281818181818</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.202479338842975</v>
+        <v>1.213636363636364</v>
       </c>
       <c r="AG20" t="n">
-        <v>64.58677685950414</v>
+        <v>64.49090909090908</v>
       </c>
       <c r="AH20" t="n">
-        <v>2112826.446280992</v>
+        <v>2153018.181818182</v>
       </c>
       <c r="AI20" t="n">
-        <v>67.92727272727274</v>
+        <v>67.84727272727272</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26.67685950413223</v>
+        <v>26.78454545454546</v>
       </c>
       <c r="AK20" t="n">
-        <v>179.7090909090909</v>
+        <v>179.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.231404958677686</v>
+        <v>1.254545454545455</v>
       </c>
       <c r="AM20" t="n">
-        <v>69.71487603305785</v>
+        <v>69.70636363636363</v>
       </c>
       <c r="AN20" t="n">
-        <v>2958000</v>
+        <v>2999050</v>
       </c>
       <c r="AO20" t="n">
-        <v>72.6694214876033</v>
+        <v>72.59636363636363</v>
       </c>
       <c r="AP20" t="n">
-        <v>23.2054606212501</v>
+        <v>23.30219715956558</v>
       </c>
       <c r="AQ20" t="n">
-        <v>178.6450216450216</v>
+        <v>178.6619047619047</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.146240601503759</v>
+        <v>1.160864661654135</v>
       </c>
       <c r="AS20" t="n">
-        <v>62.98931419457734</v>
+        <v>63.18348370927318</v>
       </c>
       <c r="AT20" t="n">
-        <v>1573240.354674566</v>
+        <v>1659254.866332498</v>
       </c>
       <c r="AU20" t="n">
-        <v>69.22209311156679</v>
+        <v>69.38239766081873</v>
       </c>
       <c r="AV20" t="n">
-        <v>25.41277671573197</v>
+        <v>25.17310200635278</v>
       </c>
       <c r="AW20" t="n">
-        <v>179.8521557905459</v>
+        <v>179.86118089341</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.153747579936716</v>
+        <v>1.126265195073245</v>
       </c>
       <c r="AY20" t="n">
-        <v>64.57245684702764</v>
+        <v>64.3297025317304</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2632059.859176381</v>
+        <v>2591051.559379733</v>
       </c>
       <c r="BA20" t="n">
-        <v>69.42460886050812</v>
+        <v>69.41945069893987</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
@@ -3862,76 +4170,76 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
-        <v>26.48035914702582</v>
+        <v>26.34040404040404</v>
       </c>
       <c r="AE21" t="n">
-        <v>181.016835016835</v>
+        <v>180.9939393939394</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.097194163860831</v>
+        <v>1.096843434343434</v>
       </c>
       <c r="AG21" t="n">
-        <v>68.87205387205387</v>
+        <v>68.7560606060606</v>
       </c>
       <c r="AH21" t="n">
-        <v>3112985.409652076</v>
+        <v>3075858.585858586</v>
       </c>
       <c r="AI21" t="n">
-        <v>71.81324354657689</v>
+        <v>71.93989898989899</v>
       </c>
       <c r="AJ21" t="n">
-        <v>25.90087412587413</v>
+        <v>25.97594696969697</v>
       </c>
       <c r="AK21" t="n">
-        <v>179.4230769230769</v>
+        <v>179.4507575757576</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.175524475524476</v>
+        <v>1.167424242424243</v>
       </c>
       <c r="AM21" t="n">
-        <v>67.23374125874126</v>
+        <v>67.11685606060605</v>
       </c>
       <c r="AN21" t="n">
-        <v>4023791.083916084</v>
+        <v>3824334.28030303</v>
       </c>
       <c r="AO21" t="n">
-        <v>72.07412587412588</v>
+        <v>71.89090909090909</v>
       </c>
       <c r="AP21" t="n">
-        <v>25.54344898928232</v>
+        <v>25.61919261294261</v>
       </c>
       <c r="AQ21" t="n">
-        <v>181.4421040923492</v>
+        <v>181.7083046038928</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.108652748848827</v>
+        <v>1.122234342454931</v>
       </c>
       <c r="AS21" t="n">
-        <v>66.22410569640962</v>
+        <v>66.29118140846083</v>
       </c>
       <c r="AT21" t="n">
-        <v>1460147.323174284</v>
+        <v>1492275.113571069</v>
       </c>
       <c r="AU21" t="n">
-        <v>71.87919589488217</v>
+        <v>72.05159538174244</v>
       </c>
       <c r="AV21" t="n">
-        <v>25.75187049009323</v>
+        <v>25.67727146230688</v>
       </c>
       <c r="AW21" t="n">
-        <v>179.8382584052673</v>
+        <v>179.9767407233533</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03751056635672</v>
+        <v>1.040636446886447</v>
       </c>
       <c r="AY21" t="n">
-        <v>65.72562230722339</v>
+        <v>65.67824769557043</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2103155.305903589</v>
+        <v>2142756.483356339</v>
       </c>
       <c r="BA21" t="n">
-        <v>70.48947342993273</v>
+        <v>70.50575307850555</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -4025,76 +4333,76 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="n">
-        <v>25.1</v>
+        <v>25.04040404040404</v>
       </c>
       <c r="AE22" t="n">
-        <v>181.8090909090909</v>
+        <v>181.6767676767677</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.063636363636364</v>
+        <v>1.070707070707071</v>
       </c>
       <c r="AG22" t="n">
-        <v>67.66363636363636</v>
+        <v>67.60606060606061</v>
       </c>
       <c r="AH22" t="n">
-        <v>2407272.727272728</v>
+        <v>2416919.191919192</v>
       </c>
       <c r="AI22" t="n">
-        <v>72.02727272727273</v>
+        <v>72.06060606060606</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25.70648148148148</v>
+        <v>25.62525252525252</v>
       </c>
       <c r="AK22" t="n">
-        <v>183.6495791245792</v>
+        <v>183.7086317722681</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.066666666666667</v>
+        <v>1.054545454545455</v>
       </c>
       <c r="AM22" t="n">
-        <v>69.34503367003367</v>
+        <v>69.08549127640036</v>
       </c>
       <c r="AN22" t="n">
-        <v>2970762.626262626</v>
+        <v>2903104.683195592</v>
       </c>
       <c r="AO22" t="n">
-        <v>73.03569023569024</v>
+        <v>72.80257116620754</v>
       </c>
       <c r="AP22" t="n">
-        <v>26.3531794406966</v>
+        <v>26.4158134136395</v>
       </c>
       <c r="AQ22" t="n">
-        <v>181.0415329578888</v>
+        <v>181.116323169584</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.143556272103183</v>
+        <v>1.141963109354414</v>
       </c>
       <c r="AS22" t="n">
-        <v>65.89872009569379</v>
+        <v>66.02196969696969</v>
       </c>
       <c r="AT22" t="n">
-        <v>1427711.637790127</v>
+        <v>1468510.006901311</v>
       </c>
       <c r="AU22" t="n">
-        <v>69.4474534904455</v>
+        <v>69.53810621745404</v>
       </c>
       <c r="AV22" t="n">
-        <v>24.50724933802394</v>
+        <v>24.52495382329884</v>
       </c>
       <c r="AW22" t="n">
-        <v>181.1947520257802</v>
+        <v>181.0988203917602</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.070842992369361</v>
+        <v>1.07728326440294</v>
       </c>
       <c r="AY22" t="n">
-        <v>65.2882518238185</v>
+        <v>65.3030928987111</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1590171.859358947</v>
+        <v>1594335.210209761</v>
       </c>
       <c r="BA22" t="n">
-        <v>70.88647381326133</v>
+        <v>70.95569870537601</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
@@ -4188,76 +4496,76 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
-        <v>26.07438016528926</v>
+        <v>25.97272727272728</v>
       </c>
       <c r="AE23" t="n">
-        <v>181.595041322314</v>
+        <v>181.6181818181818</v>
       </c>
       <c r="AF23" t="n">
         <v>1</v>
       </c>
       <c r="AG23" t="n">
-        <v>65.57851239669422</v>
+        <v>65.53636363636363</v>
       </c>
       <c r="AH23" t="n">
-        <v>1191322.314049587</v>
+        <v>1180454.545454545</v>
       </c>
       <c r="AI23" t="n">
-        <v>69.80165289256198</v>
+        <v>69.87272727272727</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25.67181818181819</v>
+        <v>25.81313131313131</v>
       </c>
       <c r="AK23" t="n">
-        <v>177.1909090909091</v>
+        <v>177.1565656565657</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>68.94727272727273</v>
+        <v>69.03030303030303</v>
       </c>
       <c r="AN23" t="n">
-        <v>2670090.909090909</v>
+        <v>2684267.676767677</v>
       </c>
       <c r="AO23" t="n">
-        <v>71.83727272727273</v>
+        <v>71.83030303030303</v>
       </c>
       <c r="AP23" t="n">
-        <v>24.57734727134041</v>
+        <v>24.61127247466492</v>
       </c>
       <c r="AQ23" t="n">
-        <v>180.0279639315681</v>
+        <v>180.0212365152011</v>
       </c>
       <c r="AR23" t="n">
         <v>1</v>
       </c>
       <c r="AS23" t="n">
-        <v>64.01881342024363</v>
+        <v>64.03498047655371</v>
       </c>
       <c r="AT23" t="n">
-        <v>1197046.509141761</v>
+        <v>1194274.969579746</v>
       </c>
       <c r="AU23" t="n">
-        <v>70.01258515194444</v>
+        <v>70.09479604809124</v>
       </c>
       <c r="AV23" t="n">
-        <v>24.9841533180778</v>
+        <v>24.83424442749386</v>
       </c>
       <c r="AW23" t="n">
-        <v>177.7262194435364</v>
+        <v>177.5793972653049</v>
       </c>
       <c r="AX23" t="n">
         <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>64.98816888235079</v>
+        <v>64.89690722377603</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1051843.875994334</v>
+        <v>1063953.513009577</v>
       </c>
       <c r="BA23" t="n">
-        <v>69.31582089281173</v>
+        <v>69.34562109783315</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
@@ -4365,22 +4673,22 @@
         <v>71.52818181818182</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26.50513468013468</v>
+        <v>26.50973370064279</v>
       </c>
       <c r="AK24" t="n">
-        <v>180.6112794612795</v>
+        <v>180.6089990817264</v>
       </c>
       <c r="AL24" t="n">
         <v>1</v>
       </c>
       <c r="AM24" t="n">
-        <v>68.87929292929293</v>
+        <v>68.94269972451791</v>
       </c>
       <c r="AN24" t="n">
-        <v>2444636.363636364</v>
+        <v>2500595.041322314</v>
       </c>
       <c r="AO24" t="n">
-        <v>72.42516835016835</v>
+        <v>72.51340679522497</v>
       </c>
       <c r="AP24" t="n">
         <v>23.94140077801456</v>
@@ -4401,22 +4709,22 @@
         <v>69.84434753327169</v>
       </c>
       <c r="AV24" t="n">
-        <v>25.65482804232805</v>
+        <v>25.65981240981241</v>
       </c>
       <c r="AW24" t="n">
-        <v>180.6182309638832</v>
+        <v>180.5198883242362</v>
       </c>
       <c r="AX24" t="n">
         <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>65.99736743731309</v>
+        <v>66.02894629525063</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1526651.066827697</v>
+        <v>1533505.709266579</v>
       </c>
       <c r="BA24" t="n">
-        <v>70.33711036346905</v>
+        <v>70.34957494196624</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
@@ -4510,76 +4818,76 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="n">
-        <v>24.40075757575758</v>
+        <v>24.38264462809917</v>
       </c>
       <c r="AE25" t="n">
-        <v>178.9327441077441</v>
+        <v>178.9266299357208</v>
       </c>
       <c r="AF25" t="n">
         <v>1</v>
       </c>
       <c r="AG25" t="n">
-        <v>66.04755892255893</v>
+        <v>65.99733700642793</v>
       </c>
       <c r="AH25" t="n">
-        <v>1930372.474747475</v>
+        <v>1909951.790633609</v>
       </c>
       <c r="AI25" t="n">
-        <v>72.55101010101009</v>
+        <v>72.5556473829201</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26.79318181818182</v>
+        <v>26.90661157024794</v>
       </c>
       <c r="AK25" t="n">
-        <v>180.5780303030303</v>
+        <v>180.7297520661157</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.153030303030303</v>
+        <v>1.166942148760331</v>
       </c>
       <c r="AM25" t="n">
-        <v>67.71363636363635</v>
+        <v>67.78677685950413</v>
       </c>
       <c r="AN25" t="n">
-        <v>1829492.424242425</v>
+        <v>1879652.892561984</v>
       </c>
       <c r="AO25" t="n">
-        <v>70.73939393939393</v>
+        <v>70.75702479338842</v>
       </c>
       <c r="AP25" t="n">
-        <v>24.74314626110082</v>
+        <v>24.61284404954314</v>
       </c>
       <c r="AQ25" t="n">
-        <v>178.7516843533312</v>
+        <v>178.6809818613881</v>
       </c>
       <c r="AR25" t="n">
         <v>1</v>
       </c>
       <c r="AS25" t="n">
-        <v>63.79586524871346</v>
+        <v>63.72917920180507</v>
       </c>
       <c r="AT25" t="n">
-        <v>1494232.098642793</v>
+        <v>1525285.284080908</v>
       </c>
       <c r="AU25" t="n">
-        <v>70.26155345389344</v>
+        <v>70.3869353186859</v>
       </c>
       <c r="AV25" t="n">
-        <v>25.67065089436371</v>
+        <v>25.41993084579937</v>
       </c>
       <c r="AW25" t="n">
-        <v>179.8500226191302</v>
+        <v>179.6805441559342</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.093092937658155</v>
+        <v>1.075581906016688</v>
       </c>
       <c r="AY25" t="n">
-        <v>64.27877445039915</v>
+        <v>64.01840329653933</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1270407.761691228</v>
+        <v>1201462.146953202</v>
       </c>
       <c r="BA25" t="n">
-        <v>68.5116460315259</v>
+        <v>68.50188225084209</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
@@ -4673,76 +4981,76 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="n">
-        <v>25.68461538461538</v>
+        <v>25.64166666666667</v>
       </c>
       <c r="AE26" t="n">
-        <v>182.33006993007</v>
+        <v>182.2909090909091</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.066433566433566</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="AG26" t="n">
-        <v>67.62027972027971</v>
+        <v>67.5719696969697</v>
       </c>
       <c r="AH26" t="n">
-        <v>2691825.174825174</v>
+        <v>2702393.939393939</v>
       </c>
       <c r="AI26" t="n">
-        <v>71.45594405594406</v>
+        <v>71.45227272727273</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26.60330578512396</v>
+        <v>26.59090909090909</v>
       </c>
       <c r="AK26" t="n">
-        <v>178.595041322314</v>
+        <v>178.7909090909091</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>69.72727272727273</v>
+        <v>69.66363636363636</v>
       </c>
       <c r="AN26" t="n">
-        <v>2824834.710743802</v>
+        <v>2848909.090909091</v>
       </c>
       <c r="AO26" t="n">
-        <v>72.3801652892562</v>
+        <v>72.32727272727273</v>
       </c>
       <c r="AP26" t="n">
-        <v>24.84679767219813</v>
+        <v>24.88561811313528</v>
       </c>
       <c r="AQ26" t="n">
-        <v>180.243165739676</v>
+        <v>180.3666041544903</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.029688351313065</v>
+        <v>1.0281941266209</v>
       </c>
       <c r="AS26" t="n">
-        <v>63.3128493169683</v>
+        <v>63.1603486648109</v>
       </c>
       <c r="AT26" t="n">
-        <v>1488422.15874324</v>
+        <v>1398727.179908351</v>
       </c>
       <c r="AU26" t="n">
-        <v>69.28995175305243</v>
+        <v>69.15141598644173</v>
       </c>
       <c r="AV26" t="n">
-        <v>26.4414631668933</v>
+        <v>26.45082687488698</v>
       </c>
       <c r="AW26" t="n">
-        <v>179.5150468715453</v>
+        <v>179.3100298195695</v>
       </c>
       <c r="AX26" t="n">
         <v>1</v>
       </c>
       <c r="AY26" t="n">
-        <v>67.28170106586172</v>
+        <v>67.32726247679572</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1725852.07901582</v>
+        <v>1739937.286917402</v>
       </c>
       <c r="BA26" t="n">
-        <v>69.64167702534361</v>
+        <v>69.67975777135624</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
@@ -4836,76 +5144,76 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="n">
-        <v>24.10909090909091</v>
+        <v>24.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>180.2181818181818</v>
+        <v>180.07</v>
       </c>
       <c r="AF27" t="n">
         <v>1</v>
       </c>
       <c r="AG27" t="n">
-        <v>65.54545454545455</v>
+        <v>65.61</v>
       </c>
       <c r="AH27" t="n">
-        <v>1664545.454545455</v>
+        <v>1665900</v>
       </c>
       <c r="AI27" t="n">
-        <v>70.65454545454546</v>
+        <v>70.71000000000001</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26.98811188811189</v>
+        <v>26.85378787878788</v>
       </c>
       <c r="AK27" t="n">
-        <v>180.0566433566434</v>
+        <v>180.1280303030303</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.05034965034965</v>
+        <v>1.046212121212121</v>
       </c>
       <c r="AM27" t="n">
-        <v>65.7888111888112</v>
+        <v>65.57954545454545</v>
       </c>
       <c r="AN27" t="n">
-        <v>1155258.741258741</v>
+        <v>1125405.303030303</v>
       </c>
       <c r="AO27" t="n">
-        <v>68.8944055944056</v>
+        <v>68.76893939393939</v>
       </c>
       <c r="AP27" t="n">
-        <v>22.00460505677897</v>
+        <v>22.13284334023464</v>
       </c>
       <c r="AQ27" t="n">
-        <v>180.0500345065562</v>
+        <v>180.1050379572118</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>60.12587991718426</v>
+        <v>60.41624568668046</v>
       </c>
       <c r="AT27" t="n">
-        <v>771341.3325804631</v>
+        <v>796169.9102829538</v>
       </c>
       <c r="AU27" t="n">
-        <v>69.14493381015122</v>
+        <v>69.25387163561076</v>
       </c>
       <c r="AV27" t="n">
-        <v>25.36563837129055</v>
+        <v>25.3405526800092</v>
       </c>
       <c r="AW27" t="n">
-        <v>180.2409542389977</v>
+        <v>180.075848573729</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.062976057758667</v>
+        <v>1.063594432942259</v>
       </c>
       <c r="AY27" t="n">
-        <v>63.37454822954823</v>
+        <v>63.50298280423281</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1002037.710357275</v>
+        <v>1022022.33436853</v>
       </c>
       <c r="BA27" t="n">
-        <v>67.66753835536444</v>
+        <v>67.78798136645963</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
@@ -5009,22 +5317,22 @@
         <v>74.17416666666665</v>
       </c>
       <c r="AJ28" t="n">
-        <v>27.55361952861953</v>
+        <v>27.50477502295684</v>
       </c>
       <c r="AK28" t="n">
-        <v>180.596127946128</v>
+        <v>180.5924701561065</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.335774410774411</v>
+        <v>1.333241505968779</v>
       </c>
       <c r="AM28" t="n">
-        <v>71.99309764309764</v>
+        <v>71.90156106519743</v>
       </c>
       <c r="AN28" t="n">
-        <v>4189000.420875421</v>
+        <v>4181388.888888889</v>
       </c>
       <c r="AO28" t="n">
-        <v>74.8462962962963</v>
+        <v>74.79100091827364</v>
       </c>
       <c r="AP28" t="n">
         <v>24.02631308663816</v>
@@ -5045,22 +5353,22 @@
         <v>70.35187656641604</v>
       </c>
       <c r="AV28" t="n">
-        <v>25.96729267464562</v>
+        <v>25.79076556242331</v>
       </c>
       <c r="AW28" t="n">
-        <v>179.5308471620972</v>
+        <v>179.3477010363374</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01058201058201</v>
+        <v>1.011544011544012</v>
       </c>
       <c r="AY28" t="n">
-        <v>67.10095466216789</v>
+        <v>67.11013235872862</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1779057.356212687</v>
+        <v>1820748.520827064</v>
       </c>
       <c r="BA28" t="n">
-        <v>72.29551528944911</v>
+        <v>72.34717370419243</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
@@ -5154,76 +5462,76 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="n">
-        <v>23.63636363636364</v>
+        <v>23.53636363636364</v>
       </c>
       <c r="AE29" t="n">
-        <v>179.2809917355372</v>
+        <v>179.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.016528925619835</v>
+        <v>1.018181818181818</v>
       </c>
       <c r="AG29" t="n">
-        <v>65.60330578512396</v>
+        <v>65.54545454545455</v>
       </c>
       <c r="AH29" t="n">
-        <v>1267768.595041322</v>
+        <v>1271363.636363636</v>
       </c>
       <c r="AI29" t="n">
-        <v>71.36363636363636</v>
+        <v>71.47272727272727</v>
       </c>
       <c r="AJ29" t="n">
-        <v>25.67181818181819</v>
+        <v>25.81313131313131</v>
       </c>
       <c r="AK29" t="n">
-        <v>177.1909090909091</v>
+        <v>177.1565656565657</v>
       </c>
       <c r="AL29" t="n">
         <v>1</v>
       </c>
       <c r="AM29" t="n">
-        <v>68.94727272727273</v>
+        <v>69.03030303030303</v>
       </c>
       <c r="AN29" t="n">
-        <v>2670090.909090909</v>
+        <v>2684267.676767677</v>
       </c>
       <c r="AO29" t="n">
-        <v>71.83727272727273</v>
+        <v>71.83030303030303</v>
       </c>
       <c r="AP29" t="n">
-        <v>23.22591499409681</v>
+        <v>23.30267316017316</v>
       </c>
       <c r="AQ29" t="n">
-        <v>180.5855485821993</v>
+        <v>180.6566034404192</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.097405704343503</v>
+        <v>1.102979608111187</v>
       </c>
       <c r="AS29" t="n">
-        <v>64.90665299612668</v>
+        <v>65.01815162907266</v>
       </c>
       <c r="AT29" t="n">
-        <v>1335678.698295325</v>
+        <v>1357684.068124857</v>
       </c>
       <c r="AU29" t="n">
-        <v>71.5697855175128</v>
+        <v>71.58093073593074</v>
       </c>
       <c r="AV29" t="n">
-        <v>24.9841533180778</v>
+        <v>24.83424442749386</v>
       </c>
       <c r="AW29" t="n">
-        <v>177.7262194435364</v>
+        <v>177.5793972653049</v>
       </c>
       <c r="AX29" t="n">
         <v>1</v>
       </c>
       <c r="AY29" t="n">
-        <v>64.98816888235079</v>
+        <v>64.89690722377603</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1051843.875994334</v>
+        <v>1063953.513009577</v>
       </c>
       <c r="BA29" t="n">
-        <v>69.31582089281173</v>
+        <v>69.34562109783315</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
@@ -5317,76 +5625,76 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="n">
-        <v>25.26818181818182</v>
+        <v>25.63506493506494</v>
       </c>
       <c r="AE30" t="n">
-        <v>180.4727272727273</v>
+        <v>180.1545454545455</v>
       </c>
       <c r="AF30" t="n">
         <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>68.3659090909091</v>
+        <v>68.86103896103897</v>
       </c>
       <c r="AH30" t="n">
-        <v>3131392.045454545</v>
+        <v>3372662.337662338</v>
       </c>
       <c r="AI30" t="n">
-        <v>72.69204545454545</v>
+        <v>72.7909090909091</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26.19421487603306</v>
+        <v>26.12272727272727</v>
       </c>
       <c r="AK30" t="n">
-        <v>182.4801652892562</v>
+        <v>182.4281818181818</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.202479338842975</v>
+        <v>1.213636363636364</v>
       </c>
       <c r="AM30" t="n">
-        <v>64.58677685950414</v>
+        <v>64.49090909090908</v>
       </c>
       <c r="AN30" t="n">
-        <v>2112826.446280992</v>
+        <v>2153018.181818182</v>
       </c>
       <c r="AO30" t="n">
-        <v>67.92727272727274</v>
+        <v>67.84727272727272</v>
       </c>
       <c r="AP30" t="n">
-        <v>24.33802787419315</v>
+        <v>24.10060328479218</v>
       </c>
       <c r="AQ30" t="n">
-        <v>180.9723922177567</v>
+        <v>181.3597525966909</v>
       </c>
       <c r="AR30" t="n">
         <v>1</v>
       </c>
       <c r="AS30" t="n">
-        <v>65.03660295639995</v>
+        <v>64.4952480992397</v>
       </c>
       <c r="AT30" t="n">
-        <v>1911195.794894045</v>
+        <v>1538416.312177045</v>
       </c>
       <c r="AU30" t="n">
-        <v>70.87722833698697</v>
+        <v>70.67956530438262</v>
       </c>
       <c r="AV30" t="n">
-        <v>23.2054606212501</v>
+        <v>23.30219715956558</v>
       </c>
       <c r="AW30" t="n">
-        <v>178.6450216450216</v>
+        <v>178.6619047619047</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.146240601503759</v>
+        <v>1.160864661654135</v>
       </c>
       <c r="AY30" t="n">
-        <v>62.98931419457734</v>
+        <v>63.18348370927318</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1573240.354674566</v>
+        <v>1659254.866332498</v>
       </c>
       <c r="BA30" t="n">
-        <v>69.22209311156679</v>
+        <v>69.38239766081873</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
@@ -5480,76 +5788,76 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="n">
-        <v>25.00454545454546</v>
+        <v>24.7939393939394</v>
       </c>
       <c r="AE31" t="n">
-        <v>179.5445454545455</v>
+        <v>179.6828282828283</v>
       </c>
       <c r="AF31" t="n">
         <v>1</v>
       </c>
       <c r="AG31" t="n">
-        <v>69</v>
+        <v>68.85555555555555</v>
       </c>
       <c r="AH31" t="n">
-        <v>3818140.909090909</v>
+        <v>3821267.676767677</v>
       </c>
       <c r="AI31" t="n">
-        <v>73.45363636363636</v>
+        <v>73.5929292929293</v>
       </c>
       <c r="AJ31" t="n">
-        <v>27.37</v>
+        <v>27.41111111111111</v>
       </c>
       <c r="AK31" t="n">
-        <v>182.0390909090909</v>
+        <v>182.0767676767677</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.753636363636363</v>
+        <v>1.75959595959596</v>
       </c>
       <c r="AM31" t="n">
-        <v>73.84</v>
+        <v>73.87777777777779</v>
       </c>
       <c r="AN31" t="n">
-        <v>6696227.272727272</v>
+        <v>6643585.858585859</v>
       </c>
       <c r="AO31" t="n">
-        <v>77.55</v>
+        <v>77.57777777777778</v>
       </c>
       <c r="AP31" t="n">
-        <v>24.61748508098892</v>
+        <v>24.63979823813584</v>
       </c>
       <c r="AQ31" t="n">
-        <v>181.3933716965047</v>
+        <v>181.5852278109311</v>
       </c>
       <c r="AR31" t="n">
         <v>1</v>
       </c>
       <c r="AS31" t="n">
-        <v>61.78537936913897</v>
+        <v>61.77542152126552</v>
       </c>
       <c r="AT31" t="n">
-        <v>1350476.417306053</v>
+        <v>1247427.500710429</v>
       </c>
       <c r="AU31" t="n">
-        <v>67.04961423699915</v>
+        <v>67.09679359666572</v>
       </c>
       <c r="AV31" t="n">
-        <v>24.19655674390969</v>
+        <v>24.05172971545521</v>
       </c>
       <c r="AW31" t="n">
-        <v>184.2788071895425</v>
+        <v>184.2958968772694</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.13625</v>
+        <v>1.088888888888889</v>
       </c>
       <c r="AY31" t="n">
-        <v>67.32904114676174</v>
+        <v>66.98365682973525</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2497732.36036839</v>
+        <v>2245049.844853766</v>
       </c>
       <c r="BA31" t="n">
-        <v>73.68435308972074</v>
+        <v>73.43400343302305</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
@@ -5639,76 +5947,76 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="n">
-        <v>26.67685950413223</v>
+        <v>26.78454545454546</v>
       </c>
       <c r="AE32" t="n">
-        <v>179.7090909090909</v>
+        <v>179.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.231404958677686</v>
+        <v>1.254545454545455</v>
       </c>
       <c r="AG32" t="n">
-        <v>69.71487603305785</v>
+        <v>69.70636363636363</v>
       </c>
       <c r="AH32" t="n">
-        <v>2958000</v>
+        <v>2999050</v>
       </c>
       <c r="AI32" t="n">
-        <v>72.6694214876033</v>
+        <v>72.59636363636363</v>
       </c>
       <c r="AJ32" t="n">
-        <v>26.33553719008264</v>
+        <v>26.36909090909091</v>
       </c>
       <c r="AK32" t="n">
-        <v>184.5619834710744</v>
+        <v>184.6181818181818</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.091735537190083</v>
+        <v>1.091818181818182</v>
       </c>
       <c r="AM32" t="n">
-        <v>66.12892561983472</v>
+        <v>66.12363636363636</v>
       </c>
       <c r="AN32" t="n">
-        <v>1300818.181818182</v>
+        <v>1288945.454545455</v>
       </c>
       <c r="AO32" t="n">
-        <v>70.36776859504131</v>
+        <v>70.38636363636363</v>
       </c>
       <c r="AP32" t="n">
-        <v>25.41277671573197</v>
+        <v>25.17310200635278</v>
       </c>
       <c r="AQ32" t="n">
-        <v>179.8521557905459</v>
+        <v>179.86118089341</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.153747579936716</v>
+        <v>1.126265195073245</v>
       </c>
       <c r="AS32" t="n">
-        <v>64.57245684702764</v>
+        <v>64.3297025317304</v>
       </c>
       <c r="AT32" t="n">
-        <v>2632059.859176381</v>
+        <v>2591051.559379733</v>
       </c>
       <c r="AU32" t="n">
-        <v>69.42460886050812</v>
+        <v>69.41945069893987</v>
       </c>
       <c r="AV32" t="n">
-        <v>23.20697987473951</v>
+        <v>23.1688543328017</v>
       </c>
       <c r="AW32" t="n">
-        <v>182.4942501083368</v>
+        <v>182.3730868838764</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.014380648591175</v>
+        <v>1.015818713450293</v>
       </c>
       <c r="AY32" t="n">
-        <v>61.80556105869925</v>
+        <v>61.85670539986329</v>
       </c>
       <c r="AZ32" t="n">
-        <v>885170.3845377502</v>
+        <v>911540.3641679958</v>
       </c>
       <c r="BA32" t="n">
-        <v>71.00139593027292</v>
+        <v>70.92506493506492</v>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
@@ -5798,76 +6106,76 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="n">
-        <v>25.70648148148148</v>
+        <v>25.62525252525252</v>
       </c>
       <c r="AE33" t="n">
-        <v>183.6495791245792</v>
+        <v>183.7086317722681</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.066666666666667</v>
+        <v>1.054545454545455</v>
       </c>
       <c r="AG33" t="n">
-        <v>69.34503367003367</v>
+        <v>69.08549127640036</v>
       </c>
       <c r="AH33" t="n">
-        <v>2970762.626262626</v>
+        <v>2903104.683195592</v>
       </c>
       <c r="AI33" t="n">
-        <v>73.03569023569024</v>
+        <v>72.80257116620754</v>
       </c>
       <c r="AJ33" t="n">
-        <v>22.99917355371901</v>
+        <v>22.98909090909091</v>
       </c>
       <c r="AK33" t="n">
-        <v>179.3239669421488</v>
+        <v>179.2063636363636</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.109090909090909</v>
+        <v>1.1</v>
       </c>
       <c r="AM33" t="n">
-        <v>67.7809917355372</v>
+        <v>67.69909090909091</v>
       </c>
       <c r="AN33" t="n">
-        <v>2817396.694214876</v>
+        <v>2739636.363636364</v>
       </c>
       <c r="AO33" t="n">
-        <v>74.36446280991736</v>
+        <v>74.25090909090909</v>
       </c>
       <c r="AP33" t="n">
-        <v>24.50724933802394</v>
+        <v>24.52495382329884</v>
       </c>
       <c r="AQ33" t="n">
-        <v>181.1947520257802</v>
+        <v>181.0988203917602</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.070842992369361</v>
+        <v>1.07728326440294</v>
       </c>
       <c r="AS33" t="n">
-        <v>65.2882518238185</v>
+        <v>65.3030928987111</v>
       </c>
       <c r="AT33" t="n">
-        <v>1590171.859358947</v>
+        <v>1594335.210209761</v>
       </c>
       <c r="AU33" t="n">
-        <v>70.88647381326133</v>
+        <v>70.95569870537601</v>
       </c>
       <c r="AV33" t="n">
-        <v>23.19050834657089</v>
+        <v>23.14434178992363</v>
       </c>
       <c r="AW33" t="n">
-        <v>180.6628698318654</v>
+        <v>180.929156815052</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.068762021517195</v>
+        <v>1.066942571495001</v>
       </c>
       <c r="AY33" t="n">
-        <v>63.75365960184897</v>
+        <v>63.58989512725126</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1711832.381435119</v>
+        <v>1687493.880448197</v>
       </c>
       <c r="BA33" t="n">
-        <v>71.82951192030477</v>
+        <v>71.84289789494393</v>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
@@ -5975,22 +6283,22 @@
         <v>68.51454545454547</v>
       </c>
       <c r="AJ34" t="n">
-        <v>23.10956790123457</v>
+        <v>23.13888888888889</v>
       </c>
       <c r="AK34" t="n">
-        <v>182.6851851851852</v>
+        <v>182.5052083333333</v>
       </c>
       <c r="AL34" t="n">
         <v>1</v>
       </c>
       <c r="AM34" t="n">
-        <v>65.90895061728396</v>
+        <v>65.81944444444446</v>
       </c>
       <c r="AN34" t="n">
-        <v>1543217.592592593</v>
+        <v>1529869.791666667</v>
       </c>
       <c r="AO34" t="n">
-        <v>71.75308641975309</v>
+        <v>71.59722222222223</v>
       </c>
       <c r="AP34" t="n">
         <v>28.00286226809564</v>
@@ -6011,22 +6319,22 @@
         <v>66.83614490723826</v>
       </c>
       <c r="AV34" t="n">
-        <v>21.55911397594195</v>
+        <v>21.42800103607076</v>
       </c>
       <c r="AW34" t="n">
-        <v>181.0105813825426</v>
+        <v>181.0745590240812</v>
       </c>
       <c r="AX34" t="n">
         <v>1</v>
       </c>
       <c r="AY34" t="n">
-        <v>62.53305314553531</v>
+        <v>62.4763392438315</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1357813.972576757</v>
+        <v>1375662.868080455</v>
       </c>
       <c r="BA34" t="n">
-        <v>71.51192892717728</v>
+        <v>71.68958286594577</v>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
@@ -6116,76 +6424,76 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="n">
-        <v>24.40075757575758</v>
+        <v>24.38264462809917</v>
       </c>
       <c r="AE35" t="n">
-        <v>178.9327441077441</v>
+        <v>178.9266299357208</v>
       </c>
       <c r="AF35" t="n">
         <v>1</v>
       </c>
       <c r="AG35" t="n">
-        <v>66.04755892255893</v>
+        <v>65.99733700642793</v>
       </c>
       <c r="AH35" t="n">
-        <v>1930372.474747475</v>
+        <v>1909951.790633609</v>
       </c>
       <c r="AI35" t="n">
-        <v>72.55101010101009</v>
+        <v>72.5556473829201</v>
       </c>
       <c r="AJ35" t="n">
-        <v>25.90087412587413</v>
+        <v>25.97594696969697</v>
       </c>
       <c r="AK35" t="n">
-        <v>179.4230769230769</v>
+        <v>179.4507575757576</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.175524475524476</v>
+        <v>1.167424242424243</v>
       </c>
       <c r="AM35" t="n">
-        <v>67.23374125874126</v>
+        <v>67.11685606060605</v>
       </c>
       <c r="AN35" t="n">
-        <v>4023791.083916084</v>
+        <v>3824334.28030303</v>
       </c>
       <c r="AO35" t="n">
-        <v>72.07412587412588</v>
+        <v>71.89090909090909</v>
       </c>
       <c r="AP35" t="n">
-        <v>24.74314626110082</v>
+        <v>24.61284404954314</v>
       </c>
       <c r="AQ35" t="n">
-        <v>178.7516843533312</v>
+        <v>178.6809818613881</v>
       </c>
       <c r="AR35" t="n">
         <v>1</v>
       </c>
       <c r="AS35" t="n">
-        <v>63.79586524871346</v>
+        <v>63.72917920180507</v>
       </c>
       <c r="AT35" t="n">
-        <v>1494232.098642793</v>
+        <v>1525285.284080908</v>
       </c>
       <c r="AU35" t="n">
-        <v>70.26155345389344</v>
+        <v>70.3869353186859</v>
       </c>
       <c r="AV35" t="n">
-        <v>25.75187049009323</v>
+        <v>25.67727146230688</v>
       </c>
       <c r="AW35" t="n">
-        <v>179.8382584052673</v>
+        <v>179.9767407233533</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03751056635672</v>
+        <v>1.040636446886447</v>
       </c>
       <c r="AY35" t="n">
-        <v>65.72562230722339</v>
+        <v>65.67824769557043</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2103155.305903589</v>
+        <v>2142756.483356339</v>
       </c>
       <c r="BA35" t="n">
-        <v>70.48947342993273</v>
+        <v>70.50575307850555</v>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
@@ -6275,76 +6583,76 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="n">
-        <v>26.7968253968254</v>
+        <v>26.75042735042735</v>
       </c>
       <c r="AE36" t="n">
-        <v>178.9045634920635</v>
+        <v>178.7895299145299</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.228571428571428</v>
+        <v>1.230769230769231</v>
       </c>
       <c r="AG36" t="n">
-        <v>68.7220238095238</v>
+        <v>68.68525641025641</v>
       </c>
       <c r="AH36" t="n">
-        <v>2021661.706349206</v>
+        <v>2021981.837606838</v>
       </c>
       <c r="AI36" t="n">
-        <v>72.56825396825397</v>
+        <v>72.58119658119658</v>
       </c>
       <c r="AJ36" t="n">
-        <v>26.48035914702582</v>
+        <v>26.34040404040404</v>
       </c>
       <c r="AK36" t="n">
-        <v>181.016835016835</v>
+        <v>180.9939393939394</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.097194163860831</v>
+        <v>1.096843434343434</v>
       </c>
       <c r="AM36" t="n">
-        <v>68.87205387205387</v>
+        <v>68.7560606060606</v>
       </c>
       <c r="AN36" t="n">
-        <v>3112985.409652076</v>
+        <v>3075858.585858586</v>
       </c>
       <c r="AO36" t="n">
-        <v>71.81324354657689</v>
+        <v>71.93989898989899</v>
       </c>
       <c r="AP36" t="n">
-        <v>23.85587126917892</v>
+        <v>23.85288160972304</v>
       </c>
       <c r="AQ36" t="n">
-        <v>178.3148709560102</v>
+        <v>178.3471889647721</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.09323959942482</v>
+        <v>1.084217544319846</v>
       </c>
       <c r="AS36" t="n">
-        <v>63.16177276402552</v>
+        <v>63.18636257178457</v>
       </c>
       <c r="AT36" t="n">
-        <v>1392433.157053821</v>
+        <v>1407336.922171321</v>
       </c>
       <c r="AU36" t="n">
-        <v>69.73043520230365</v>
+        <v>69.77042819357396</v>
       </c>
       <c r="AV36" t="n">
-        <v>25.54344898928232</v>
+        <v>25.61919261294261</v>
       </c>
       <c r="AW36" t="n">
-        <v>181.4421040923492</v>
+        <v>181.7083046038928</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.108652748848827</v>
+        <v>1.122234342454931</v>
       </c>
       <c r="AY36" t="n">
-        <v>66.22410569640962</v>
+        <v>66.29118140846083</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1460147.323174284</v>
+        <v>1492275.113571069</v>
       </c>
       <c r="BA36" t="n">
-        <v>71.87919589488217</v>
+        <v>72.05159538174244</v>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
@@ -6434,76 +6742,76 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="n">
-        <v>26.79318181818182</v>
+        <v>26.90661157024794</v>
       </c>
       <c r="AE37" t="n">
-        <v>180.5780303030303</v>
+        <v>180.7297520661157</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.153030303030303</v>
+        <v>1.166942148760331</v>
       </c>
       <c r="AG37" t="n">
-        <v>67.71363636363635</v>
+        <v>67.78677685950413</v>
       </c>
       <c r="AH37" t="n">
-        <v>1829492.424242425</v>
+        <v>1879652.892561984</v>
       </c>
       <c r="AI37" t="n">
-        <v>70.73939393939393</v>
+        <v>70.75702479338842</v>
       </c>
       <c r="AJ37" t="n">
-        <v>27.55361952861953</v>
+        <v>27.50477502295684</v>
       </c>
       <c r="AK37" t="n">
-        <v>180.596127946128</v>
+        <v>180.5924701561065</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.335774410774411</v>
+        <v>1.333241505968779</v>
       </c>
       <c r="AM37" t="n">
-        <v>71.99309764309764</v>
+        <v>71.90156106519743</v>
       </c>
       <c r="AN37" t="n">
-        <v>4189000.420875421</v>
+        <v>4181388.888888889</v>
       </c>
       <c r="AO37" t="n">
-        <v>74.8462962962963</v>
+        <v>74.79100091827364</v>
       </c>
       <c r="AP37" t="n">
-        <v>25.67065089436371</v>
+        <v>25.41993084579937</v>
       </c>
       <c r="AQ37" t="n">
-        <v>179.8500226191302</v>
+        <v>179.6805441559342</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.093092937658155</v>
+        <v>1.075581906016688</v>
       </c>
       <c r="AS37" t="n">
-        <v>64.27877445039915</v>
+        <v>64.01840329653933</v>
       </c>
       <c r="AT37" t="n">
-        <v>1270407.761691228</v>
+        <v>1201462.146953202</v>
       </c>
       <c r="AU37" t="n">
-        <v>68.5116460315259</v>
+        <v>68.50188225084209</v>
       </c>
       <c r="AV37" t="n">
-        <v>25.96729267464562</v>
+        <v>25.79076556242331</v>
       </c>
       <c r="AW37" t="n">
-        <v>179.5308471620972</v>
+        <v>179.3477010363374</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01058201058201</v>
+        <v>1.011544011544012</v>
       </c>
       <c r="AY37" t="n">
-        <v>67.10095466216789</v>
+        <v>67.11013235872862</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1779057.356212687</v>
+        <v>1820748.520827064</v>
       </c>
       <c r="BA37" t="n">
-        <v>72.29551528944911</v>
+        <v>72.34717370419243</v>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
@@ -6593,76 +6901,76 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="n">
-        <v>26.50513468013468</v>
+        <v>26.50973370064279</v>
       </c>
       <c r="AE38" t="n">
-        <v>180.6112794612795</v>
+        <v>180.6089990817264</v>
       </c>
       <c r="AF38" t="n">
         <v>1</v>
       </c>
       <c r="AG38" t="n">
-        <v>68.87929292929293</v>
+        <v>68.94269972451791</v>
       </c>
       <c r="AH38" t="n">
-        <v>2444636.363636364</v>
+        <v>2500595.041322314</v>
       </c>
       <c r="AI38" t="n">
-        <v>72.42516835016835</v>
+        <v>72.51340679522497</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25.1</v>
+        <v>25.04040404040404</v>
       </c>
       <c r="AK38" t="n">
-        <v>181.8090909090909</v>
+        <v>181.6767676767677</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.063636363636364</v>
+        <v>1.070707070707071</v>
       </c>
       <c r="AM38" t="n">
-        <v>67.66363636363636</v>
+        <v>67.60606060606061</v>
       </c>
       <c r="AN38" t="n">
-        <v>2407272.727272728</v>
+        <v>2416919.191919192</v>
       </c>
       <c r="AO38" t="n">
-        <v>72.02727272727273</v>
+        <v>72.06060606060606</v>
       </c>
       <c r="AP38" t="n">
-        <v>25.65482804232805</v>
+        <v>25.65981240981241</v>
       </c>
       <c r="AQ38" t="n">
-        <v>180.6182309638832</v>
+        <v>180.5198883242362</v>
       </c>
       <c r="AR38" t="n">
         <v>1</v>
       </c>
       <c r="AS38" t="n">
-        <v>65.99736743731309</v>
+        <v>66.02894629525063</v>
       </c>
       <c r="AT38" t="n">
-        <v>1526651.066827697</v>
+        <v>1533505.709266579</v>
       </c>
       <c r="AU38" t="n">
-        <v>70.33711036346905</v>
+        <v>70.34957494196624</v>
       </c>
       <c r="AV38" t="n">
-        <v>26.3531794406966</v>
+        <v>26.4158134136395</v>
       </c>
       <c r="AW38" t="n">
-        <v>181.0415329578888</v>
+        <v>181.116323169584</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.143556272103183</v>
+        <v>1.141963109354414</v>
       </c>
       <c r="AY38" t="n">
-        <v>65.89872009569379</v>
+        <v>66.02196969696969</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1427711.637790127</v>
+        <v>1468510.006901311</v>
       </c>
       <c r="BA38" t="n">
-        <v>69.4474534904455</v>
+        <v>69.53810621745404</v>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
@@ -6756,76 +7064,76 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>26.98811188811189</v>
+        <v>26.85378787878788</v>
       </c>
       <c r="AE39" t="n">
-        <v>180.0566433566434</v>
+        <v>180.1280303030303</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.05034965034965</v>
+        <v>1.046212121212121</v>
       </c>
       <c r="AG39" t="n">
-        <v>65.7888111888112</v>
+        <v>65.57954545454545</v>
       </c>
       <c r="AH39" t="n">
-        <v>1155258.741258741</v>
+        <v>1125405.303030303</v>
       </c>
       <c r="AI39" t="n">
-        <v>68.8944055944056</v>
+        <v>68.76893939393939</v>
       </c>
       <c r="AJ39" t="n">
-        <v>25.68461538461538</v>
+        <v>25.64166666666667</v>
       </c>
       <c r="AK39" t="n">
-        <v>182.33006993007</v>
+        <v>182.2909090909091</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.066433566433566</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="AM39" t="n">
-        <v>67.62027972027971</v>
+        <v>67.5719696969697</v>
       </c>
       <c r="AN39" t="n">
-        <v>2691825.174825174</v>
+        <v>2702393.939393939</v>
       </c>
       <c r="AO39" t="n">
-        <v>71.45594405594406</v>
+        <v>71.45227272727273</v>
       </c>
       <c r="AP39" t="n">
-        <v>25.36563837129055</v>
+        <v>25.3405526800092</v>
       </c>
       <c r="AQ39" t="n">
-        <v>180.2409542389977</v>
+        <v>180.075848573729</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.062976057758667</v>
+        <v>1.063594432942259</v>
       </c>
       <c r="AS39" t="n">
-        <v>63.37454822954823</v>
+        <v>63.50298280423281</v>
       </c>
       <c r="AT39" t="n">
-        <v>1002037.710357275</v>
+        <v>1022022.33436853</v>
       </c>
       <c r="AU39" t="n">
-        <v>67.66753835536444</v>
+        <v>67.78798136645963</v>
       </c>
       <c r="AV39" t="n">
-        <v>24.84679767219813</v>
+        <v>24.88561811313528</v>
       </c>
       <c r="AW39" t="n">
-        <v>180.243165739676</v>
+        <v>180.3666041544903</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.029688351313065</v>
+        <v>1.0281941266209</v>
       </c>
       <c r="AY39" t="n">
-        <v>63.3128493169683</v>
+        <v>63.1603486648109</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1488422.15874324</v>
+        <v>1398727.179908351</v>
       </c>
       <c r="BA39" t="n">
-        <v>69.28995175305243</v>
+        <v>69.15141598644173</v>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
@@ -6919,22 +7227,22 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="n">
-        <v>24.10909090909091</v>
+        <v>24.12</v>
       </c>
       <c r="AE40" t="n">
-        <v>180.2181818181818</v>
+        <v>180.07</v>
       </c>
       <c r="AF40" t="n">
         <v>1</v>
       </c>
       <c r="AG40" t="n">
-        <v>65.54545454545455</v>
+        <v>65.61</v>
       </c>
       <c r="AH40" t="n">
-        <v>1664545.454545455</v>
+        <v>1665900</v>
       </c>
       <c r="AI40" t="n">
-        <v>70.65454545454546</v>
+        <v>70.71000000000001</v>
       </c>
       <c r="AJ40" t="n">
         <v>25.52313131313131</v>
@@ -6955,22 +7263,22 @@
         <v>71.52818181818182</v>
       </c>
       <c r="AP40" t="n">
-        <v>22.00460505677897</v>
+        <v>22.13284334023464</v>
       </c>
       <c r="AQ40" t="n">
-        <v>180.0500345065562</v>
+        <v>180.1050379572118</v>
       </c>
       <c r="AR40" t="n">
         <v>1</v>
       </c>
       <c r="AS40" t="n">
-        <v>60.12587991718426</v>
+        <v>60.41624568668046</v>
       </c>
       <c r="AT40" t="n">
-        <v>771341.3325804631</v>
+        <v>796169.9102829538</v>
       </c>
       <c r="AU40" t="n">
-        <v>69.14493381015122</v>
+        <v>69.25387163561076</v>
       </c>
       <c r="AV40" t="n">
         <v>23.94140077801456</v>
@@ -7096,22 +7404,22 @@
         <v>74.17416666666665</v>
       </c>
       <c r="AJ41" t="n">
-        <v>26.07438016528926</v>
+        <v>25.97272727272728</v>
       </c>
       <c r="AK41" t="n">
-        <v>181.595041322314</v>
+        <v>181.6181818181818</v>
       </c>
       <c r="AL41" t="n">
         <v>1</v>
       </c>
       <c r="AM41" t="n">
-        <v>65.57851239669422</v>
+        <v>65.53636363636363</v>
       </c>
       <c r="AN41" t="n">
-        <v>1191322.314049587</v>
+        <v>1180454.545454545</v>
       </c>
       <c r="AO41" t="n">
-        <v>69.80165289256198</v>
+        <v>69.87272727272727</v>
       </c>
       <c r="AP41" t="n">
         <v>24.02631308663816</v>
@@ -7132,22 +7440,22 @@
         <v>70.35187656641604</v>
       </c>
       <c r="AV41" t="n">
-        <v>24.57734727134041</v>
+        <v>24.61127247466492</v>
       </c>
       <c r="AW41" t="n">
-        <v>180.0279639315681</v>
+        <v>180.0212365152011</v>
       </c>
       <c r="AX41" t="n">
         <v>1</v>
       </c>
       <c r="AY41" t="n">
-        <v>64.01881342024363</v>
+        <v>64.03498047655371</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1197046.509141761</v>
+        <v>1194274.969579746</v>
       </c>
       <c r="BA41" t="n">
-        <v>70.01258515194444</v>
+        <v>70.09479604809124</v>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
@@ -7241,76 +7549,76 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="n">
-        <v>26.60330578512396</v>
+        <v>26.59090909090909</v>
       </c>
       <c r="AE42" t="n">
-        <v>178.595041322314</v>
+        <v>178.7909090909091</v>
       </c>
       <c r="AF42" t="n">
         <v>1</v>
       </c>
       <c r="AG42" t="n">
-        <v>69.72727272727273</v>
+        <v>69.66363636363636</v>
       </c>
       <c r="AH42" t="n">
-        <v>2824834.710743802</v>
+        <v>2848909.090909091</v>
       </c>
       <c r="AI42" t="n">
-        <v>72.3801652892562</v>
+        <v>72.32727272727273</v>
       </c>
       <c r="AJ42" t="n">
-        <v>27.80165289256198</v>
+        <v>27.78181818181818</v>
       </c>
       <c r="AK42" t="n">
-        <v>183.9173553719008</v>
+        <v>184.0090909090909</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.165289256198347</v>
+        <v>1.172727272727273</v>
       </c>
       <c r="AM42" t="n">
-        <v>69.28925619834712</v>
+        <v>69.33636363636364</v>
       </c>
       <c r="AN42" t="n">
-        <v>3259090.909090909</v>
+        <v>3287272.727272728</v>
       </c>
       <c r="AO42" t="n">
-        <v>71.09917355371901</v>
+        <v>71.11818181818182</v>
       </c>
       <c r="AP42" t="n">
-        <v>26.4414631668933</v>
+        <v>26.45082687488698</v>
       </c>
       <c r="AQ42" t="n">
-        <v>179.5150468715453</v>
+        <v>179.3100298195695</v>
       </c>
       <c r="AR42" t="n">
         <v>1</v>
       </c>
       <c r="AS42" t="n">
-        <v>67.28170106586172</v>
+        <v>67.32726247679572</v>
       </c>
       <c r="AT42" t="n">
-        <v>1725852.07901582</v>
+        <v>1739937.286917402</v>
       </c>
       <c r="AU42" t="n">
-        <v>69.64167702534361</v>
+        <v>69.67975777135624</v>
       </c>
       <c r="AV42" t="n">
-        <v>27.60005409610153</v>
+        <v>27.51658124484211</v>
       </c>
       <c r="AW42" t="n">
-        <v>182.8966305433696</v>
+        <v>182.7862935977066</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.050919271769074</v>
+        <v>1.042967720685112</v>
       </c>
       <c r="AY42" t="n">
-        <v>65.31591613261573</v>
+        <v>65.20837731109471</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1190932.419030245</v>
+        <v>1180460.443541965</v>
       </c>
       <c r="BA42" t="n">
-        <v>66.50598150202893</v>
+        <v>66.44788400005791</v>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
@@ -7396,22 +7704,22 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="n">
-        <v>25.90087412587413</v>
+        <v>25.97594696969697</v>
       </c>
       <c r="AE43" t="n">
-        <v>179.4230769230769</v>
+        <v>179.4507575757576</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.175524475524476</v>
+        <v>1.167424242424243</v>
       </c>
       <c r="AG43" t="n">
-        <v>67.23374125874126</v>
+        <v>67.11685606060605</v>
       </c>
       <c r="AH43" t="n">
-        <v>4023791.083916084</v>
+        <v>3824334.28030303</v>
       </c>
       <c r="AI43" t="n">
-        <v>72.07412587412588</v>
+        <v>71.89090909090909</v>
       </c>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
@@ -7420,22 +7728,22 @@
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="n">
-        <v>25.75187049009323</v>
+        <v>25.67727146230688</v>
       </c>
       <c r="AQ43" t="n">
-        <v>179.8382584052673</v>
+        <v>179.9767407233533</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03751056635672</v>
+        <v>1.040636446886447</v>
       </c>
       <c r="AS43" t="n">
-        <v>65.72562230722339</v>
+        <v>65.67824769557043</v>
       </c>
       <c r="AT43" t="n">
-        <v>2103155.305903589</v>
+        <v>2142756.483356339</v>
       </c>
       <c r="AU43" t="n">
-        <v>70.48947342993273</v>
+        <v>70.50575307850555</v>
       </c>
       <c r="AV43" t="n">
         <v>20.5</v>
@@ -7549,22 +7857,22 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="n">
-        <v>26.7968253968254</v>
+        <v>26.75042735042735</v>
       </c>
       <c r="AK44" t="n">
-        <v>178.9045634920635</v>
+        <v>178.7895299145299</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.228571428571428</v>
+        <v>1.230769230769231</v>
       </c>
       <c r="AM44" t="n">
-        <v>68.7220238095238</v>
+        <v>68.68525641025641</v>
       </c>
       <c r="AN44" t="n">
-        <v>2021661.706349206</v>
+        <v>2021981.837606838</v>
       </c>
       <c r="AO44" t="n">
-        <v>72.56825396825397</v>
+        <v>72.58119658119658</v>
       </c>
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr"/>
@@ -7573,22 +7881,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AU44" t="inlineStr"/>
       <c r="AV44" t="n">
-        <v>23.85587126917892</v>
+        <v>23.85288160972304</v>
       </c>
       <c r="AW44" t="n">
-        <v>178.3148709560102</v>
+        <v>178.3471889647721</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.09323959942482</v>
+        <v>1.084217544319846</v>
       </c>
       <c r="AY44" t="n">
-        <v>63.16177276402552</v>
+        <v>63.18636257178457</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1392433.157053821</v>
+        <v>1407336.922171321</v>
       </c>
       <c r="BA44" t="n">
-        <v>69.73043520230365</v>
+        <v>69.77042819357396</v>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
@@ -7682,76 +7990,76 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="n">
-        <v>26.98811188811189</v>
+        <v>26.85378787878788</v>
       </c>
       <c r="AE45" t="n">
-        <v>180.0566433566434</v>
+        <v>180.1280303030303</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.05034965034965</v>
+        <v>1.046212121212121</v>
       </c>
       <c r="AG45" t="n">
-        <v>65.7888111888112</v>
+        <v>65.57954545454545</v>
       </c>
       <c r="AH45" t="n">
-        <v>1155258.741258741</v>
+        <v>1125405.303030303</v>
       </c>
       <c r="AI45" t="n">
-        <v>68.8944055944056</v>
+        <v>68.76893939393939</v>
       </c>
       <c r="AJ45" t="n">
-        <v>25.68461538461538</v>
+        <v>25.64166666666667</v>
       </c>
       <c r="AK45" t="n">
-        <v>182.33006993007</v>
+        <v>182.2909090909091</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.066433566433566</v>
+        <v>1.063636363636364</v>
       </c>
       <c r="AM45" t="n">
-        <v>67.62027972027971</v>
+        <v>67.5719696969697</v>
       </c>
       <c r="AN45" t="n">
-        <v>2691825.174825174</v>
+        <v>2702393.939393939</v>
       </c>
       <c r="AO45" t="n">
-        <v>71.45594405594406</v>
+        <v>71.45227272727273</v>
       </c>
       <c r="AP45" t="n">
-        <v>25.36563837129055</v>
+        <v>25.3405526800092</v>
       </c>
       <c r="AQ45" t="n">
-        <v>180.2409542389977</v>
+        <v>180.075848573729</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.062976057758667</v>
+        <v>1.063594432942259</v>
       </c>
       <c r="AS45" t="n">
-        <v>63.37454822954823</v>
+        <v>63.50298280423281</v>
       </c>
       <c r="AT45" t="n">
-        <v>1002037.710357275</v>
+        <v>1022022.33436853</v>
       </c>
       <c r="AU45" t="n">
-        <v>67.66753835536444</v>
+        <v>67.78798136645963</v>
       </c>
       <c r="AV45" t="n">
-        <v>24.84679767219813</v>
+        <v>24.88561811313528</v>
       </c>
       <c r="AW45" t="n">
-        <v>180.243165739676</v>
+        <v>180.3666041544903</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.029688351313065</v>
+        <v>1.0281941266209</v>
       </c>
       <c r="AY45" t="n">
-        <v>63.3128493169683</v>
+        <v>63.1603486648109</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1488422.15874324</v>
+        <v>1398727.179908351</v>
       </c>
       <c r="BA45" t="n">
-        <v>69.28995175305243</v>
+        <v>69.15141598644173</v>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
@@ -7837,22 +8145,22 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="n">
-        <v>27.55361952861953</v>
+        <v>27.50477502295684</v>
       </c>
       <c r="AE46" t="n">
-        <v>180.596127946128</v>
+        <v>180.5924701561065</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.335774410774411</v>
+        <v>1.333241505968779</v>
       </c>
       <c r="AG46" t="n">
-        <v>71.99309764309764</v>
+        <v>71.90156106519743</v>
       </c>
       <c r="AH46" t="n">
-        <v>4189000.420875421</v>
+        <v>4181388.888888889</v>
       </c>
       <c r="AI46" t="n">
-        <v>74.8462962962963</v>
+        <v>74.79100091827364</v>
       </c>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
@@ -7861,22 +8169,22 @@
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>25.96729267464562</v>
+        <v>25.79076556242331</v>
       </c>
       <c r="AQ46" t="n">
-        <v>179.5308471620972</v>
+        <v>179.3477010363374</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01058201058201</v>
+        <v>1.011544011544012</v>
       </c>
       <c r="AS46" t="n">
-        <v>67.10095466216789</v>
+        <v>67.11013235872862</v>
       </c>
       <c r="AT46" t="n">
-        <v>1779057.356212687</v>
+        <v>1820748.520827064</v>
       </c>
       <c r="AU46" t="n">
-        <v>72.29551528944911</v>
+        <v>72.34717370419243</v>
       </c>
       <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>

--- a/p6_deployment/data/usa/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_filled.xlsx
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23112</v>
+        <v>71000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,24 +760,38 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>135</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>146</v>
+      </c>
       <c r="W2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="X2" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -786,129 +800,129 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2300000</v>
+        <v>50000</v>
       </c>
       <c r="AC2" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.06060606060606</v>
+        <v>26.11477272727273</v>
       </c>
       <c r="AE2" t="n">
-        <v>178.7424242424242</v>
+        <v>179.775</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.075757575757576</v>
+        <v>1.125</v>
       </c>
       <c r="AG2" t="n">
-        <v>65.77272727272727</v>
+        <v>66.0840909090909</v>
       </c>
       <c r="AH2" t="n">
-        <v>1437500</v>
+        <v>2105852.272727272</v>
       </c>
       <c r="AI2" t="n">
-        <v>72.27272727272727</v>
+        <v>70.42727272727274</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25.68961038961039</v>
+        <v>26.07012987012987</v>
       </c>
       <c r="AK2" t="n">
-        <v>179.7558441558442</v>
+        <v>180.6012987012987</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.155844155844156</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>65.92727272727272</v>
+        <v>69.00129870129869</v>
       </c>
       <c r="AN2" t="n">
-        <v>2824675.324675325</v>
+        <v>3949870.12987013</v>
       </c>
       <c r="AO2" t="n">
-        <v>71.02077922077922</v>
+        <v>72.5090909090909</v>
       </c>
       <c r="AP2" t="n">
-        <v>23.89393939393939</v>
+        <v>25.23044590643275</v>
       </c>
       <c r="AQ2" t="n">
-        <v>180.0772860180755</v>
+        <v>179.0544185985798</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.131678628389155</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>66.26279239766082</v>
+        <v>64.19908625730994</v>
       </c>
       <c r="AT2" t="n">
-        <v>1643782.396331738</v>
+        <v>873303.8977652465</v>
       </c>
       <c r="AU2" t="n">
-        <v>71.83672248803828</v>
+        <v>69.95427501044277</v>
       </c>
       <c r="AV2" t="n">
-        <v>25.0890246449457</v>
+        <v>23.87860290158427</v>
       </c>
       <c r="AW2" t="n">
-        <v>179.1881325337152</v>
+        <v>180.6446092899509</v>
       </c>
       <c r="AX2" t="n">
         <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>64.14341060985798</v>
+        <v>63.96714017521471</v>
       </c>
       <c r="AZ2" t="n">
-        <v>884492.5184986275</v>
+        <v>1532860.887387285</v>
       </c>
       <c r="BA2" t="n">
-        <v>70.01729174125792</v>
+        <v>70.3349557619744</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>txm4BKVR</t>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>23112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -933,169 +947,173 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q3" t="n">
-        <v>185.5</v>
+        <v>191</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>260</v>
+        <v>58</v>
       </c>
       <c r="U3" t="n">
-        <v>3750000</v>
+        <v>140000</v>
       </c>
       <c r="V3" t="n">
-        <v>282</v>
+        <v>58</v>
       </c>
       <c r="W3" t="n">
-        <v>26.6</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>179.6</v>
+        <v>181.5</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>318</v>
+        <v>117</v>
       </c>
       <c r="AB3" t="n">
-        <v>3225000</v>
+        <v>990000</v>
       </c>
       <c r="AC3" t="n">
-        <v>331</v>
+        <v>129</v>
       </c>
       <c r="AD3" t="n">
-        <v>25.93636363636364</v>
+        <v>23.4025974025974</v>
       </c>
       <c r="AE3" t="n">
-        <v>184.5287878787879</v>
+        <v>178.8051948051948</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.063636363636364</v>
+        <v>1.077922077922078</v>
       </c>
       <c r="AG3" t="n">
-        <v>65.67272727272727</v>
+        <v>66.01298701298701</v>
       </c>
       <c r="AH3" t="n">
-        <v>1212984.848484848</v>
+        <v>1451948.051948052</v>
       </c>
       <c r="AI3" t="n">
-        <v>70.44848484848485</v>
+        <v>72.02597402597402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27.40909090909091</v>
+        <v>26.44285714285714</v>
       </c>
       <c r="AK3" t="n">
-        <v>184.1818181818182</v>
+        <v>181.7428571428572</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.181818181818182</v>
+        <v>1.314285714285714</v>
       </c>
       <c r="AM3" t="n">
-        <v>68.39393939393939</v>
+        <v>66</v>
       </c>
       <c r="AN3" t="n">
-        <v>3231212.121212121</v>
+        <v>2824428.571428571</v>
       </c>
       <c r="AO3" t="n">
-        <v>70.34848484848484</v>
+        <v>69.04285714285716</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.44259259259259</v>
+        <v>24.00162337662337</v>
       </c>
       <c r="AQ3" t="n">
-        <v>182.8909932659933</v>
+        <v>180.1955741626794</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>1.142088174982912</v>
       </c>
       <c r="AS3" t="n">
-        <v>60.51489898989899</v>
+        <v>66.12568352699931</v>
       </c>
       <c r="AT3" t="n">
-        <v>843837.962962963</v>
+        <v>1607054.283435863</v>
       </c>
       <c r="AU3" t="n">
-        <v>69.65673400673401</v>
+        <v>71.79348940533151</v>
       </c>
       <c r="AV3" t="n">
-        <v>27.69977045583453</v>
+        <v>23.77710808406297</v>
       </c>
       <c r="AW3" t="n">
-        <v>183.1425854211896</v>
+        <v>179.6469878701082</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.029644268774703</v>
+        <v>1.210016925430459</v>
       </c>
       <c r="AY3" t="n">
-        <v>64.104258124281</v>
+        <v>63.75034311970403</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1040039.067847992</v>
+        <v>1877737.187937376</v>
       </c>
       <c r="BA3" t="n">
-        <v>65.32316324661862</v>
+        <v>69.39254765702132</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>EgT3xN3S</t>
+          <t>xA45kovo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>21550</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1122,152 +1140,152 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25.33333333333333</v>
+        <v>27.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>181.3333333333333</v>
+        <v>177.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="U4" t="n">
-        <v>4530000</v>
+        <v>56625000</v>
       </c>
       <c r="V4" t="n">
-        <v>203</v>
+        <v>313</v>
       </c>
       <c r="W4" t="n">
-        <v>28</v>
+        <v>25.8</v>
       </c>
       <c r="X4" t="n">
-        <v>186.5</v>
+        <v>177.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="AB4" t="n">
-        <v>900000</v>
+        <v>8875000</v>
       </c>
       <c r="AC4" t="n">
-        <v>135</v>
+        <v>358</v>
       </c>
       <c r="AD4" t="n">
-        <v>24.82272727272727</v>
+        <v>25.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>179.7712121212121</v>
+        <v>183.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>68.62424242424242</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>3615643.939393939</v>
+        <v>3928000</v>
       </c>
       <c r="AI4" t="n">
-        <v>73.33636363636363</v>
+        <v>75.92</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25.61090909090909</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
-        <v>181.8945454545455</v>
+        <v>182.6515151515152</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.018181818181818</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AM4" t="n">
-        <v>66.67272727272727</v>
+        <v>67.7121212121212</v>
       </c>
       <c r="AN4" t="n">
-        <v>1914909.090909091</v>
+        <v>2270454.545454545</v>
       </c>
       <c r="AO4" t="n">
-        <v>71.66</v>
+        <v>71.07575757575758</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.73128019323671</v>
+        <v>22.82824842855802</v>
       </c>
       <c r="AQ4" t="n">
-        <v>181.6524758454106</v>
+        <v>185.5553250773994</v>
       </c>
       <c r="AR4" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>62.05102657004831</v>
+        <v>64.76912343246708</v>
       </c>
       <c r="AT4" t="n">
-        <v>1298008.756038647</v>
+        <v>1675504.589236013</v>
       </c>
       <c r="AU4" t="n">
-        <v>67.16213768115942</v>
+        <v>72.93087969478061</v>
       </c>
       <c r="AV4" t="n">
-        <v>25.91542986425339</v>
+        <v>25.31161832859488</v>
       </c>
       <c r="AW4" t="n">
-        <v>182.2620814479638</v>
+        <v>181.6358697096827</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.0675</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>65.27691176470589</v>
+        <v>64.7368455724291</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1779773.076923077</v>
+        <v>1338518.516833091</v>
       </c>
       <c r="BA4" t="n">
-        <v>70.01356334841628</v>
+        <v>69.16006749416361</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6gpXy3vi</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1286,7 +1304,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1314,7 +1332,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1339,141 +1357,141 @@
         <v>146</v>
       </c>
       <c r="W5" t="n">
-        <v>20</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>185</v>
+        <v>176.6666666666667</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>58</v>
+        <v>420</v>
       </c>
       <c r="AB5" t="n">
-        <v>475000</v>
+        <v>35150000</v>
       </c>
       <c r="AC5" t="n">
-        <v>72</v>
+        <v>467</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.38444444444444</v>
+        <v>25.65555555555556</v>
       </c>
       <c r="AE5" t="n">
-        <v>181.010101010101</v>
+        <v>181.1954545454545</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.042222222222222</v>
+        <v>1.035185185185185</v>
       </c>
       <c r="AG5" t="n">
-        <v>67.51010101010101</v>
+        <v>67.11582491582492</v>
       </c>
       <c r="AH5" t="n">
-        <v>2048060.606060606</v>
+        <v>1608430.134680135</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.37979797979798</v>
+        <v>71.96835016835017</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26.43333333333333</v>
+        <v>25.94545454545455</v>
       </c>
       <c r="AK5" t="n">
-        <v>179.9</v>
+        <v>182.0944444444444</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.183333333333333</v>
+        <v>1.059090909090909</v>
       </c>
       <c r="AM5" t="n">
-        <v>68.71666666666667</v>
+        <v>66.45883838383838</v>
       </c>
       <c r="AN5" t="n">
-        <v>2638166.666666667</v>
+        <v>2139725.378787879</v>
       </c>
       <c r="AO5" t="n">
-        <v>71.66666666666667</v>
+        <v>70.14179292929293</v>
       </c>
       <c r="AP5" t="n">
-        <v>26.61187837453823</v>
+        <v>26.36937576963153</v>
       </c>
       <c r="AQ5" t="n">
-        <v>181.7775049730037</v>
+        <v>181.6511887846926</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.13131003125888</v>
+        <v>1.100165766789808</v>
       </c>
       <c r="AS5" t="n">
-        <v>66.72192100028417</v>
+        <v>66.34560954816709</v>
       </c>
       <c r="AT5" t="n">
-        <v>1359559.81813015</v>
+        <v>1299129.36913896</v>
       </c>
       <c r="AU5" t="n">
-        <v>71.16270531400967</v>
+        <v>70.77992327365729</v>
       </c>
       <c r="AV5" t="n">
-        <v>24.70130469842746</v>
+        <v>25.66576314489286</v>
       </c>
       <c r="AW5" t="n">
-        <v>180.2565966571082</v>
+        <v>181.46438154118</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.210826847207921</v>
+        <v>1.022997835497836</v>
       </c>
       <c r="AY5" t="n">
-        <v>64.47422932282268</v>
+        <v>63.17020785040665</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2877415.500455782</v>
+        <v>1355908.359012031</v>
       </c>
       <c r="BA5" t="n">
-        <v>70.4483193277311</v>
+        <v>67.90356147594777</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30991</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1498,173 +1516,169 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.6666666666667</v>
+        <v>183.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="U6" t="n">
-        <v>11490000</v>
+        <v>3300000</v>
       </c>
       <c r="V6" t="n">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="W6" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="X6" t="n">
-        <v>183.6666666666667</v>
+        <v>182.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>206</v>
+        <v>321</v>
       </c>
       <c r="AB6" t="n">
-        <v>8375000</v>
+        <v>3855000</v>
       </c>
       <c r="AC6" t="n">
-        <v>213</v>
+        <v>330</v>
       </c>
       <c r="AD6" t="n">
-        <v>25.96666666666667</v>
+        <v>22.40909090909091</v>
       </c>
       <c r="AE6" t="n">
-        <v>181.6833333333333</v>
+        <v>180.7151515151515</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>65.28333333333333</v>
+        <v>65.51363636363637</v>
       </c>
       <c r="AH6" t="n">
-        <v>2802833.333333333</v>
+        <v>1866303.030303031</v>
       </c>
       <c r="AI6" t="n">
-        <v>68.73333333333333</v>
+        <v>73.21212121212122</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24.64444444444445</v>
+        <v>24.83116883116883</v>
       </c>
       <c r="AK6" t="n">
-        <v>183.6925925925926</v>
+        <v>179.8051948051948</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.016666666666667</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>68.16111111111111</v>
+        <v>68.16883116883116</v>
       </c>
       <c r="AN6" t="n">
-        <v>2637333.333333333</v>
+        <v>3325389.61038961</v>
       </c>
       <c r="AO6" t="n">
-        <v>72.79074074074073</v>
+        <v>72.83116883116882</v>
       </c>
       <c r="AP6" t="n">
-        <v>23.38633389028126</v>
+        <v>23.0734971620227</v>
       </c>
       <c r="AQ6" t="n">
-        <v>179.3485240879978</v>
+        <v>180.9445755933953</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.14906015037594</v>
+        <v>1.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>63.50932887774993</v>
+        <v>63.7452334881321</v>
       </c>
       <c r="AT6" t="n">
-        <v>1571354.010025063</v>
+        <v>1656492.131062952</v>
       </c>
       <c r="AU6" t="n">
-        <v>69.59514759120022</v>
+        <v>71.80626289989681</v>
       </c>
       <c r="AV6" t="n">
-        <v>23.5082702020202</v>
+        <v>24.60041407867495</v>
       </c>
       <c r="AW6" t="n">
-        <v>181.1729527417027</v>
+        <v>181.8592132505176</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.047619047619047</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>62.36371753246753</v>
+        <v>62.25155279503105</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1235730.925324675</v>
+        <v>1406934.523809524</v>
       </c>
       <c r="BA6" t="n">
-        <v>68.940386002886</v>
+        <v>67.37629399585921</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20700</v>
+        <v>25500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1691,143 +1705,167 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>185</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>475000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>72</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>242</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3395000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>274</v>
+      </c>
       <c r="AD7" t="n">
-        <v>28.21636363636363</v>
+        <v>26.34285714285714</v>
       </c>
       <c r="AE7" t="n">
-        <v>180.0745454545454</v>
+        <v>179.6714285714286</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.158181818181818</v>
+        <v>1.114285714285714</v>
       </c>
       <c r="AG7" t="n">
-        <v>67.21454545454546</v>
+        <v>69.01428571428572</v>
       </c>
       <c r="AH7" t="n">
-        <v>2052000</v>
+        <v>2555071.428571429</v>
       </c>
       <c r="AI7" t="n">
-        <v>68.15636363636364</v>
+        <v>71.89999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26.92407407407407</v>
+        <v>23.12962962962963</v>
       </c>
       <c r="AK7" t="n">
-        <v>179.2944444444445</v>
+        <v>182.4143518518519</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.194444444444444</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>69.40925925925926</v>
+        <v>65.75694444444444</v>
       </c>
       <c r="AN7" t="n">
-        <v>2095064.814814815</v>
+        <v>1525682.870370371</v>
       </c>
       <c r="AO7" t="n">
-        <v>72.93518518518518</v>
+        <v>71.67824074074075</v>
       </c>
       <c r="AP7" t="n">
-        <v>28.4587367555718</v>
+        <v>25.39614936883844</v>
       </c>
       <c r="AQ7" t="n">
-        <v>181.4352986846913</v>
+        <v>180.0320517930492</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.210084033613445</v>
+        <v>1.292509968414243</v>
       </c>
       <c r="AS7" t="n">
-        <v>63.70407837047863</v>
+        <v>65.24706198685007</v>
       </c>
       <c r="AT7" t="n">
-        <v>830038.0815369627</v>
+        <v>3032406.867885494</v>
       </c>
       <c r="AU7" t="n">
-        <v>65.74657471684324</v>
+        <v>70.60270021051898</v>
       </c>
       <c r="AV7" t="n">
-        <v>24.23426636355025</v>
+        <v>21.5848975954018</v>
       </c>
       <c r="AW7" t="n">
-        <v>177.8638557355309</v>
+        <v>182.2341098677233</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.122817206592782</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>65.5856463720754</v>
+        <v>62.4972295211791</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2221970.437269111</v>
+        <v>1392773.892074313</v>
       </c>
       <c r="BA7" t="n">
-        <v>71.8185783129677</v>
+        <v>71.71853356727307</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>EgT3xN3S</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61500</v>
+        <v>18500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1854,153 +1892,171 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
       <c r="P8" t="n">
-        <v>27.2</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>337</v>
+        <v>56</v>
       </c>
       <c r="U8" t="n">
-        <v>5575000</v>
+        <v>275000</v>
       </c>
       <c r="V8" t="n">
-        <v>351</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="W8" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>255</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>268</v>
+      </c>
       <c r="AD8" t="n">
-        <v>25.54545454545454</v>
+        <v>25.24199134199134</v>
       </c>
       <c r="AE8" t="n">
-        <v>182.2909090909091</v>
+        <v>183.7507936507936</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.090909090909091</v>
+        <v>1.025974025974026</v>
       </c>
       <c r="AG8" t="n">
-        <v>67.40000000000001</v>
+        <v>69.41601731601732</v>
       </c>
       <c r="AH8" t="n">
-        <v>2285000</v>
+        <v>2863870.129870129</v>
       </c>
       <c r="AI8" t="n">
-        <v>71.29090909090908</v>
+        <v>73.09725829725831</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23.44444444444445</v>
+        <v>27.48051948051948</v>
       </c>
       <c r="AK8" t="n">
-        <v>182.1527777777778</v>
+        <v>184</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>1.155844155844156</v>
       </c>
       <c r="AM8" t="n">
-        <v>66.43333333333334</v>
+        <v>68.22077922077922</v>
       </c>
       <c r="AN8" t="n">
-        <v>1587347.222222222</v>
+        <v>3130649.35064935</v>
       </c>
       <c r="AO8" t="n">
-        <v>71.34444444444445</v>
+        <v>70.1038961038961</v>
       </c>
       <c r="AP8" t="n">
-        <v>25.4705303030303</v>
+        <v>23.82035405071119</v>
       </c>
       <c r="AQ8" t="n">
-        <v>181.9903787878788</v>
+        <v>181.6322588126159</v>
       </c>
       <c r="AR8" t="n">
-        <v>1</v>
+        <v>1.071088435374149</v>
       </c>
       <c r="AS8" t="n">
-        <v>64.6509090909091</v>
+        <v>62.6637987012987</v>
       </c>
       <c r="AT8" t="n">
-        <v>1368751.136363636</v>
+        <v>1208323.786332715</v>
       </c>
       <c r="AU8" t="n">
-        <v>68.9969696969697</v>
+        <v>69.29788188002475</v>
       </c>
       <c r="AV8" t="n">
-        <v>21.48630209659622</v>
+        <v>27.22530932073266</v>
       </c>
       <c r="AW8" t="n">
-        <v>181.9360241066123</v>
+        <v>182.6720714830555</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>1.02540937323546</v>
       </c>
       <c r="AY8" t="n">
-        <v>62.22942237501061</v>
+        <v>63.98479499143115</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1249578.59052712</v>
+        <v>1029008.472267626</v>
       </c>
       <c r="BA8" t="n">
-        <v>71.61204481792718</v>
+        <v>65.56395484759329</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20500</v>
+        <v>20738</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2030,164 +2086,168 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>22.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>27050000</v>
+        <v>15000000</v>
       </c>
       <c r="V9" t="n">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="W9" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="X9" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AB9" t="n">
-        <v>2900000</v>
+        <v>1150000</v>
       </c>
       <c r="AC9" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AD9" t="n">
-        <v>26.09480519480519</v>
+        <v>28.13030303030303</v>
       </c>
       <c r="AE9" t="n">
-        <v>181.9988455988455</v>
+        <v>180.4454545454546</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.066233766233766</v>
+        <v>1.215151515151515</v>
       </c>
       <c r="AG9" t="n">
-        <v>66.8958152958153</v>
+        <v>67.11212121212121</v>
       </c>
       <c r="AH9" t="n">
-        <v>2268290.043290044</v>
+        <v>2087916.666666667</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.48932178932179</v>
+        <v>68.23030303030303</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26.22546296296296</v>
+        <v>25.61515151515152</v>
       </c>
       <c r="AK9" t="n">
-        <v>179.0537037037037</v>
+        <v>181.8666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.033333333333333</v>
+        <v>1.015151515151515</v>
       </c>
       <c r="AM9" t="n">
-        <v>70.55462962962963</v>
+        <v>66.75757575757576</v>
       </c>
       <c r="AN9" t="n">
-        <v>3214756.944444444</v>
+        <v>1923409.090909091</v>
       </c>
       <c r="AO9" t="n">
-        <v>74.3125</v>
+        <v>71.7469696969697</v>
       </c>
       <c r="AP9" t="n">
-        <v>25.14661914172784</v>
+        <v>28.23547091761606</v>
       </c>
       <c r="AQ9" t="n">
-        <v>181.2339238659891</v>
+        <v>181.3054837053398</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.019480519480519</v>
+        <v>1.15709524916686</v>
       </c>
       <c r="AS9" t="n">
-        <v>62.88794936947111</v>
+        <v>64.29179502828799</v>
       </c>
       <c r="AT9" t="n">
-        <v>1386293.65471485</v>
+        <v>893454.3928737504</v>
       </c>
       <c r="AU9" t="n">
-        <v>68.05407726331639</v>
+        <v>66.33553727815237</v>
       </c>
       <c r="AV9" t="n">
-        <v>23.78057510085374</v>
+        <v>25.37841080488139</v>
       </c>
       <c r="AW9" t="n">
-        <v>179.3332770428746</v>
+        <v>182.5526703688468</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.044288863870907</v>
+        <v>1.03125</v>
       </c>
       <c r="AY9" t="n">
-        <v>64.89519654751852</v>
+        <v>65.20794340463458</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1964302.936485599</v>
+        <v>1841423.196901138</v>
       </c>
       <c r="BA9" t="n">
-        <v>70.58185805422647</v>
+        <v>70.25787141779789</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>19400</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2214,171 +2274,167 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
           <t>CURGfJWt</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>29.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>175</v>
+        <v>186.25</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>253</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>260</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
-        <v>130</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1975000</v>
-      </c>
-      <c r="V10" t="n">
-        <v>140</v>
-      </c>
-      <c r="W10" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="X10" t="n">
-        <v>185.6666666666667</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
       <c r="AA10" t="n">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="AB10" t="n">
-        <v>1270000</v>
+        <v>1225000</v>
       </c>
       <c r="AC10" t="n">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="AD10" t="n">
-        <v>27.16363636363636</v>
+        <v>25.30779220779221</v>
       </c>
       <c r="AE10" t="n">
-        <v>180.8727272727273</v>
+        <v>180.9948051948052</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>68.41818181818182</v>
+        <v>64.91428571428573</v>
       </c>
       <c r="AH10" t="n">
-        <v>1946818.181818182</v>
+        <v>1134629.87012987</v>
       </c>
       <c r="AI10" t="n">
-        <v>71.23636363636363</v>
+        <v>69.86363636363637</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25.68333333333333</v>
+        <v>26.14285714285714</v>
       </c>
       <c r="AK10" t="n">
-        <v>180.8318181818182</v>
+        <v>179.7571428571429</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>65.37575757575758</v>
+        <v>68.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>1162462.121212121</v>
+        <v>2472214.285714286</v>
       </c>
       <c r="AO10" t="n">
-        <v>70.14848484848484</v>
+        <v>71.87142857142857</v>
       </c>
       <c r="AP10" t="n">
-        <v>25.09232980148581</v>
+        <v>24.81272298393041</v>
       </c>
       <c r="AQ10" t="n">
-        <v>179.1268694434295</v>
+        <v>177.390648364609</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.035714285714286</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>63.33391426135672</v>
+        <v>64.16433389145131</v>
       </c>
       <c r="AT10" t="n">
-        <v>1010234.7004019</v>
+        <v>1188586.855794949</v>
       </c>
       <c r="AU10" t="n">
-        <v>68.30000121787846</v>
+        <v>70.0062740885828</v>
       </c>
       <c r="AV10" t="n">
-        <v>24.30637009189641</v>
+        <v>26.74380952380952</v>
       </c>
       <c r="AW10" t="n">
-        <v>178.1801378446115</v>
+        <v>180.8554761904762</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>63.39302422723475</v>
+        <v>66.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1024350.981620718</v>
+        <v>1530757.142857143</v>
       </c>
       <c r="BA10" t="n">
-        <v>69.73817878028404</v>
+        <v>69.45023809523809</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">da silva a 
+  usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>21650</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2405,137 +2461,137 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="n">
-        <v>27</v>
-      </c>
-      <c r="X11" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="P11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="T11" t="n">
+        <v>129</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V11" t="n">
         <v>137</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>139</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>24.94444444444444</v>
+        <v>26.58068181818182</v>
       </c>
       <c r="AE11" t="n">
-        <v>181.824074074074</v>
+        <v>180.0522727272727</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.174074074074074</v>
+        <v>1.047727272727273</v>
       </c>
       <c r="AG11" t="n">
-        <v>66.68148148148147</v>
+        <v>64.81363636363636</v>
       </c>
       <c r="AH11" t="n">
-        <v>2087314.814814815</v>
+        <v>1086454.545454545</v>
       </c>
       <c r="AI11" t="n">
-        <v>70.95370370370371</v>
+        <v>68.73636363636363</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25.54363636363636</v>
+        <v>24.95108225108225</v>
       </c>
       <c r="AK11" t="n">
-        <v>177.4018181818182</v>
+        <v>181.7764790764791</v>
       </c>
       <c r="AL11" t="n">
-        <v>1</v>
+        <v>1.175180375180375</v>
       </c>
       <c r="AM11" t="n">
-        <v>68.33454545454545</v>
+        <v>66.3139971139971</v>
       </c>
       <c r="AN11" t="n">
-        <v>2452181.818181818</v>
+        <v>1983477.633477634</v>
       </c>
       <c r="AO11" t="n">
-        <v>71.25454545454545</v>
+        <v>70.60057720057721</v>
       </c>
       <c r="AP11" t="n">
-        <v>23.21260504201681</v>
+        <v>26.00713957571795</v>
       </c>
       <c r="AQ11" t="n">
-        <v>182.2930926916221</v>
+        <v>180.8995534166444</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.019607843137255</v>
+        <v>1.054855889724311</v>
       </c>
       <c r="AS11" t="n">
-        <v>61.60583142347848</v>
+        <v>63.62922746589795</v>
       </c>
       <c r="AT11" t="n">
-        <v>1011558.441558442</v>
+        <v>992424.1159655562</v>
       </c>
       <c r="AU11" t="n">
-        <v>69.07197606315253</v>
+        <v>67.31972458319711</v>
       </c>
       <c r="AV11" t="n">
-        <v>24.48081339712919</v>
+        <v>23.08339335734294</v>
       </c>
       <c r="AW11" t="n">
-        <v>177.9576076555024</v>
+        <v>182.2262304921969</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>1.016806722689076</v>
       </c>
       <c r="AY11" t="n">
-        <v>64.64263157894736</v>
+        <v>61.53105242096839</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1201808.612440191</v>
+        <v>1040452.180872349</v>
       </c>
       <c r="BA11" t="n">
-        <v>69.66650717703349</v>
+        <v>69.35350140056022</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45486.9375</v>
+        <v>45493.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">gonzalez g  jr 
   usa </t>
         </is>
       </c>
@@ -2555,7 +2611,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2585,7 +2641,11 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
       <c r="P12" t="n">
         <v>22</v>
       </c>
@@ -2608,141 +2668,141 @@
         <v>77</v>
       </c>
       <c r="W12" t="n">
-        <v>19.33333333333333</v>
+        <v>26.4</v>
       </c>
       <c r="X12" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y12" t="n">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="AB12" t="n">
-        <v>1600000</v>
+        <v>10375000</v>
       </c>
       <c r="AC12" t="n">
-        <v>210</v>
+        <v>355</v>
       </c>
       <c r="AD12" t="n">
-        <v>24.6</v>
+        <v>24.49523809523809</v>
       </c>
       <c r="AE12" t="n">
-        <v>179.65</v>
+        <v>179.9444444444444</v>
       </c>
       <c r="AF12" t="n">
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>65.96666666666665</v>
+        <v>65.73968253968253</v>
       </c>
       <c r="AH12" t="n">
-        <v>1657583.333333333</v>
+        <v>1549039.682539683</v>
       </c>
       <c r="AI12" t="n">
-        <v>70.26666666666667</v>
+        <v>70.1952380952381</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22.39454545454545</v>
+        <v>24.76363636363636</v>
       </c>
       <c r="AK12" t="n">
-        <v>180.3763636363637</v>
+        <v>179.0409090909091</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
       </c>
       <c r="AM12" t="n">
-        <v>65.52727272727273</v>
+        <v>66.43181818181817</v>
       </c>
       <c r="AN12" t="n">
-        <v>1783309.090909091</v>
+        <v>1939174.242424242</v>
       </c>
       <c r="AO12" t="n">
-        <v>73.36909090909091</v>
+        <v>72.61818181818181</v>
       </c>
       <c r="AP12" t="n">
-        <v>21.60319008688574</v>
+        <v>21.55795470919694</v>
       </c>
       <c r="AQ12" t="n">
-        <v>180.9041310541311</v>
+        <v>180.9188913915622</v>
       </c>
       <c r="AR12" t="n">
         <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>59.3917228504185</v>
+        <v>59.15859592443444</v>
       </c>
       <c r="AT12" t="n">
-        <v>710347.6579780928</v>
+        <v>678154.2480983475</v>
       </c>
       <c r="AU12" t="n">
-        <v>69.23166109253066</v>
+        <v>69.02678315473347</v>
       </c>
       <c r="AV12" t="n">
-        <v>23.18257918552036</v>
+        <v>25.86842740910246</v>
       </c>
       <c r="AW12" t="n">
-        <v>180.7509502262444</v>
+        <v>179.6100241545894</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AY12" t="n">
-        <v>63.55171945701356</v>
+        <v>64.43808797355707</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1643742.986425339</v>
+        <v>1409403.79481312</v>
       </c>
       <c r="BA12" t="n">
-        <v>71.55380090497736</v>
+        <v>69.27018815153826</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45486.97569444445</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">gonzalez g  jr 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25218</v>
+        <v>72000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2769,171 +2829,153 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>178</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>775000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>65</v>
-      </c>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="X13" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y13" t="n">
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="AB13" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="AC13" t="n">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="AD13" t="n">
-        <v>26.27272727272727</v>
+        <v>26.67103174603175</v>
       </c>
       <c r="AE13" t="n">
-        <v>178.2727272727273</v>
+        <v>179.143253968254</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>1.186507936507937</v>
       </c>
       <c r="AG13" t="n">
-        <v>69.40000000000001</v>
+        <v>68.94603174603175</v>
       </c>
       <c r="AH13" t="n">
-        <v>2870454.545454546</v>
+        <v>2121345.238095238</v>
       </c>
       <c r="AI13" t="n">
-        <v>72.23636363636362</v>
+        <v>72.60515873015872</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24.57636363636363</v>
+        <v>28.35454545454546</v>
       </c>
       <c r="AK13" t="n">
-        <v>178.2890909090909</v>
+        <v>181.1558441558442</v>
       </c>
       <c r="AL13" t="n">
-        <v>1</v>
+        <v>1.379220779220779</v>
       </c>
       <c r="AM13" t="n">
-        <v>66.35818181818181</v>
+        <v>72.04805194805195</v>
       </c>
       <c r="AN13" t="n">
-        <v>2002509.090909091</v>
+        <v>3994870.129870129</v>
       </c>
       <c r="AO13" t="n">
-        <v>72.74181818181816</v>
+        <v>74.59090909090909</v>
       </c>
       <c r="AP13" t="n">
-        <v>26.17086956521739</v>
+        <v>24.41616632160111</v>
       </c>
       <c r="AQ13" t="n">
-        <v>179.8934782608696</v>
+        <v>177.7917356797792</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>1.139311594202899</v>
       </c>
       <c r="AS13" t="n">
-        <v>66.88521739130435</v>
+        <v>66.08472222222221</v>
       </c>
       <c r="AT13" t="n">
-        <v>1638691.304347826</v>
+        <v>2364852.613871635</v>
       </c>
       <c r="AU13" t="n">
-        <v>69.83869565217393</v>
+        <v>72.38803485162181</v>
       </c>
       <c r="AV13" t="n">
-        <v>25.26006160887167</v>
+        <v>24.58154328925246</v>
       </c>
       <c r="AW13" t="n">
-        <v>179.9710033444816</v>
+        <v>179.0381586626745</v>
       </c>
       <c r="AX13" t="n">
-        <v>1</v>
+        <v>1.013354037267081</v>
       </c>
       <c r="AY13" t="n">
-        <v>63.51057736314029</v>
+        <v>66.61309330056133</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1389730.707621898</v>
+        <v>1798994.645288946</v>
       </c>
       <c r="BA13" t="n">
-        <v>69.39781552543567</v>
+        <v>72.94517522423989</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>CfE5JcGF</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45486.97916666666</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22000</v>
+        <v>54405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2958,38 +3000,42 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>21.5</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="U14" t="n">
-        <v>3200000</v>
+        <v>1300000</v>
       </c>
       <c r="V14" t="n">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="W14" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="X14" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
@@ -2998,129 +3044,129 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB14" t="n">
-        <v>50000</v>
+        <v>875000</v>
       </c>
       <c r="AC14" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="AD14" t="n">
-        <v>28.52575757575757</v>
+        <v>25.51969696969697</v>
       </c>
       <c r="AE14" t="n">
-        <v>181.4818181818182</v>
+        <v>177.0681818181818</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.375757575757576</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>72.05757575757575</v>
+        <v>68.54545454545455</v>
       </c>
       <c r="AH14" t="n">
-        <v>3938181.818181818</v>
+        <v>2561818.181818182</v>
       </c>
       <c r="AI14" t="n">
-        <v>74.40454545454546</v>
+        <v>71.42878787878787</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25.94545454545455</v>
+        <v>27.21212121212121</v>
       </c>
       <c r="AK14" t="n">
-        <v>180.5954545454545</v>
+        <v>181.2121212121212</v>
       </c>
       <c r="AL14" t="n">
-        <v>1</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AM14" t="n">
-        <v>69.0469696969697</v>
+        <v>68.45454545454545</v>
       </c>
       <c r="AN14" t="n">
-        <v>3996060.606060606</v>
+        <v>1968636.363636364</v>
       </c>
       <c r="AO14" t="n">
-        <v>72.7</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="AP14" t="n">
-        <v>24.66131030804944</v>
+        <v>24.89524304833229</v>
       </c>
       <c r="AQ14" t="n">
-        <v>178.6249105966498</v>
+        <v>177.8864121766868</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.007246376811594</v>
+        <v>1</v>
       </c>
       <c r="AS14" t="n">
-        <v>66.55596179183135</v>
+        <v>64.84929443173149</v>
       </c>
       <c r="AT14" t="n">
-        <v>1698459.439111613</v>
+        <v>1214233.626308855</v>
       </c>
       <c r="AU14" t="n">
-        <v>72.59878285965243</v>
+        <v>69.44527771999168</v>
       </c>
       <c r="AV14" t="n">
-        <v>24.16379991610171</v>
+        <v>25.05111029919214</v>
       </c>
       <c r="AW14" t="n">
-        <v>180.8364728148615</v>
+        <v>178.9472633256201</v>
       </c>
       <c r="AX14" t="n">
-        <v>1</v>
+        <v>1.029761904761905</v>
       </c>
       <c r="AY14" t="n">
-        <v>64.65429443626375</v>
+        <v>63.12444688020135</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1758076.623161342</v>
+        <v>947557.0499939105</v>
       </c>
       <c r="BA14" t="n">
-        <v>70.44371571641392</v>
+        <v>67.84546137295497</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45486.97916666666</v>
+        <v>45493.98958333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18000</v>
+        <v>27000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -3148,14 +3194,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="Q15" t="n">
-        <v>185.5</v>
+        <v>175</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -3164,115 +3210,115 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="U15" t="n">
-        <v>1225000</v>
+        <v>5100000</v>
       </c>
       <c r="V15" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W15" t="n">
-        <v>24.66666666666667</v>
+        <v>31.5</v>
       </c>
       <c r="X15" t="n">
-        <v>180.3333333333333</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="AB15" t="n">
-        <v>2500000</v>
+        <v>1375000</v>
       </c>
       <c r="AC15" t="n">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="AD15" t="n">
-        <v>26.28333333333333</v>
+        <v>26.03968253968254</v>
       </c>
       <c r="AE15" t="n">
-        <v>180.05</v>
+        <v>178.3888888888889</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>1.028571428571428</v>
       </c>
       <c r="AG15" t="n">
-        <v>68.71666666666667</v>
+        <v>70.48253968253968</v>
       </c>
       <c r="AH15" t="n">
-        <v>2501333.333333333</v>
+        <v>3523095.238095238</v>
       </c>
       <c r="AI15" t="n">
-        <v>72.33333333333333</v>
+        <v>74.31428571428572</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26.85064935064935</v>
+        <v>26.43939393939394</v>
       </c>
       <c r="AK15" t="n">
-        <v>179.9792207792208</v>
+        <v>178.1515151515151</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.04025974025974</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
-        <v>65.06233766233767</v>
+        <v>69.45454545454545</v>
       </c>
       <c r="AN15" t="n">
-        <v>1070603.896103896</v>
+        <v>2875757.575757576</v>
       </c>
       <c r="AO15" t="n">
-        <v>68.77012987012986</v>
+        <v>72.16666666666667</v>
       </c>
       <c r="AP15" t="n">
-        <v>26.55972222222222</v>
+        <v>24.0777085315785</v>
       </c>
       <c r="AQ15" t="n">
-        <v>180.9111111111111</v>
+        <v>180.0209110119327</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>1.060886842775387</v>
       </c>
       <c r="AS15" t="n">
-        <v>66.40833333333333</v>
+        <v>64.44220935583164</v>
       </c>
       <c r="AT15" t="n">
-        <v>1520000</v>
+        <v>1691208.256827452</v>
       </c>
       <c r="AU15" t="n">
-        <v>69.64027777777778</v>
+        <v>70.09800325233762</v>
       </c>
       <c r="AV15" t="n">
-        <v>25.52201232895905</v>
+        <v>26.0481884057971</v>
       </c>
       <c r="AW15" t="n">
-        <v>180.2916974112299</v>
+        <v>179.802536231884</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.06031149301826</v>
+        <v>1</v>
       </c>
       <c r="AY15" t="n">
-        <v>63.37561061037687</v>
+        <v>66.84637681159421</v>
       </c>
       <c r="AZ15" t="n">
-        <v>960495.5264714583</v>
+        <v>1601119.565217391</v>
       </c>
       <c r="BA15" t="n">
-        <v>67.45825666651101</v>
+        <v>69.86557971014493</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
     </row>
